--- a/examples/excel/pivot-tables.xlsx
+++ b/examples/excel/pivot-tables.xlsx
@@ -3,31 +3,31 @@
 <x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="rId1"/>
-    <x:sheet name="CNData" sheetId="2" r:id="R4d1869bec5e84653"/>
-    <x:sheet name="1-Sales Overview" sheetId="3" r:id="Ra99077e4aec24491"/>
-    <x:sheet name="2-Market Share" sheetId="4" r:id="R5df740be5f4d4e6a"/>
-    <x:sheet name="3-Product Deep Dive" sheetId="5" r:id="R8cbcd37d8aaa4cb5"/>
-    <x:sheet name="4-Channel Analysis" sheetId="6" r:id="Rbd2b5b8fd4214a77"/>
-    <x:sheet name="5-Priority Matrix" sheetId="7" r:id="R9dc22268f2a14d2f"/>
-    <x:sheet name="6-Compact 3-Level" sheetId="8" r:id="R4b7e1c8bc3e34b3c"/>
-    <x:sheet name="7-No Subtotals" sheetId="9" r:id="Rb3ecc4d8957447d7"/>
-    <x:sheet name="8-Date Grouping" sheetId="10" r:id="Rb120b69b369f47bd"/>
-    <x:sheet name="9-Top 5 Products" sheetId="11" r:id="R54196c454add439b"/>
-    <x:sheet name="10-Ultimate" sheetId="12" r:id="R5edf80e0791d4a67"/>
-    <x:sheet name="11-Chinese Locale" sheetId="13" r:id="Rf458cb55d44f4872"/>
+    <x:sheet name="CNData" sheetId="2" r:id="Rfa2f4f1d8a56428d"/>
+    <x:sheet name="1-Sales Overview" sheetId="3" r:id="R1ab5d031d8f84159"/>
+    <x:sheet name="2-Market Share" sheetId="4" r:id="Rb52fc8ce73dc4b66"/>
+    <x:sheet name="3-Product Deep Dive" sheetId="5" r:id="Rc043ebb0a3e54231"/>
+    <x:sheet name="4-Channel Analysis" sheetId="6" r:id="R4b8ff493cb3f4154"/>
+    <x:sheet name="5-Priority Matrix" sheetId="7" r:id="Rc261dafdada343e9"/>
+    <x:sheet name="6-Compact 3-Level" sheetId="8" r:id="Rb84b37ac538741d3"/>
+    <x:sheet name="7-No Subtotals" sheetId="9" r:id="R5c3ec716001d4370"/>
+    <x:sheet name="8-Date Grouping" sheetId="10" r:id="Rf5831a060b704b09"/>
+    <x:sheet name="9-Top 5 Products" sheetId="11" r:id="R0a2288c10d9d4908"/>
+    <x:sheet name="10-Ultimate" sheetId="12" r:id="R87396368a8064634"/>
+    <x:sheet name="11-Chinese Locale" sheetId="13" r:id="R8d6ba6f71d664f20"/>
+    <x:sheet name="12-Position + Aggregates" sheetId="14" r:id="R3c272421b0634f62"/>
+    <x:sheet name="13-Calculated Field" sheetId="15" r:id="R7ca93a1ef796497a"/>
+    <x:sheet name="14-Statistical" sheetId="16" r:id="R2dfdc0b142454b90"/>
+    <x:sheet name="15-Independent Totals" sheetId="17" r:id="R43506f9449794503"/>
+    <x:sheet name="16-Style Flags" sheetId="18" r:id="R12f2a17d002f4a34"/>
+    <x:sheet name="17-Display Toggles" sheetId="19" r:id="R298b36fe782a4cfa"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache cacheId="0" r:id="Re8cdfef1ebd440b5"/>
-    <x:pivotCache cacheId="1" r:id="R94b7a82801b14656"/>
-    <x:pivotCache cacheId="2" r:id="R3cc9deabc61449af"/>
-    <x:pivotCache cacheId="3" r:id="Rebb72410b6904e8f"/>
-    <x:pivotCache cacheId="4" r:id="R7c45d229f4fe4971"/>
-    <x:pivotCache cacheId="5" r:id="Rc402d4a76e0942c2"/>
-    <x:pivotCache cacheId="6" r:id="R8997938c96094534"/>
-    <x:pivotCache cacheId="7" r:id="Rac6ebe2dced94863"/>
-    <x:pivotCache cacheId="8" r:id="R3086b897572d4ba5"/>
-    <x:pivotCache cacheId="9" r:id="Rf8c0f52879814921"/>
-    <x:pivotCache cacheId="10" r:id="R5077f46aba404916"/>
+    <x:pivotCache cacheId="0" r:id="Rf0fa8c9e10a94fb4"/>
+    <x:pivotCache cacheId="1" r:id="R4fb92e772a6c4cbf"/>
+    <x:pivotCache cacheId="2" r:id="R22a83956b2354de0"/>
+    <x:pivotCache cacheId="3" r:id="R5e88c575d0e34143"/>
+    <x:pivotCache cacheId="4" r:id="R8a40d7bbe87742a4"/>
   </x:pivotCaches>
 </x:workbook>
 </file>
@@ -80,10 +80,10 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable.xml><?xml version="1.0" encoding="utf-8"?>
-<x:pivotTableDefinition xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="SalesOverview" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" grandTotalCaption="Grand Total" updatedVersion="3" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="Region" colHeaderCaption="Quarter">
+<x:pivotTableDefinition xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="SalesOverview" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" grandTotalCaption="Grand Total" updatedVersion="4" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="Region" colHeaderCaption="Quarter">
   <x:location ref="L4:AB23" firstHeaderRow="1" firstDataRow="3" firstDataCol="2" rowPageCount="2" colPageCount="1"/>
   <x:pivotFields count="10">
-    <x:pivotField axis="axisRow" compact="0" outline="0" showAll="0">
+    <x:pivotField axis="axisRow" compact="0" outline="0" showAll="0" sortType="descending">
       <x:items count="5">
         <x:item x="0"/>
         <x:item x="1"/>
@@ -91,8 +91,13 @@
         <x:item x="3"/>
         <x:item t="default"/>
       </x:items>
+      <x:extLst>
+        <x:ext uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" fillDownLabels="1"/>
+        </x:ext>
+      </x:extLst>
     </x:pivotField>
-    <x:pivotField axis="axisRow" compact="0" outline="0" showAll="0">
+    <x:pivotField axis="axisRow" compact="0" outline="0" showAll="0" sortType="descending">
       <x:items count="4">
         <x:item x="0"/>
         <x:item x="1"/>
@@ -256,19 +261,14 @@
     <x:dataField name="Sum of Cost" fld="6" subtotal="sum" showDataAs="percentOfRow" baseField="0" baseItem="0" numFmtId="10"/>
   </x:dataFields>
   <x:pivotTableStyleInfo name="PivotStyleDark2" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <x:extLst>
-    <x:ext uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" fillDownLabelsDefault="1"/>
-    </x:ext>
-  </x:extLst>
 </x:pivotTableDefinition>
 </file>
 
 <file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
-<x:pivotTableDefinition xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="UltimatePivot" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" grandTotalCaption="Grand Total" updatedVersion="3" minRefreshableVersion="3" useAutoFormatting="1" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="Region" colHeaderCaption="Quarter">
+<x:pivotTableDefinition xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="UltimatePivot" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" grandTotalCaption="Grand Total" updatedVersion="4" minRefreshableVersion="3" useAutoFormatting="1" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="Region" colHeaderCaption="Quarter">
   <x:location ref="L4:Y27" firstHeaderRow="1" firstDataRow="3" firstDataCol="2" rowPageCount="2" colPageCount="1"/>
   <x:pivotFields count="10">
-    <x:pivotField axis="axisRow" compact="0" outline="0" showAll="0" insertBlankRow="1">
+    <x:pivotField axis="axisRow" compact="0" outline="0" showAll="0" insertBlankRow="1" sortType="descending">
       <x:items count="5">
         <x:item x="0"/>
         <x:item x="1"/>
@@ -276,8 +276,13 @@
         <x:item x="3"/>
         <x:item t="default"/>
       </x:items>
+      <x:extLst>
+        <x:ext uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" fillDownLabels="1"/>
+        </x:ext>
+      </x:extLst>
     </x:pivotField>
-    <x:pivotField axis="axisRow" compact="0" outline="0" showAll="0" insertBlankRow="1">
+    <x:pivotField axis="axisRow" compact="0" outline="0" showAll="0" insertBlankRow="1" sortType="descending">
       <x:items count="4">
         <x:item x="0"/>
         <x:item x="1"/>
@@ -444,19 +449,14 @@
     <x:dataField name="Sum of Cost" fld="6" subtotal="sum" showDataAs="percentOfRow" baseField="0" baseItem="0" numFmtId="10"/>
   </x:dataFields>
   <x:pivotTableStyleInfo name="PivotStyleDark11" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <x:extLst>
-    <x:ext uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" fillDownLabelsDefault="1"/>
-    </x:ext>
-  </x:extLst>
 </x:pivotTableDefinition>
 </file>
 
 <file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
-<x:pivotTableDefinition xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="ChineseLocale" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" grandTotalCaption="合计" updatedVersion="3" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="地区" colHeaderCaption="Columns">
+<x:pivotTableDefinition xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="ChineseLocale" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" grandTotalCaption="合计" updatedVersion="4" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="地区" colHeaderCaption="Columns">
   <x:location ref="E1:G18" firstHeaderRow="1" firstDataRow="1" firstDataCol="2"/>
   <x:pivotFields count="3">
-    <x:pivotField axis="axisRow" compact="0" outline="0" showAll="0">
+    <x:pivotField axis="axisRow" compact="0" outline="0" showAll="0" sortType="ascending">
       <x:items count="5">
         <x:item x="0"/>
         <x:item x="1"/>
@@ -465,7 +465,7 @@
         <x:item t="default"/>
       </x:items>
     </x:pivotField>
-    <x:pivotField axis="axisRow" compact="0" outline="0" showAll="0">
+    <x:pivotField axis="axisRow" compact="0" outline="0" showAll="0" sortType="ascending">
       <x:items count="4">
         <x:item x="0"/>
         <x:item x="1"/>
@@ -546,24 +546,559 @@
 </x:pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:pivotTableDefinition xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="MarketShare" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" grandTotalCaption="Grand Total" updatedVersion="3" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" outline="1" outlineData="1" compactData="0" multipleFieldFilters="0" rowHeaderCaption="Region" colHeaderCaption="Category">
-  <x:location ref="L3:P9" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+<file path=xl/pivotTables/pivotTable12.xml><?xml version="1.0" encoding="utf-8"?>
+<x:pivotTableDefinition xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PositionAggs" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" grandTotalCaption="Grand Total" updatedVersion="4" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="Category" colHeaderCaption="Columns">
+  <x:location ref="D2:H7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <x:pivotFields count="10">
-    <x:pivotField axis="axisRow" compact="0" showAll="0">
+    <x:pivotField compact="0" outline="0" showAll="0"/>
+    <x:pivotField axis="axisRow" compact="0" outline="0" showAll="0">
+      <x:items count="4">
+        <x:item x="2"/>
+        <x:item x="1"/>
+        <x:item x="0"/>
+        <x:item t="default"/>
+      </x:items>
+    </x:pivotField>
+    <x:pivotField compact="0" outline="0" showAll="0"/>
+    <x:pivotField compact="0" outline="0" showAll="0"/>
+    <x:pivotField dataField="1" compact="0" outline="0" showAll="0"/>
+    <x:pivotField dataField="1" compact="0" outline="0" showAll="0"/>
+    <x:pivotField compact="0" outline="0" showAll="0"/>
+    <x:pivotField compact="0" outline="0" showAll="0"/>
+    <x:pivotField compact="0" outline="0" showAll="0"/>
+    <x:pivotField compact="0" outline="0" showAll="0"/>
+  </x:pivotFields>
+  <x:rowFields count="1">
+    <x:field x="1"/>
+  </x:rowFields>
+  <x:rowItems count="4">
+    <x:i>
+      <x:x/>
+    </x:i>
+    <x:i>
+      <x:x v="1"/>
+    </x:i>
+    <x:i>
+      <x:x v="2"/>
+    </x:i>
+    <x:i t="grand">
+      <x:x/>
+    </x:i>
+  </x:rowItems>
+  <x:colFields count="1">
+    <x:field x="-2"/>
+  </x:colFields>
+  <x:colItems count="4">
+    <x:i>
+      <x:x/>
+    </x:i>
+    <x:i i="1">
+      <x:x/>
+    </x:i>
+    <x:i i="2">
+      <x:x/>
+    </x:i>
+    <x:i i="3">
+      <x:x/>
+    </x:i>
+  </x:colItems>
+  <x:dataFields count="4">
+    <x:dataField name="Avg of Sales" fld="4" subtotal="average" baseField="0" baseItem="0"/>
+    <x:dataField name="Min of Quantity" fld="5" subtotal="min" baseField="0" baseItem="0"/>
+    <x:dataField name="Product of Quantity" fld="5" subtotal="product" baseField="0" baseItem="0"/>
+    <x:dataField name="Countnums of Sales" fld="4" subtotal="countNums" baseField="0" baseItem="0"/>
+  </x:dataFields>
+  <x:pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+</x:pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable13.xml><?xml version="1.0" encoding="utf-8"?>
+<x:pivotTableDefinition xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="CalcField" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" grandTotalCaption="Grand Total" updatedVersion="4" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="Region" colHeaderCaption="Columns">
+  <x:location ref="L1:O4" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <x:pivotFields count="12">
+    <x:pivotField axis="axisRow" compact="0" outline="0" showAll="0">
+      <x:items count="2">
+        <x:item x="1"/>
+        <x:item t="default"/>
+      </x:items>
+    </x:pivotField>
+    <x:pivotField compact="0" outline="0" showAll="0"/>
+    <x:pivotField compact="0" outline="0" showAll="0"/>
+    <x:pivotField compact="0" outline="0" showAll="0"/>
+    <x:pivotField dataField="1" compact="0" outline="0" showAll="0"/>
+    <x:pivotField compact="0" outline="0" showAll="0"/>
+    <x:pivotField compact="0" outline="0" showAll="0"/>
+    <x:pivotField compact="0" outline="0" showAll="0"/>
+    <x:pivotField compact="0" outline="0" showAll="0"/>
+    <x:pivotField compact="0" outline="0" showAll="0"/>
+    <x:pivotField dataField="1" compact="0" outline="0" dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <x:pivotField dataField="1" compact="0" outline="0" dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+  </x:pivotFields>
+  <x:rowFields count="1">
+    <x:field x="0"/>
+  </x:rowFields>
+  <x:rowItems count="2">
+    <x:i>
+      <x:x/>
+    </x:i>
+    <x:i t="grand">
+      <x:x/>
+    </x:i>
+  </x:rowItems>
+  <x:colFields count="1">
+    <x:field x="-2"/>
+  </x:colFields>
+  <x:colItems count="3">
+    <x:i>
+      <x:x/>
+    </x:i>
+    <x:i i="1">
+      <x:x v="1"/>
+    </x:i>
+    <x:i i="2">
+      <x:x v="2"/>
+    </x:i>
+  </x:colItems>
+  <x:dataFields count="3">
+    <x:dataField name="Sum of Sales" fld="4" subtotal="sum" baseField="0" baseItem="0"/>
+    <x:dataField name="Sum of Margin" fld="10" baseField="0" baseItem="0"/>
+    <x:dataField name="Sum of Tax" fld="11" baseField="0" baseItem="0"/>
+  </x:dataFields>
+  <x:pivotTableStyleInfo name="PivotStyleMedium3" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <x:filters count="1">
+    <x:filter fld="0" type="captionBeginsWith" evalOrder="-1" id="1" stringValue1="N">
+      <x:autoFilter ref="A1">
+        <x:filterColumn colId="0">
+          <x:customFilters>
+            <x:customFilter val="N*"/>
+          </x:customFilters>
+        </x:filterColumn>
+      </x:autoFilter>
+    </x:filter>
+  </x:filters>
+</x:pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable14.xml><?xml version="1.0" encoding="utf-8"?>
+<x:pivotTableDefinition xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Statistical" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" grandTotalCaption="Grand Total" updatedVersion="4" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="Region" colHeaderCaption="Quarter">
+  <x:location ref="L1:AA8" firstHeaderRow="1" firstDataRow="3" firstDataCol="1"/>
+  <x:pivotFields count="10">
+    <x:pivotField axis="axisRow" compact="0" outline="0" showAll="0">
       <x:items count="5">
+        <x:item x="3"/>
+        <x:item x="2"/>
+        <x:item x="1"/>
         <x:item x="0"/>
+        <x:item t="default"/>
+      </x:items>
+    </x:pivotField>
+    <x:pivotField compact="0" outline="0" showAll="0"/>
+    <x:pivotField compact="0" outline="0" showAll="0"/>
+    <x:pivotField axis="axisCol" compact="0" outline="0" showAll="0">
+      <x:items count="5">
+        <x:item x="3"/>
+        <x:item x="2"/>
         <x:item x="1"/>
+        <x:item x="0"/>
+        <x:item t="default"/>
+      </x:items>
+    </x:pivotField>
+    <x:pivotField dataField="1" compact="0" outline="0" showAll="0"/>
+    <x:pivotField compact="0" outline="0" showAll="0"/>
+    <x:pivotField compact="0" outline="0" showAll="0"/>
+    <x:pivotField compact="0" outline="0" showAll="0"/>
+    <x:pivotField compact="0" outline="0" showAll="0"/>
+    <x:pivotField compact="0" outline="0" showAll="0"/>
+  </x:pivotFields>
+  <x:rowFields count="1">
+    <x:field x="0"/>
+  </x:rowFields>
+  <x:rowItems count="5">
+    <x:i>
+      <x:x/>
+    </x:i>
+    <x:i>
+      <x:x v="1"/>
+    </x:i>
+    <x:i>
+      <x:x v="2"/>
+    </x:i>
+    <x:i>
+      <x:x v="3"/>
+    </x:i>
+    <x:i t="grand">
+      <x:x/>
+    </x:i>
+  </x:rowItems>
+  <x:colFields count="2">
+    <x:field x="3"/>
+    <x:field x="-2"/>
+  </x:colFields>
+  <x:colItems count="15">
+    <x:i>
+      <x:x/>
+      <x:x/>
+    </x:i>
+    <x:i r="1" i="1">
+      <x:x v="1"/>
+    </x:i>
+    <x:i r="1" i="2">
+      <x:x v="2"/>
+    </x:i>
+    <x:i>
+      <x:x v="1"/>
+      <x:x/>
+    </x:i>
+    <x:i r="1" i="1">
+      <x:x v="1"/>
+    </x:i>
+    <x:i r="1" i="2">
+      <x:x v="2"/>
+    </x:i>
+    <x:i>
+      <x:x v="2"/>
+      <x:x/>
+    </x:i>
+    <x:i r="1" i="1">
+      <x:x v="1"/>
+    </x:i>
+    <x:i r="1" i="2">
+      <x:x v="2"/>
+    </x:i>
+    <x:i>
+      <x:x v="3"/>
+      <x:x/>
+    </x:i>
+    <x:i r="1" i="1">
+      <x:x v="1"/>
+    </x:i>
+    <x:i r="1" i="2">
+      <x:x v="2"/>
+    </x:i>
+    <x:i t="grand">
+      <x:x/>
+    </x:i>
+    <x:i t="grand" i="1">
+      <x:x/>
+    </x:i>
+    <x:i t="grand" i="2">
+      <x:x/>
+    </x:i>
+  </x:colItems>
+  <x:dataFields count="3">
+    <x:dataField name="Var of Sales" fld="4" subtotal="var" showDataAs="runTotal" baseField="0" baseItem="0"/>
+    <x:dataField name="Varp of Sales" fld="4" subtotal="varp" baseField="0" baseItem="0"/>
+    <x:dataField name="Sum of Sales" fld="4" subtotal="sum" baseField="0" baseItem="0"/>
+  </x:dataFields>
+  <x:pivotTableStyleInfo name="PivotStyleLight10" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+</x:pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable15.xml><?xml version="1.0" encoding="utf-8"?>
+<x:pivotTableDefinition xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="IndepTotals" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" grandTotalCaption="Grand Total" updatedVersion="4" minRefreshableVersion="3" useAutoFormatting="1" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" outline="1" outlineData="1" compactData="0" multipleFieldFilters="0" rowHeaderCaption="地区" colHeaderCaption="品类">
+  <x:location ref="E1:H7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <x:pivotFields count="3">
+    <x:pivotField axis="axisRow" compact="0" showAll="0" sortType="descending">
+      <x:items count="5">
+        <x:item x="3"/>
         <x:item x="2"/>
-        <x:item x="3"/>
+        <x:item x="1"/>
+        <x:item x="0"/>
         <x:item t="default"/>
       </x:items>
     </x:pivotField>
     <x:pivotField axis="axisCol" compact="0" showAll="0">
       <x:items count="4">
+        <x:item x="2"/>
+        <x:item x="1"/>
         <x:item x="0"/>
+        <x:item t="default"/>
+      </x:items>
+    </x:pivotField>
+    <x:pivotField dataField="1" compact="0" showAll="0"/>
+  </x:pivotFields>
+  <x:rowFields count="1">
+    <x:field x="0"/>
+  </x:rowFields>
+  <x:rowItems count="5">
+    <x:i>
+      <x:x/>
+    </x:i>
+    <x:i>
+      <x:x v="1"/>
+    </x:i>
+    <x:i>
+      <x:x v="2"/>
+    </x:i>
+    <x:i>
+      <x:x v="3"/>
+    </x:i>
+    <x:i t="grand">
+      <x:x/>
+    </x:i>
+  </x:rowItems>
+  <x:colFields count="1">
+    <x:field x="1"/>
+  </x:colFields>
+  <x:colItems count="3">
+    <x:i>
+      <x:x/>
+    </x:i>
+    <x:i>
+      <x:x v="1"/>
+    </x:i>
+    <x:i>
+      <x:x v="2"/>
+    </x:i>
+  </x:colItems>
+  <x:dataFields count="1">
+    <x:dataField name="Sum of 销售额" fld="2" subtotal="sum" baseField="0" baseItem="0"/>
+  </x:dataFields>
+  <x:pivotTableStyleInfo name="PivotStyleMedium11" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+</x:pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable16.xml><?xml version="1.0" encoding="utf-8"?>
+<x:pivotTableDefinition xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="StyleFlags" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" grandTotalCaption="Grand Total" updatedVersion="4" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="Region" colHeaderCaption="Quarter">
+  <x:location ref="L1:R19" firstHeaderRow="1" firstDataRow="2" firstDataCol="2"/>
+  <x:pivotFields count="10">
+    <x:pivotField axis="axisRow" compact="0" outline="0" showAll="0">
+      <x:items count="5">
+        <x:item x="3"/>
+        <x:item x="2"/>
         <x:item x="1"/>
+        <x:item x="0"/>
+        <x:item t="default"/>
+      </x:items>
+    </x:pivotField>
+    <x:pivotField axis="axisRow" compact="0" outline="0" showAll="0">
+      <x:items count="4">
         <x:item x="2"/>
+        <x:item x="1"/>
+        <x:item x="0"/>
+        <x:item t="default"/>
+      </x:items>
+    </x:pivotField>
+    <x:pivotField compact="0" outline="0" showAll="0"/>
+    <x:pivotField axis="axisCol" compact="0" outline="0" showAll="0">
+      <x:items count="5">
+        <x:item x="3"/>
+        <x:item x="2"/>
+        <x:item x="1"/>
+        <x:item x="0"/>
+        <x:item t="default"/>
+      </x:items>
+    </x:pivotField>
+    <x:pivotField dataField="1" compact="0" outline="0" showAll="0"/>
+    <x:pivotField compact="0" outline="0" showAll="0"/>
+    <x:pivotField compact="0" outline="0" showAll="0"/>
+    <x:pivotField compact="0" outline="0" showAll="0"/>
+    <x:pivotField compact="0" outline="0" showAll="0"/>
+    <x:pivotField compact="0" outline="0" showAll="0"/>
+  </x:pivotFields>
+  <x:rowFields count="2">
+    <x:field x="0"/>
+    <x:field x="1"/>
+  </x:rowFields>
+  <x:rowItems count="17">
+    <x:i>
+      <x:x/>
+      <x:x/>
+    </x:i>
+    <x:i r="1">
+      <x:x v="1"/>
+    </x:i>
+    <x:i r="1">
+      <x:x v="2"/>
+    </x:i>
+    <x:i t="default">
+      <x:x/>
+    </x:i>
+    <x:i>
+      <x:x v="1"/>
+      <x:x/>
+    </x:i>
+    <x:i r="1">
+      <x:x v="1"/>
+    </x:i>
+    <x:i r="1">
+      <x:x v="2"/>
+    </x:i>
+    <x:i t="default">
+      <x:x v="1"/>
+    </x:i>
+    <x:i>
+      <x:x v="2"/>
+      <x:x/>
+    </x:i>
+    <x:i r="1">
+      <x:x v="1"/>
+    </x:i>
+    <x:i r="1">
+      <x:x v="2"/>
+    </x:i>
+    <x:i t="default">
+      <x:x v="2"/>
+    </x:i>
+    <x:i>
+      <x:x v="3"/>
+      <x:x/>
+    </x:i>
+    <x:i r="1">
+      <x:x v="1"/>
+    </x:i>
+    <x:i r="1">
+      <x:x v="2"/>
+    </x:i>
+    <x:i t="default">
+      <x:x v="3"/>
+    </x:i>
+    <x:i t="grand">
+      <x:x/>
+    </x:i>
+  </x:rowItems>
+  <x:colFields count="1">
+    <x:field x="3"/>
+  </x:colFields>
+  <x:colItems count="5">
+    <x:i>
+      <x:x/>
+    </x:i>
+    <x:i>
+      <x:x v="1"/>
+    </x:i>
+    <x:i>
+      <x:x v="2"/>
+    </x:i>
+    <x:i>
+      <x:x v="3"/>
+    </x:i>
+    <x:i t="grand">
+      <x:x/>
+    </x:i>
+  </x:colItems>
+  <x:dataFields count="1">
+    <x:dataField name="Sum of Sales" fld="4" subtotal="sum" baseField="0" baseItem="0"/>
+  </x:dataFields>
+  <x:pivotTableStyleInfo name="PivotStyleMedium17" showRowHeaders="1" showColHeaders="1" showRowStripes="1" showColStripes="1" showLastColumn="1"/>
+</x:pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable17.xml><?xml version="1.0" encoding="utf-8"?>
+<x:pivotTableDefinition xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="DisplayToggles" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" grandTotalCaption="Grand Total" updatedVersion="4" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" mergeItem="1" createdVersion="3" indent="0" compact="0" outline="1" outlineData="1" compactData="0" multipleFieldFilters="0" rowHeaderCaption="Region" colHeaderCaption="Columns">
+  <x:location ref="L1:N18" firstHeaderRow="0" firstDataRow="1" firstDataCol="2"/>
+  <x:pivotFields count="10">
+    <x:pivotField axis="axisRow" showDropDowns="0" compact="0" showAll="0">
+      <x:items count="5">
+        <x:item x="3"/>
+        <x:item x="2"/>
+        <x:item x="1"/>
+        <x:item x="0"/>
+        <x:item t="default"/>
+      </x:items>
+    </x:pivotField>
+    <x:pivotField axis="axisRow" showDropDowns="0" compact="0" showAll="0">
+      <x:items count="4">
+        <x:item x="2"/>
+        <x:item x="1"/>
+        <x:item x="0"/>
+        <x:item t="default"/>
+      </x:items>
+    </x:pivotField>
+    <x:pivotField showDropDowns="0" compact="0" showAll="0"/>
+    <x:pivotField showDropDowns="0" compact="0" showAll="0"/>
+    <x:pivotField dataField="1" showDropDowns="0" compact="0" showAll="0"/>
+    <x:pivotField showDropDowns="0" compact="0" showAll="0"/>
+    <x:pivotField showDropDowns="0" compact="0" showAll="0"/>
+    <x:pivotField showDropDowns="0" compact="0" showAll="0"/>
+    <x:pivotField showDropDowns="0" compact="0" showAll="0"/>
+    <x:pivotField showDropDowns="0" compact="0" showAll="0"/>
+  </x:pivotFields>
+  <x:rowFields count="2">
+    <x:field x="0"/>
+    <x:field x="1"/>
+  </x:rowFields>
+  <x:rowItems count="17">
+    <x:i>
+      <x:x/>
+    </x:i>
+    <x:i r="1">
+      <x:x/>
+    </x:i>
+    <x:i r="1">
+      <x:x v="1"/>
+    </x:i>
+    <x:i r="1">
+      <x:x v="2"/>
+    </x:i>
+    <x:i>
+      <x:x v="1"/>
+    </x:i>
+    <x:i r="1">
+      <x:x/>
+    </x:i>
+    <x:i r="1">
+      <x:x v="1"/>
+    </x:i>
+    <x:i r="1">
+      <x:x v="2"/>
+    </x:i>
+    <x:i>
+      <x:x v="2"/>
+    </x:i>
+    <x:i r="1">
+      <x:x/>
+    </x:i>
+    <x:i r="1">
+      <x:x v="1"/>
+    </x:i>
+    <x:i r="1">
+      <x:x v="2"/>
+    </x:i>
+    <x:i>
+      <x:x v="3"/>
+    </x:i>
+    <x:i r="1">
+      <x:x/>
+    </x:i>
+    <x:i r="1">
+      <x:x v="1"/>
+    </x:i>
+    <x:i r="1">
+      <x:x v="2"/>
+    </x:i>
+    <x:i t="grand">
+      <x:x/>
+    </x:i>
+  </x:rowItems>
+  <x:colItems count="1">
+    <x:i/>
+  </x:colItems>
+  <x:dataFields count="1">
+    <x:dataField name="Sum of Sales" fld="4" subtotal="sum" baseField="0" baseItem="0"/>
+  </x:dataFields>
+  <x:pivotTableStyleInfo name="PivotStyleLight19" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+</x:pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<x:pivotTableDefinition xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="MarketShare" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" grandTotalCaption="Grand Total" updatedVersion="4" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" outline="1" outlineData="1" compactData="0" multipleFieldFilters="0" rowHeaderCaption="Region" colHeaderCaption="Category">
+  <x:location ref="L3:P9" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <x:pivotFields count="10">
+    <x:pivotField axis="axisRow" compact="0" showAll="0">
+      <x:items count="5">
+        <x:item x="3"/>
+        <x:item x="2"/>
+        <x:item x="1"/>
+        <x:item x="0"/>
+        <x:item t="default"/>
+      </x:items>
+    </x:pivotField>
+    <x:pivotField axis="axisCol" compact="0" showAll="0">
+      <x:items count="4">
+        <x:item x="2"/>
+        <x:item x="1"/>
+        <x:item x="0"/>
         <x:item t="default"/>
       </x:items>
     </x:pivotField>
@@ -574,8 +1109,8 @@
     <x:pivotField compact="0" showAll="0"/>
     <x:pivotField axis="axisPage" compact="0" showAll="0">
       <x:items count="3">
+        <x:item x="1"/>
         <x:item x="0"/>
-        <x:item x="1"/>
         <x:item t="default"/>
       </x:items>
     </x:pivotField>
@@ -630,7 +1165,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:pivotTableDefinition xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="ProductDeepDive" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" grandTotalCaption="Grand Total" updatedVersion="3" minRefreshableVersion="3" useAutoFormatting="1" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="Category" colHeaderCaption="Columns">
+<x:pivotTableDefinition xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="ProductDeepDive" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" grandTotalCaption="Grand Total" updatedVersion="4" minRefreshableVersion="3" useAutoFormatting="1" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="Category" colHeaderCaption="Columns">
   <x:location ref="L3:R17" firstHeaderRow="1" firstDataRow="2" firstDataCol="2" rowPageCount="1" colPageCount="1"/>
   <x:pivotFields count="10">
     <x:pivotField axis="axisPage" compact="0" outline="0" showAll="0">
@@ -642,7 +1177,7 @@
         <x:item t="default"/>
       </x:items>
     </x:pivotField>
-    <x:pivotField axis="axisRow" compact="0" outline="0" showAll="0">
+    <x:pivotField axis="axisRow" compact="0" outline="0" showAll="0" sortType="descending">
       <x:items count="4">
         <x:item x="0"/>
         <x:item x="1"/>
@@ -650,7 +1185,7 @@
         <x:item t="default"/>
       </x:items>
     </x:pivotField>
-    <x:pivotField axis="axisRow" compact="0" outline="0" showAll="0">
+    <x:pivotField axis="axisRow" compact="0" outline="0" showAll="0" sortType="descending">
       <x:items count="10">
         <x:item x="0"/>
         <x:item x="1"/>
@@ -755,7 +1290,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:pivotTableDefinition xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="ChannelTrend" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" grandTotalCaption="Grand Total" updatedVersion="3" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" outline="1" outlineData="1" compactData="0" multipleFieldFilters="0" rowHeaderCaption="Channel" colHeaderCaption="Quarter">
+<x:pivotTableDefinition xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="ChannelTrend" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" grandTotalCaption="Grand Total" updatedVersion="4" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" outline="1" outlineData="1" compactData="0" multipleFieldFilters="0" rowHeaderCaption="Channel" colHeaderCaption="Quarter">
   <x:location ref="L1:V6" firstHeaderRow="1" firstDataRow="3" firstDataCol="1"/>
   <x:pivotFields count="10">
     <x:pivotField compact="0" showAll="0"/>
@@ -763,10 +1298,10 @@
     <x:pivotField compact="0" showAll="0"/>
     <x:pivotField axis="axisCol" compact="0" showAll="0">
       <x:items count="5">
+        <x:item x="3"/>
+        <x:item x="2"/>
+        <x:item x="1"/>
         <x:item x="0"/>
-        <x:item x="1"/>
-        <x:item x="2"/>
-        <x:item x="3"/>
         <x:item t="default"/>
       </x:items>
     </x:pivotField>
@@ -775,8 +1310,8 @@
     <x:pivotField compact="0" showAll="0"/>
     <x:pivotField axis="axisRow" compact="0" showAll="0">
       <x:items count="3">
+        <x:item x="1"/>
         <x:item x="0"/>
-        <x:item x="1"/>
         <x:item t="default"/>
       </x:items>
     </x:pivotField>
@@ -846,23 +1381,23 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:pivotTableDefinition xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PriorityMatrix" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" grandTotalCaption="Grand Total" updatedVersion="3" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="Priority" colHeaderCaption="Category">
+<x:pivotTableDefinition xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PriorityMatrix" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" grandTotalCaption="Grand Total" updatedVersion="4" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="Priority" colHeaderCaption="Category">
   <x:location ref="L3:U24" firstHeaderRow="1" firstDataRow="3" firstDataCol="2" rowPageCount="1" colPageCount="1"/>
   <x:pivotFields count="10">
-    <x:pivotField axis="axisRow" compact="0" outline="0" showAll="0" insertBlankRow="1">
+    <x:pivotField axis="axisRow" compact="0" outline="0" showAll="0" insertBlankRow="1" sortType="ascending">
       <x:items count="5">
+        <x:item x="3"/>
+        <x:item x="2"/>
+        <x:item x="1"/>
         <x:item x="0"/>
-        <x:item x="1"/>
-        <x:item x="2"/>
-        <x:item x="3"/>
         <x:item t="default"/>
       </x:items>
     </x:pivotField>
     <x:pivotField axis="axisCol" compact="0" outline="0" showAll="0" insertBlankRow="1">
       <x:items count="4">
+        <x:item x="2"/>
+        <x:item x="1"/>
         <x:item x="0"/>
-        <x:item x="1"/>
-        <x:item x="2"/>
         <x:item t="default"/>
       </x:items>
     </x:pivotField>
@@ -873,16 +1408,16 @@
     <x:pivotField dataField="1" compact="0" outline="0" showAll="0" insertBlankRow="1"/>
     <x:pivotField axis="axisPage" compact="0" outline="0" showAll="0" insertBlankRow="1">
       <x:items count="3">
+        <x:item x="1"/>
         <x:item x="0"/>
-        <x:item x="1"/>
         <x:item t="default"/>
       </x:items>
     </x:pivotField>
-    <x:pivotField axis="axisRow" compact="0" outline="0" showAll="0" insertBlankRow="1">
+    <x:pivotField axis="axisRow" compact="0" outline="0" showAll="0" insertBlankRow="1" sortType="ascending">
       <x:items count="4">
+        <x:item x="2"/>
+        <x:item x="1"/>
         <x:item x="0"/>
-        <x:item x="1"/>
-        <x:item x="2"/>
         <x:item t="default"/>
       </x:items>
     </x:pivotField>
@@ -999,10 +1534,10 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:pivotTableDefinition xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Compact3Level" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" grandTotalCaption="Grand Total" updatedVersion="3" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="3" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Region" colHeaderCaption="Columns">
+<x:pivotTableDefinition xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Compact3Level" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" grandTotalCaption="Grand Total" updatedVersion="4" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="3" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Region" colHeaderCaption="Columns">
   <x:location ref="L3:N57" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <x:pivotFields count="10">
-    <x:pivotField axis="axisRow" showAll="0">
+    <x:pivotField axis="axisRow" showAll="0" sortType="descending">
       <x:items count="5">
         <x:item x="0"/>
         <x:item x="1"/>
@@ -1011,7 +1546,7 @@
         <x:item t="default"/>
       </x:items>
     </x:pivotField>
-    <x:pivotField axis="axisRow" showAll="0">
+    <x:pivotField axis="axisRow" showAll="0" sortType="descending">
       <x:items count="4">
         <x:item x="0"/>
         <x:item x="1"/>
@@ -1019,7 +1554,7 @@
         <x:item t="default"/>
       </x:items>
     </x:pivotField>
-    <x:pivotField axis="axisRow" showAll="0">
+    <x:pivotField axis="axisRow" showAll="0" sortType="descending">
       <x:items count="10">
         <x:item x="0"/>
         <x:item x="1"/>
@@ -1237,31 +1772,36 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<x:pivotTableDefinition xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="FlatView" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" grandTotalCaption="Grand Total" updatedVersion="3" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="Region" colHeaderCaption="Quarter">
+<x:pivotTableDefinition xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="FlatView" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" grandTotalCaption="Grand Total" updatedVersion="4" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="Region" colHeaderCaption="Quarter">
   <x:location ref="L1:R14" firstHeaderRow="1" firstDataRow="2" firstDataCol="2"/>
   <x:pivotFields count="10">
-    <x:pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
+    <x:pivotField axis="axisRow" compact="0" outline="0" showAll="0" sortType="ascending" defaultSubtotal="0">
       <x:items count="4">
+        <x:item x="3"/>
+        <x:item x="2"/>
+        <x:item x="1"/>
         <x:item x="0"/>
+      </x:items>
+      <x:extLst>
+        <x:ext uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" fillDownLabels="1"/>
+        </x:ext>
+      </x:extLst>
+    </x:pivotField>
+    <x:pivotField axis="axisRow" compact="0" outline="0" showAll="0" sortType="ascending" defaultSubtotal="0">
+      <x:items count="3">
+        <x:item x="2"/>
         <x:item x="1"/>
-        <x:item x="2"/>
-        <x:item x="3"/>
-      </x:items>
-    </x:pivotField>
-    <x:pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
-      <x:items count="3">
         <x:item x="0"/>
-        <x:item x="1"/>
-        <x:item x="2"/>
       </x:items>
     </x:pivotField>
     <x:pivotField compact="0" outline="0" showAll="0"/>
     <x:pivotField axis="axisCol" compact="0" outline="0" showAll="0" defaultSubtotal="0">
       <x:items count="4">
+        <x:item x="3"/>
+        <x:item x="2"/>
+        <x:item x="1"/>
         <x:item x="0"/>
-        <x:item x="1"/>
-        <x:item x="2"/>
-        <x:item x="3"/>
       </x:items>
     </x:pivotField>
     <x:pivotField dataField="1" compact="0" outline="0" showAll="0"/>
@@ -1341,16 +1881,11 @@
     <x:dataField name="Sum of Sales" fld="4" subtotal="sum" baseField="0" baseItem="0"/>
   </x:dataFields>
   <x:pivotTableStyleInfo name="PivotStyleLight1" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <x:extLst>
-    <x:ext uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" fillDownLabelsDefault="1"/>
-    </x:ext>
-  </x:extLst>
 </x:pivotTableDefinition>
 </file>
 
 <file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<x:pivotTableDefinition xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="DateGrouping" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" grandTotalCaption="Grand Total" updatedVersion="3" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" outline="1" outlineData="1" compactData="0" multipleFieldFilters="0" rowHeaderCaption="Date (Year)" colHeaderCaption="Columns">
+<x:pivotTableDefinition xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="DateGrouping" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" grandTotalCaption="Grand Total" updatedVersion="4" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" outline="1" outlineData="1" compactData="0" multipleFieldFilters="0" rowHeaderCaption="Date (Year)" colHeaderCaption="Columns">
   <x:location ref="L3:O15" firstHeaderRow="1" firstDataRow="2" firstDataCol="2" rowPageCount="1" colPageCount="1"/>
   <x:pivotFields count="12">
     <x:pivotField axis="axisPage" compact="0" showAll="0">
@@ -1454,12 +1989,12 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
-<x:pivotTableDefinition xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Top5Products" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" grandTotalCaption="Grand Total" updatedVersion="3" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="Product" colHeaderCaption="Columns">
-  <x:location ref="L1:O8" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+<x:pivotTableDefinition xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Top5Products" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" grandTotalCaption="Grand Total" updatedVersion="4" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="3" indent="0" compact="0" compactData="0" multipleFieldFilters="0" rowHeaderCaption="Product" colHeaderCaption="Columns">
+  <x:location ref="L1:O7" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <x:pivotFields count="10">
     <x:pivotField compact="0" outline="0" showAll="0"/>
     <x:pivotField compact="0" outline="0" showAll="0"/>
-    <x:pivotField axis="axisRow" compact="0" outline="0" showAll="0">
+    <x:pivotField axis="axisRow" compact="0" outline="0" showAll="0" sortType="descending">
       <x:items count="6">
         <x:item x="0"/>
         <x:item x="1"/>
@@ -1517,6 +2052,15 @@
     <x:dataField name="Sum of Cost" fld="6" subtotal="sum" baseField="0" baseItem="0"/>
   </x:dataFields>
   <x:pivotTableStyleInfo name="PivotStyleDark1" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <x:filters count="1">
+    <x:filter fld="2" type="count" evalOrder="-1" id="1" iMeasureFld="0">
+      <x:autoFilter ref="A1">
+        <x:filterColumn colId="0">
+          <x:top10 val="5" filterVal="5"/>
+        </x:filterColumn>
+      </x:autoFilter>
+    </x:filter>
+  </x:filters>
 </x:pivotTableDefinition>
 </file>
 
@@ -3612,7 +4156,7 @@
         <x:v>400</x:v>
       </x:c>
       <x:c r="P7">
-        <x:v>2900</x:v>
+        <x:v>0.3558282208588957</x:v>
       </x:c>
       <x:c r="Q7">
         <x:v>3200</x:v>
@@ -3621,7 +4165,7 @@
         <x:v>260</x:v>
       </x:c>
       <x:c r="S7">
-        <x:v>1600</x:v>
+        <x:v>0.19631901840490798</x:v>
       </x:c>
       <x:c r="T7">
         <x:v>2800</x:v>
@@ -3630,7 +4174,7 @@
         <x:v>280</x:v>
       </x:c>
       <x:c r="V7">
-        <x:v>1400</x:v>
+        <x:v>0.17177914110429449</x:v>
       </x:c>
       <x:c r="W7">
         <x:v>4500</x:v>
@@ -3639,7 +4183,7 @@
         <x:v>350</x:v>
       </x:c>
       <x:c r="Y7">
-        <x:v>2250</x:v>
+        <x:v>0.27607361963190186</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -3660,7 +4204,7 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="P8">
-        <x:v>15000</x:v>
+        <x:v>0.351123595505618</x:v>
       </x:c>
       <x:c r="Q8">
         <x:v>8900</x:v>
@@ -3669,7 +4213,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S8">
-        <x:v>5340</x:v>
+        <x:v>0.125</x:v>
       </x:c>
       <x:c r="T8">
         <x:v>16800</x:v>
@@ -3678,7 +4222,7 @@
         <x:v>190</x:v>
       </x:c>
       <x:c r="V8">
-        <x:v>10080</x:v>
+        <x:v>0.23595505617977527</x:v>
       </x:c>
       <x:c r="W8">
         <x:v>20500</x:v>
@@ -3687,7 +4231,7 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="Y8">
-        <x:v>12300</x:v>
+        <x:v>0.28792134831460675</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -3708,7 +4252,7 @@
         <x:v>105</x:v>
       </x:c>
       <x:c r="P9">
-        <x:v>6750</x:v>
+        <x:v>0.3729281767955801</x:v>
       </x:c>
       <x:c r="Q9">
         <x:v>4200</x:v>
@@ -3717,7 +4261,7 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="S9">
-        <x:v>2100</x:v>
+        <x:v>0.11602209944751381</x:v>
       </x:c>
       <x:c r="T9">
         <x:v>7500</x:v>
@@ -3726,7 +4270,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="V9">
-        <x:v>3750</x:v>
+        <x:v>0.20718232044198895</x:v>
       </x:c>
       <x:c r="W9">
         <x:v>11000</x:v>
@@ -3735,13 +4279,13 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="Y9">
-        <x:v>5500</x:v>
+        <x:v>0.30386740331491713</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="L10" t="inlineStr">
         <x:is>
-          <x:t>West</x:t>
+          <x:t>West Total</x:t>
         </x:is>
       </x:c>
       <x:c r="N10">
@@ -3751,7 +4295,7 @@
         <x:v>195.66666666666666</x:v>
       </x:c>
       <x:c r="P10">
-        <x:v>24650</x:v>
+        <x:v>0.35740176888502245</x:v>
       </x:c>
       <x:c r="Q10">
         <x:v>16300</x:v>
@@ -3760,7 +4304,7 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="S10">
-        <x:v>9040</x:v>
+        <x:v>0.131071480353777</x:v>
       </x:c>
       <x:c r="T10">
         <x:v>27100</x:v>
@@ -3769,7 +4313,7 @@
         <x:v>188.33333333333334</x:v>
       </x:c>
       <x:c r="V10">
-        <x:v>15230</x:v>
+        <x:v>0.22082064665796725</x:v>
       </x:c>
       <x:c r="W10">
         <x:v>36000</x:v>
@@ -3778,7 +4322,7 @@
         <x:v>168.66666666666666</x:v>
       </x:c>
       <x:c r="Y10">
-        <x:v>20050</x:v>
+        <x:v>0.2907061041032333</x:v>
       </x:c>
     </x:row>
     <x:row r="11"/>
@@ -3800,7 +4344,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="P12">
-        <x:v>1400</x:v>
+        <x:v>0.27184466019417475</x:v>
       </x:c>
       <x:c r="Q12">
         <x:v>2200</x:v>
@@ -3809,7 +4353,7 @@
         <x:v>190</x:v>
       </x:c>
       <x:c r="S12">
-        <x:v>1100</x:v>
+        <x:v>0.21359223300970873</x:v>
       </x:c>
       <x:c r="T12">
         <x:v>3500</x:v>
@@ -3818,7 +4362,7 @@
         <x:v>280</x:v>
       </x:c>
       <x:c r="V12">
-        <x:v>1750</x:v>
+        <x:v>0.33980582524271846</x:v>
       </x:c>
       <x:c r="W12">
         <x:v>1800</x:v>
@@ -3827,7 +4371,7 @@
         <x:v>240</x:v>
       </x:c>
       <x:c r="Y12">
-        <x:v>900</x:v>
+        <x:v>0.17475728155339806</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -3848,7 +4392,7 @@
         <x:v>165</x:v>
       </x:c>
       <x:c r="P13">
-        <x:v>8520</x:v>
+        <x:v>0.2272</x:v>
       </x:c>
       <x:c r="Q13">
         <x:v>7800</x:v>
@@ -3857,7 +4401,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="S13">
-        <x:v>4680</x:v>
+        <x:v>0.1248</x:v>
       </x:c>
       <x:c r="T13">
         <x:v>22000</x:v>
@@ -3866,7 +4410,7 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="V13">
-        <x:v>13200</x:v>
+        <x:v>0.352</x:v>
       </x:c>
       <x:c r="W13">
         <x:v>18500</x:v>
@@ -3875,7 +4419,7 @@
         <x:v>200</x:v>
       </x:c>
       <x:c r="Y13">
-        <x:v>11100</x:v>
+        <x:v>0.296</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -3896,7 +4440,7 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="P14">
-        <x:v>4400</x:v>
+        <x:v>0.3188405797101449</x:v>
       </x:c>
       <x:c r="Q14">
         <x:v>3100</x:v>
@@ -3905,7 +4449,7 @@
         <x:v>130</x:v>
       </x:c>
       <x:c r="S14">
-        <x:v>1550</x:v>
+        <x:v>0.11231884057971014</x:v>
       </x:c>
       <x:c r="T14">
         <x:v>6500</x:v>
@@ -3914,7 +4458,7 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="V14">
-        <x:v>3250</x:v>
+        <x:v>0.23550724637681159</x:v>
       </x:c>
       <x:c r="W14">
         <x:v>9200</x:v>
@@ -3923,13 +4467,13 @@
         <x:v>110</x:v>
       </x:c>
       <x:c r="Y14">
-        <x:v>4600</x:v>
+        <x:v>0.3333333333333333</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="L15" t="inlineStr">
         <x:is>
-          <x:t>South</x:t>
+          <x:t>South Total</x:t>
         </x:is>
       </x:c>
       <x:c r="N15">
@@ -3939,7 +4483,7 @@
         <x:v>157.66666666666666</x:v>
       </x:c>
       <x:c r="P15">
-        <x:v>14320</x:v>
+        <x:v>0.25367581930912314</x:v>
       </x:c>
       <x:c r="Q15">
         <x:v>13100</x:v>
@@ -3948,7 +4492,7 @@
         <x:v>122.66666666666667</x:v>
       </x:c>
       <x:c r="S15">
-        <x:v>7330</x:v>
+        <x:v>0.12984942426926482</x:v>
       </x:c>
       <x:c r="T15">
         <x:v>32000</x:v>
@@ -3957,7 +4501,7 @@
         <x:v>143.33333333333334</x:v>
       </x:c>
       <x:c r="V15">
-        <x:v>18200</x:v>
+        <x:v>0.3224092116917626</x:v>
       </x:c>
       <x:c r="W15">
         <x:v>29500</x:v>
@@ -3966,7 +4510,7 @@
         <x:v>183.33333333333334</x:v>
       </x:c>
       <x:c r="Y15">
-        <x:v>16600</x:v>
+        <x:v>0.2940655447298494</x:v>
       </x:c>
     </x:row>
     <x:row r="16"/>
@@ -3988,7 +4532,7 @@
         <x:v>220</x:v>
       </x:c>
       <x:c r="P17">
-        <x:v>1600</x:v>
+        <x:v>0.35555555555555557</x:v>
       </x:c>
       <x:c r="Q17">
         <x:v>1900</x:v>
@@ -3997,7 +4541,7 @@
         <x:v>160</x:v>
       </x:c>
       <x:c r="S17">
-        <x:v>950</x:v>
+        <x:v>0.2111111111111111</x:v>
       </x:c>
       <x:c r="T17">
         <x:v>1500</x:v>
@@ -4006,7 +4550,7 @@
         <x:v>180</x:v>
       </x:c>
       <x:c r="V17">
-        <x:v>750</x:v>
+        <x:v>0.16666666666666666</x:v>
       </x:c>
       <x:c r="W17">
         <x:v>2400</x:v>
@@ -4015,7 +4559,7 @@
         <x:v>200</x:v>
       </x:c>
       <x:c r="Y17">
-        <x:v>1200</x:v>
+        <x:v>0.26666666666666666</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -4036,7 +4580,7 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="P18">
-        <x:v>5700</x:v>
+        <x:v>0.1482059282371295</x:v>
       </x:c>
       <x:c r="Q18">
         <x:v>11200</x:v>
@@ -4045,7 +4589,7 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="S18">
-        <x:v>6720</x:v>
+        <x:v>0.1747269890795632</x:v>
       </x:c>
       <x:c r="T18">
         <x:v>22000</x:v>
@@ -4054,7 +4598,7 @@
         <x:v>46.5</x:v>
       </x:c>
       <x:c r="V18">
-        <x:v>13200</x:v>
+        <x:v>0.34321372854914195</x:v>
       </x:c>
       <x:c r="W18">
         <x:v>21400</x:v>
@@ -4063,7 +4607,7 @@
         <x:v>82.5</x:v>
       </x:c>
       <x:c r="Y18">
-        <x:v>12840</x:v>
+        <x:v>0.3338533541341654</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -4084,7 +4628,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="P19">
-        <x:v>3900</x:v>
+        <x:v>0.4020618556701031</x:v>
       </x:c>
       <x:c r="Q19">
         <x:v>1800</x:v>
@@ -4093,7 +4637,7 @@
         <x:v>110</x:v>
       </x:c>
       <x:c r="S19">
-        <x:v>900</x:v>
+        <x:v>0.09278350515463918</x:v>
       </x:c>
       <x:c r="T19">
         <x:v>5600</x:v>
@@ -4102,7 +4646,7 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="V19">
-        <x:v>2800</x:v>
+        <x:v>0.28865979381443296</x:v>
       </x:c>
       <x:c r="W19">
         <x:v>4200</x:v>
@@ -4111,13 +4655,13 @@
         <x:v>85</x:v>
       </x:c>
       <x:c r="Y19">
-        <x:v>2100</x:v>
+        <x:v>0.21649484536082475</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="L20" t="inlineStr">
         <x:is>
-          <x:t>North</x:t>
+          <x:t>North Total</x:t>
         </x:is>
       </x:c>
       <x:c r="N20">
@@ -4127,7 +4671,7 @@
         <x:v>125.66666666666667</x:v>
       </x:c>
       <x:c r="P20">
-        <x:v>11200</x:v>
+        <x:v>0.21268515001898974</x:v>
       </x:c>
       <x:c r="Q20">
         <x:v>14900</x:v>
@@ -4136,7 +4680,7 @@
         <x:v>140</x:v>
       </x:c>
       <x:c r="S20">
-        <x:v>8570</x:v>
+        <x:v>0.16274211925560197</x:v>
       </x:c>
       <x:c r="T20">
         <x:v>29100</x:v>
@@ -4145,7 +4689,7 @@
         <x:v>85.75</x:v>
       </x:c>
       <x:c r="V20">
-        <x:v>16750</x:v>
+        <x:v>0.31807823775161415</x:v>
       </x:c>
       <x:c r="W20">
         <x:v>28000</x:v>
@@ -4154,7 +4698,7 @@
         <x:v>112.5</x:v>
       </x:c>
       <x:c r="Y20">
-        <x:v>16140</x:v>
+        <x:v>0.30649449297379416</x:v>
       </x:c>
     </x:row>
     <x:row r="21"/>
@@ -4176,7 +4720,7 @@
         <x:v>250</x:v>
       </x:c>
       <x:c r="P22">
-        <x:v>800</x:v>
+        <x:v>0.2077922077922078</x:v>
       </x:c>
       <x:c r="Q22">
         <x:v>2800</x:v>
@@ -4185,7 +4729,7 @@
         <x:v>230</x:v>
       </x:c>
       <x:c r="S22">
-        <x:v>1400</x:v>
+        <x:v>0.36363636363636365</x:v>
       </x:c>
       <x:c r="T22">
         <x:v>2100</x:v>
@@ -4194,7 +4738,7 @@
         <x:v>170</x:v>
       </x:c>
       <x:c r="V22">
-        <x:v>1050</x:v>
+        <x:v>0.2727272727272727</x:v>
       </x:c>
       <x:c r="W22">
         <x:v>1200</x:v>
@@ -4203,7 +4747,7 @@
         <x:v>300</x:v>
       </x:c>
       <x:c r="Y22">
-        <x:v>600</x:v>
+        <x:v>0.15584415584415584</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -4224,7 +4768,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="P23">
-        <x:v>4920</x:v>
+        <x:v>0.17484008528784648</x:v>
       </x:c>
       <x:c r="Q23">
         <x:v>13800</x:v>
@@ -4233,7 +4777,7 @@
         <x:v>180</x:v>
       </x:c>
       <x:c r="S23">
-        <x:v>8280</x:v>
+        <x:v>0.2942430703624733</x:v>
       </x:c>
       <x:c r="T23">
         <x:v>19500</x:v>
@@ -4242,7 +4786,7 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="V23">
-        <x:v>11700</x:v>
+        <x:v>0.4157782515991471</x:v>
       </x:c>
       <x:c r="W23">
         <x:v>5400</x:v>
@@ -4251,7 +4795,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="Y23">
-        <x:v>3240</x:v>
+        <x:v>0.11513859275053305</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -4272,7 +4816,7 @@
         <x:v>105</x:v>
       </x:c>
       <x:c r="P24">
-        <x:v>1800</x:v>
+        <x:v>0.18848167539267016</x:v>
       </x:c>
       <x:c r="Q24">
         <x:v>5500</x:v>
@@ -4281,7 +4825,7 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="S24">
-        <x:v>2750</x:v>
+        <x:v>0.2879581151832461</x:v>
       </x:c>
       <x:c r="T24">
         <x:v>7200</x:v>
@@ -4290,7 +4834,7 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="V24">
-        <x:v>3600</x:v>
+        <x:v>0.3769633507853403</x:v>
       </x:c>
       <x:c r="W24">
         <x:v>2800</x:v>
@@ -4299,13 +4843,13 @@
         <x:v>140</x:v>
       </x:c>
       <x:c r="Y24">
-        <x:v>1400</x:v>
+        <x:v>0.14659685863874344</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="L25" t="inlineStr">
         <x:is>
-          <x:t>East</x:t>
+          <x:t>East Total</x:t>
         </x:is>
       </x:c>
       <x:c r="N25">
@@ -4315,7 +4859,7 @@
         <x:v>135.66666666666666</x:v>
       </x:c>
       <x:c r="P25">
-        <x:v>7520</x:v>
+        <x:v>0.18103033220991815</x:v>
       </x:c>
       <x:c r="Q25">
         <x:v>22100</x:v>
@@ -4324,7 +4868,7 @@
         <x:v>166</x:v>
       </x:c>
       <x:c r="S25">
-        <x:v>12430</x:v>
+        <x:v>0.2992296581608089</x:v>
       </x:c>
       <x:c r="T25">
         <x:v>28800</x:v>
@@ -4333,7 +4877,7 @@
         <x:v>98.33333333333333</x:v>
       </x:c>
       <x:c r="V25">
-        <x:v>16350</x:v>
+        <x:v>0.39359653346172363</x:v>
       </x:c>
       <x:c r="W25">
         <x:v>9400</x:v>
@@ -4342,7 +4886,7 @@
         <x:v>158.33333333333334</x:v>
       </x:c>
       <x:c r="Y25">
-        <x:v>5240</x:v>
+        <x:v>0.12614347616754934</x:v>
       </x:c>
     </x:row>
     <x:row r="26"/>
@@ -4359,7 +4903,7 @@
         <x:v>153.66666666666666</x:v>
       </x:c>
       <x:c r="P27">
-        <x:v>57690</x:v>
+        <x:v>0.26268099444495036</x:v>
       </x:c>
       <x:c r="Q27">
         <x:v>66400</x:v>
@@ -4368,7 +4912,7 @@
         <x:v>143.41666666666666</x:v>
       </x:c>
       <x:c r="S27">
-        <x:v>37370</x:v>
+        <x:v>0.1701575448501958</x:v>
       </x:c>
       <x:c r="T27">
         <x:v>117000</x:v>
@@ -4377,7 +4921,7 @@
         <x:v>125.61538461538461</x:v>
       </x:c>
       <x:c r="V27">
-        <x:v>66530</x:v>
+        <x:v>0.30293233767416444</x:v>
       </x:c>
       <x:c r="W27">
         <x:v>102900</x:v>
@@ -4386,7 +4930,7 @@
         <x:v>152.3846153846154</x:v>
       </x:c>
       <x:c r="Y27">
-        <x:v>58030</x:v>
+        <x:v>0.26422912303068935</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4451,7 +4995,7 @@
     <x:row r="5">
       <x:c r="E5" t="inlineStr">
         <x:is>
-          <x:t>华北</x:t>
+          <x:t>华北 Total</x:t>
         </x:is>
       </x:c>
       <x:c r="G5">
@@ -4496,7 +5040,7 @@
     <x:row r="9">
       <x:c r="E9" t="inlineStr">
         <x:is>
-          <x:t>华东</x:t>
+          <x:t>华东 Total</x:t>
         </x:is>
       </x:c>
       <x:c r="G9">
@@ -4541,7 +5085,7 @@
     <x:row r="13">
       <x:c r="E13" t="inlineStr">
         <x:is>
-          <x:t>华南</x:t>
+          <x:t>华南 Total</x:t>
         </x:is>
       </x:c>
       <x:c r="G13">
@@ -4586,7 +5130,7 @@
     <x:row r="17">
       <x:c r="E17" t="inlineStr">
         <x:is>
-          <x:t>西南</x:t>
+          <x:t>西南 Total</x:t>
         </x:is>
       </x:c>
       <x:c r="G17">
@@ -4601,6 +5145,1305 @@
       </x:c>
       <x:c r="G18">
         <x:v>118300</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetData>
+    <x:row r="2">
+      <x:c r="E2" t="inlineStr">
+        <x:is>
+          <x:t>Values</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="D3" t="inlineStr">
+        <x:is>
+          <x:t>Category</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E3" t="inlineStr">
+        <x:is>
+          <x:t>Avg of Sales</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F3" t="inlineStr">
+        <x:is>
+          <x:t>Min of Quantity</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G3" t="inlineStr">
+        <x:is>
+          <x:t>Product of Quantity</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H3" t="inlineStr">
+        <x:is>
+          <x:t>Countnums of Sales</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="D4" t="inlineStr">
+        <x:is>
+          <x:t>Clothing</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E4">
+        <x:v>6393.75</x:v>
+      </x:c>
+      <x:c r="F4">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="G4">
+        <x:v>5.556714093664954E+31</x:v>
+      </x:c>
+      <x:c r="H4">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="D5" t="inlineStr">
+        <x:is>
+          <x:t>Electronics</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E5">
+        <x:v>13594.444444444445</x:v>
+      </x:c>
+      <x:c r="F5">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="G5">
+        <x:v>1.485275349964097E+34</x:v>
+      </x:c>
+      <x:c r="H5">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="D6" t="inlineStr">
+        <x:is>
+          <x:t>Food</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E6">
+        <x:v>2706.25</x:v>
+      </x:c>
+      <x:c r="F6">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="G6">
+        <x:v>1.0155113197092866E+38</x:v>
+      </x:c>
+      <x:c r="H6">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="D7" t="inlineStr">
+        <x:is>
+          <x:t>Grand Total</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E7">
+        <x:v>7806</x:v>
+      </x:c>
+      <x:c r="F7">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="G7">
+        <x:v>8.381269276801474E+103</x:v>
+      </x:c>
+      <x:c r="H7">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="L1" t="inlineStr">
+        <x:is>
+          <x:t>Region</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M1" t="inlineStr">
+        <x:is>
+          <x:t>Sum of Sales</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="L2" t="inlineStr">
+        <x:is>
+          <x:t>North</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M2">
+        <x:v>92500</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="L3" t="inlineStr">
+        <x:is>
+          <x:t>Grand Total</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M3">
+        <x:v>92500</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="M1" t="inlineStr">
+        <x:is>
+          <x:t>Quarter</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="M2" t="inlineStr">
+        <x:is>
+          <x:t>Q1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P2" t="inlineStr">
+        <x:is>
+          <x:t>Q2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="S2" t="inlineStr">
+        <x:is>
+          <x:t>Q3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="V2" t="inlineStr">
+        <x:is>
+          <x:t>Q4</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="L3" t="inlineStr">
+        <x:is>
+          <x:t>Region</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M3" t="inlineStr">
+        <x:is>
+          <x:t>Var of Sales</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N3" t="inlineStr">
+        <x:is>
+          <x:t>Varp of Sales</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O3" t="inlineStr">
+        <x:is>
+          <x:t>Sum of Sales</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P3" t="inlineStr">
+        <x:is>
+          <x:t>Var of Sales</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Q3" t="inlineStr">
+        <x:is>
+          <x:t>Varp of Sales</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="R3" t="inlineStr">
+        <x:is>
+          <x:t>Sum of Sales</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="S3" t="inlineStr">
+        <x:is>
+          <x:t>Var of Sales</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="T3" t="inlineStr">
+        <x:is>
+          <x:t>Varp of Sales</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="U3" t="inlineStr">
+        <x:is>
+          <x:t>Sum of Sales</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="V3" t="inlineStr">
+        <x:is>
+          <x:t>Var of Sales</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="W3" t="inlineStr">
+        <x:is>
+          <x:t>Varp of Sales</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="X3" t="inlineStr">
+        <x:is>
+          <x:t>Sum of Sales</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Y3" t="inlineStr">
+        <x:is>
+          <x:t>Total Var of Sales</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Z3" t="inlineStr">
+        <x:is>
+          <x:t>Total Varp of Sales</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="AA3" t="inlineStr">
+        <x:is>
+          <x:t>Total Sum of Sales</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="L4" t="inlineStr">
+        <x:is>
+          <x:t>East</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M4">
+        <x:v>4493333.333333333</x:v>
+      </x:c>
+      <x:c r="N4">
+        <x:v>2995555.5555555555</x:v>
+      </x:c>
+      <x:c r="O4">
+        <x:v>9400</x:v>
+      </x:c>
+      <x:c r="P4">
+        <x:v>80010000</x:v>
+      </x:c>
+      <x:c r="Q4">
+        <x:v>53340000</x:v>
+      </x:c>
+      <x:c r="R4">
+        <x:v>28800</x:v>
+      </x:c>
+      <x:c r="S4">
+        <x:v>32863333.333333336</x:v>
+      </x:c>
+      <x:c r="T4">
+        <x:v>21908888.88888889</x:v>
+      </x:c>
+      <x:c r="U4">
+        <x:v>22100</x:v>
+      </x:c>
+      <x:c r="V4">
+        <x:v>11453333.333333334</x:v>
+      </x:c>
+      <x:c r="W4">
+        <x:v>7635555.555555556</x:v>
+      </x:c>
+      <x:c r="X4">
+        <x:v>13400</x:v>
+      </x:c>
+      <x:c r="Y4">
+        <x:v>30326287.878787875</x:v>
+      </x:c>
+      <x:c r="Z4">
+        <x:v>27799097.22222222</x:v>
+      </x:c>
+      <x:c r="AA4">
+        <x:v>73700</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="L5" t="inlineStr">
+        <x:is>
+          <x:t>North</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M5">
+        <x:v>20953333.333333332</x:v>
+      </x:c>
+      <x:c r="N5">
+        <x:v>15715000</x:v>
+      </x:c>
+      <x:c r="O5">
+        <x:v>28000</x:v>
+      </x:c>
+      <x:c r="P5">
+        <x:v>36662500</x:v>
+      </x:c>
+      <x:c r="Q5">
+        <x:v>27496875</x:v>
+      </x:c>
+      <x:c r="R5">
+        <x:v>29100</x:v>
+      </x:c>
+      <x:c r="S5">
+        <x:v>29143333.333333336</x:v>
+      </x:c>
+      <x:c r="T5">
+        <x:v>19428888.88888889</x:v>
+      </x:c>
+      <x:c r="U5">
+        <x:v>14900</x:v>
+      </x:c>
+      <x:c r="V5">
+        <x:v>10623333.333333332</x:v>
+      </x:c>
+      <x:c r="W5">
+        <x:v>7082222.222222221</x:v>
+      </x:c>
+      <x:c r="X5">
+        <x:v>20500</x:v>
+      </x:c>
+      <x:c r="Y5">
+        <x:v>20231483.516483516</x:v>
+      </x:c>
+      <x:c r="Z5">
+        <x:v>18786377.551020406</x:v>
+      </x:c>
+      <x:c r="AA5">
+        <x:v>92500</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="L6" t="inlineStr">
+        <x:is>
+          <x:t>South</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M6">
+        <x:v>70023333.33333333</x:v>
+      </x:c>
+      <x:c r="N6">
+        <x:v>46682222.22222222</x:v>
+      </x:c>
+      <x:c r="O6">
+        <x:v>29500</x:v>
+      </x:c>
+      <x:c r="P6">
+        <x:v>98583333.33333334</x:v>
+      </x:c>
+      <x:c r="Q6">
+        <x:v>65722222.22222223</x:v>
+      </x:c>
+      <x:c r="R6">
+        <x:v>32000</x:v>
+      </x:c>
+      <x:c r="S6">
+        <x:v>9043333.333333334</x:v>
+      </x:c>
+      <x:c r="T6">
+        <x:v>6028888.888888889</x:v>
+      </x:c>
+      <x:c r="U6">
+        <x:v>13100</x:v>
+      </x:c>
+      <x:c r="V6">
+        <x:v>32520000</x:v>
+      </x:c>
+      <x:c r="W6">
+        <x:v>21680000</x:v>
+      </x:c>
+      <x:c r="X6">
+        <x:v>25800</x:v>
+      </x:c>
+      <x:c r="Y6">
+        <x:v>44620606.06060606</x:v>
+      </x:c>
+      <x:c r="Z6">
+        <x:v>40902222.222222224</x:v>
+      </x:c>
+      <x:c r="AA6">
+        <x:v>100400</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="L7" t="inlineStr">
+        <x:is>
+          <x:t>West</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M7">
+        <x:v>64750000</x:v>
+      </x:c>
+      <x:c r="N7">
+        <x:v>43166666.666666664</x:v>
+      </x:c>
+      <x:c r="O7">
+        <x:v>36000</x:v>
+      </x:c>
+      <x:c r="P7">
+        <x:v>50763333.333333336</x:v>
+      </x:c>
+      <x:c r="Q7">
+        <x:v>33842222.222222224</x:v>
+      </x:c>
+      <x:c r="R7">
+        <x:v>27100</x:v>
+      </x:c>
+      <x:c r="S7">
+        <x:v>9263333.333333332</x:v>
+      </x:c>
+      <x:c r="T7">
+        <x:v>6175555.555555555</x:v>
+      </x:c>
+      <x:c r="U7">
+        <x:v>16300</x:v>
+      </x:c>
+      <x:c r="V7">
+        <x:v>93363333.33333334</x:v>
+      </x:c>
+      <x:c r="W7">
+        <x:v>62242222.22222223</x:v>
+      </x:c>
+      <x:c r="X7">
+        <x:v>44300</x:v>
+      </x:c>
+      <x:c r="Y7">
+        <x:v>52788106.060606055</x:v>
+      </x:c>
+      <x:c r="Z7">
+        <x:v>48389097.22222222</x:v>
+      </x:c>
+      <x:c r="AA7">
+        <x:v>123700</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="L8" t="inlineStr">
+        <x:is>
+          <x:t>Grand Total</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M8">
+        <x:v>39536410.25641026</x:v>
+      </x:c>
+      <x:c r="N8">
+        <x:v>36495147.92899409</x:v>
+      </x:c>
+      <x:c r="O8">
+        <x:v>102900</x:v>
+      </x:c>
+      <x:c r="P8">
+        <x:v>49168333.333333336</x:v>
+      </x:c>
+      <x:c r="Q8">
+        <x:v>45386153.84615385</x:v>
+      </x:c>
+      <x:c r="R8">
+        <x:v>117000</x:v>
+      </x:c>
+      <x:c r="S8">
+        <x:v>15980606.060606062</x:v>
+      </x:c>
+      <x:c r="T8">
+        <x:v>14648888.88888889</x:v>
+      </x:c>
+      <x:c r="U8">
+        <x:v>66400</x:v>
+      </x:c>
+      <x:c r="V8">
+        <x:v>42778787.87878788</x:v>
+      </x:c>
+      <x:c r="W8">
+        <x:v>39213888.88888889</x:v>
+      </x:c>
+      <x:c r="X8">
+        <x:v>104000</x:v>
+      </x:c>
+      <x:c r="Y8">
+        <x:v>36742208.1632653</x:v>
+      </x:c>
+      <x:c r="Z8">
+        <x:v>36007364</x:v>
+      </x:c>
+      <x:c r="AA8">
+        <x:v>390300</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="E1" t="inlineStr">
+        <x:is>
+          <x:t>Sum of 销售额</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F1" t="inlineStr">
+        <x:is>
+          <x:t>品类</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="E2" t="inlineStr">
+        <x:is>
+          <x:t>地区</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F2" t="inlineStr">
+        <x:is>
+          <x:t>食品</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G2" t="inlineStr">
+        <x:is>
+          <x:t>服装</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H2" t="inlineStr">
+        <x:is>
+          <x:t>电子产品</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="E3" t="inlineStr">
+        <x:is>
+          <x:t>西南</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F3">
+        <x:v>2900</x:v>
+      </x:c>
+      <x:c r="G3">
+        <x:v>6500</x:v>
+      </x:c>
+      <x:c r="H3">
+        <x:v>11000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="E4" t="inlineStr">
+        <x:is>
+          <x:t>华南</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F4">
+        <x:v>5800</x:v>
+      </x:c>
+      <x:c r="G4">
+        <x:v>12000</x:v>
+      </x:c>
+      <x:c r="H4">
+        <x:v>22000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="E5" t="inlineStr">
+        <x:is>
+          <x:t>华东</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F5">
+        <x:v>4200</x:v>
+      </x:c>
+      <x:c r="G5">
+        <x:v>9500</x:v>
+      </x:c>
+      <x:c r="H5">
+        <x:v>18000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="E6" t="inlineStr">
+        <x:is>
+          <x:t>华北</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F6">
+        <x:v>3600</x:v>
+      </x:c>
+      <x:c r="G6">
+        <x:v>7800</x:v>
+      </x:c>
+      <x:c r="H6">
+        <x:v>15000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="E7" t="inlineStr">
+        <x:is>
+          <x:t>Grand Total</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F7">
+        <x:v>16500</x:v>
+      </x:c>
+      <x:c r="G7">
+        <x:v>35800</x:v>
+      </x:c>
+      <x:c r="H7">
+        <x:v>66000</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="L1" t="inlineStr">
+        <x:is>
+          <x:t>Sum of Sales</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N1" t="inlineStr">
+        <x:is>
+          <x:t>Quarter</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="L2" t="inlineStr">
+        <x:is>
+          <x:t>Region</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M2" t="inlineStr">
+        <x:is>
+          <x:t>Category</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N2" t="inlineStr">
+        <x:is>
+          <x:t>Q1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O2" t="inlineStr">
+        <x:is>
+          <x:t>Q2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P2" t="inlineStr">
+        <x:is>
+          <x:t>Q3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="Q2" t="inlineStr">
+        <x:is>
+          <x:t>Q4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="R2" t="inlineStr">
+        <x:is>
+          <x:t>Grand Total</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="L3" t="inlineStr">
+        <x:is>
+          <x:t>East</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M3" t="inlineStr">
+        <x:is>
+          <x:t>Clothing</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N3">
+        <x:v>2800</x:v>
+      </x:c>
+      <x:c r="O3">
+        <x:v>7200</x:v>
+      </x:c>
+      <x:c r="P3">
+        <x:v>5500</x:v>
+      </x:c>
+      <x:c r="Q3">
+        <x:v>3600</x:v>
+      </x:c>
+      <x:c r="R3">
+        <x:v>19100</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="M4" t="inlineStr">
+        <x:is>
+          <x:t>Electronics</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N4">
+        <x:v>5400</x:v>
+      </x:c>
+      <x:c r="O4">
+        <x:v>19500</x:v>
+      </x:c>
+      <x:c r="P4">
+        <x:v>13800</x:v>
+      </x:c>
+      <x:c r="Q4">
+        <x:v>8200</x:v>
+      </x:c>
+      <x:c r="R4">
+        <x:v>46900</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="M5" t="inlineStr">
+        <x:is>
+          <x:t>Food</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N5">
+        <x:v>1200</x:v>
+      </x:c>
+      <x:c r="O5">
+        <x:v>2100</x:v>
+      </x:c>
+      <x:c r="P5">
+        <x:v>2800</x:v>
+      </x:c>
+      <x:c r="Q5">
+        <x:v>1600</x:v>
+      </x:c>
+      <x:c r="R5">
+        <x:v>7700</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="L6" t="inlineStr">
+        <x:is>
+          <x:t>East Total</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N6">
+        <x:v>9400</x:v>
+      </x:c>
+      <x:c r="O6">
+        <x:v>28800</x:v>
+      </x:c>
+      <x:c r="P6">
+        <x:v>22100</x:v>
+      </x:c>
+      <x:c r="Q6">
+        <x:v>13400</x:v>
+      </x:c>
+      <x:c r="R6">
+        <x:v>73700</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="L7" t="inlineStr">
+        <x:is>
+          <x:t>North</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M7" t="inlineStr">
+        <x:is>
+          <x:t>Clothing</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N7">
+        <x:v>4200</x:v>
+      </x:c>
+      <x:c r="O7">
+        <x:v>5600</x:v>
+      </x:c>
+      <x:c r="P7">
+        <x:v>1800</x:v>
+      </x:c>
+      <x:c r="Q7">
+        <x:v>7800</x:v>
+      </x:c>
+      <x:c r="R7">
+        <x:v>19400</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="M8" t="inlineStr">
+        <x:is>
+          <x:t>Electronics</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N8">
+        <x:v>21400</x:v>
+      </x:c>
+      <x:c r="O8">
+        <x:v>22000</x:v>
+      </x:c>
+      <x:c r="P8">
+        <x:v>11200</x:v>
+      </x:c>
+      <x:c r="Q8">
+        <x:v>9500</x:v>
+      </x:c>
+      <x:c r="R8">
+        <x:v>64100</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="M9" t="inlineStr">
+        <x:is>
+          <x:t>Food</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N9">
+        <x:v>2400</x:v>
+      </x:c>
+      <x:c r="O9">
+        <x:v>1500</x:v>
+      </x:c>
+      <x:c r="P9">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="Q9">
+        <x:v>3200</x:v>
+      </x:c>
+      <x:c r="R9">
+        <x:v>9000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="L10" t="inlineStr">
+        <x:is>
+          <x:t>North Total</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N10">
+        <x:v>28000</x:v>
+      </x:c>
+      <x:c r="O10">
+        <x:v>29100</x:v>
+      </x:c>
+      <x:c r="P10">
+        <x:v>14900</x:v>
+      </x:c>
+      <x:c r="Q10">
+        <x:v>20500</x:v>
+      </x:c>
+      <x:c r="R10">
+        <x:v>92500</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="L11" t="inlineStr">
+        <x:is>
+          <x:t>South</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M11" t="inlineStr">
+        <x:is>
+          <x:t>Clothing</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N11">
+        <x:v>9200</x:v>
+      </x:c>
+      <x:c r="O11">
+        <x:v>6500</x:v>
+      </x:c>
+      <x:c r="P11">
+        <x:v>3100</x:v>
+      </x:c>
+      <x:c r="Q11">
+        <x:v>8800</x:v>
+      </x:c>
+      <x:c r="R11">
+        <x:v>27600</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="M12" t="inlineStr">
+        <x:is>
+          <x:t>Electronics</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N12">
+        <x:v>18500</x:v>
+      </x:c>
+      <x:c r="O12">
+        <x:v>22000</x:v>
+      </x:c>
+      <x:c r="P12">
+        <x:v>7800</x:v>
+      </x:c>
+      <x:c r="Q12">
+        <x:v>14200</x:v>
+      </x:c>
+      <x:c r="R12">
+        <x:v>62500</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="M13" t="inlineStr">
+        <x:is>
+          <x:t>Food</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N13">
+        <x:v>1800</x:v>
+      </x:c>
+      <x:c r="O13">
+        <x:v>3500</x:v>
+      </x:c>
+      <x:c r="P13">
+        <x:v>2200</x:v>
+      </x:c>
+      <x:c r="Q13">
+        <x:v>2800</x:v>
+      </x:c>
+      <x:c r="R13">
+        <x:v>10300</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="L14" t="inlineStr">
+        <x:is>
+          <x:t>South Total</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N14">
+        <x:v>29500</x:v>
+      </x:c>
+      <x:c r="O14">
+        <x:v>32000</x:v>
+      </x:c>
+      <x:c r="P14">
+        <x:v>13100</x:v>
+      </x:c>
+      <x:c r="Q14">
+        <x:v>25800</x:v>
+      </x:c>
+      <x:c r="R14">
+        <x:v>100400</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="L15" t="inlineStr">
+        <x:is>
+          <x:t>West</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M15" t="inlineStr">
+        <x:is>
+          <x:t>Clothing</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N15">
+        <x:v>11000</x:v>
+      </x:c>
+      <x:c r="O15">
+        <x:v>7500</x:v>
+      </x:c>
+      <x:c r="P15">
+        <x:v>4200</x:v>
+      </x:c>
+      <x:c r="Q15">
+        <x:v>13500</x:v>
+      </x:c>
+      <x:c r="R15">
+        <x:v>36200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="M16" t="inlineStr">
+        <x:is>
+          <x:t>Electronics</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N16">
+        <x:v>20500</x:v>
+      </x:c>
+      <x:c r="O16">
+        <x:v>16800</x:v>
+      </x:c>
+      <x:c r="P16">
+        <x:v>8900</x:v>
+      </x:c>
+      <x:c r="Q16">
+        <x:v>25000</x:v>
+      </x:c>
+      <x:c r="R16">
+        <x:v>71200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="M17" t="inlineStr">
+        <x:is>
+          <x:t>Food</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N17">
+        <x:v>4500</x:v>
+      </x:c>
+      <x:c r="O17">
+        <x:v>2800</x:v>
+      </x:c>
+      <x:c r="P17">
+        <x:v>3200</x:v>
+      </x:c>
+      <x:c r="Q17">
+        <x:v>5800</x:v>
+      </x:c>
+      <x:c r="R17">
+        <x:v>16300</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="L18" t="inlineStr">
+        <x:is>
+          <x:t>West Total</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N18">
+        <x:v>36000</x:v>
+      </x:c>
+      <x:c r="O18">
+        <x:v>27100</x:v>
+      </x:c>
+      <x:c r="P18">
+        <x:v>16300</x:v>
+      </x:c>
+      <x:c r="Q18">
+        <x:v>44300</x:v>
+      </x:c>
+      <x:c r="R18">
+        <x:v>123700</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="L19" t="inlineStr">
+        <x:is>
+          <x:t>Grand Total</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N19">
+        <x:v>102900</x:v>
+      </x:c>
+      <x:c r="O19">
+        <x:v>117000</x:v>
+      </x:c>
+      <x:c r="P19">
+        <x:v>66400</x:v>
+      </x:c>
+      <x:c r="Q19">
+        <x:v>104000</x:v>
+      </x:c>
+      <x:c r="R19">
+        <x:v>390300</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="L1" t="inlineStr">
+        <x:is>
+          <x:t>Region</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M1" t="inlineStr">
+        <x:is>
+          <x:t>Category</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N1" t="inlineStr">
+        <x:is>
+          <x:t>Sum of Sales</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="L2" t="inlineStr">
+        <x:is>
+          <x:t>East</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N2">
+        <x:v>73700</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="M3" t="inlineStr">
+        <x:is>
+          <x:t>Clothing</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N3">
+        <x:v>19100</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="M4" t="inlineStr">
+        <x:is>
+          <x:t>Electronics</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N4">
+        <x:v>46900</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="M5" t="inlineStr">
+        <x:is>
+          <x:t>Food</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N5">
+        <x:v>7700</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="L6" t="inlineStr">
+        <x:is>
+          <x:t>North</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N6">
+        <x:v>92500</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="M7" t="inlineStr">
+        <x:is>
+          <x:t>Clothing</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N7">
+        <x:v>19400</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="M8" t="inlineStr">
+        <x:is>
+          <x:t>Electronics</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N8">
+        <x:v>64100</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="M9" t="inlineStr">
+        <x:is>
+          <x:t>Food</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N9">
+        <x:v>9000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="L10" t="inlineStr">
+        <x:is>
+          <x:t>South</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N10">
+        <x:v>100400</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="M11" t="inlineStr">
+        <x:is>
+          <x:t>Clothing</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N11">
+        <x:v>27600</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="M12" t="inlineStr">
+        <x:is>
+          <x:t>Electronics</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N12">
+        <x:v>62500</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="M13" t="inlineStr">
+        <x:is>
+          <x:t>Food</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N13">
+        <x:v>10300</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="L14" t="inlineStr">
+        <x:is>
+          <x:t>West</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N14">
+        <x:v>123700</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="M15" t="inlineStr">
+        <x:is>
+          <x:t>Clothing</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N15">
+        <x:v>36200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="M16" t="inlineStr">
+        <x:is>
+          <x:t>Electronics</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N16">
+        <x:v>71200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="M17" t="inlineStr">
+        <x:is>
+          <x:t>Food</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N17">
+        <x:v>16300</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="L18" t="inlineStr">
+        <x:is>
+          <x:t>Grand Total</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="N18">
+        <x:v>390300</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4812,21 +6655,6 @@
           <x:t>Q1</x:t>
         </x:is>
       </x:c>
-      <x:c r="Z5" t="inlineStr">
-        <x:is>
-          <x:t>Total Sum of Sales</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="AA5" t="inlineStr">
-        <x:is>
-          <x:t>Total Sum of Quantity</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="AB5" t="inlineStr">
-        <x:is>
-          <x:t>Total Sum of Cost</x:t>
-        </x:is>
-      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="L6" t="inlineStr">
@@ -4899,6 +6727,21 @@
           <x:t>Sum of Cost</x:t>
         </x:is>
       </x:c>
+      <x:c r="Z6" t="inlineStr">
+        <x:is>
+          <x:t>Total Sum of Sales</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="AA6" t="inlineStr">
+        <x:is>
+          <x:t>Total Sum of Quantity</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="AB6" t="inlineStr">
+        <x:is>
+          <x:t>Total Sum of Cost</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="L7" t="inlineStr">
@@ -4918,7 +6761,7 @@
         <x:v>400</x:v>
       </x:c>
       <x:c r="P7">
-        <x:v>2900</x:v>
+        <x:v>0.3558282208588957</x:v>
       </x:c>
       <x:c r="Q7">
         <x:v>3200</x:v>
@@ -4927,7 +6770,7 @@
         <x:v>260</x:v>
       </x:c>
       <x:c r="S7">
-        <x:v>1600</x:v>
+        <x:v>0.19631901840490798</x:v>
       </x:c>
       <x:c r="T7">
         <x:v>2800</x:v>
@@ -4936,7 +6779,7 @@
         <x:v>280</x:v>
       </x:c>
       <x:c r="V7">
-        <x:v>1400</x:v>
+        <x:v>0.17177914110429449</x:v>
       </x:c>
       <x:c r="W7">
         <x:v>4500</x:v>
@@ -4945,7 +6788,7 @@
         <x:v>350</x:v>
       </x:c>
       <x:c r="Y7">
-        <x:v>2250</x:v>
+        <x:v>0.27607361963190186</x:v>
       </x:c>
       <x:c r="Z7">
         <x:v>16300</x:v>
@@ -4954,7 +6797,7 @@
         <x:v>1290</x:v>
       </x:c>
       <x:c r="AB7">
-        <x:v>8150</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -4975,7 +6818,7 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="P8">
-        <x:v>15000</x:v>
+        <x:v>0.351123595505618</x:v>
       </x:c>
       <x:c r="Q8">
         <x:v>8900</x:v>
@@ -4984,7 +6827,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="S8">
-        <x:v>5340</x:v>
+        <x:v>0.125</x:v>
       </x:c>
       <x:c r="T8">
         <x:v>16800</x:v>
@@ -4993,7 +6836,7 @@
         <x:v>190</x:v>
       </x:c>
       <x:c r="V8">
-        <x:v>10080</x:v>
+        <x:v>0.23595505617977527</x:v>
       </x:c>
       <x:c r="W8">
         <x:v>20500</x:v>
@@ -5002,7 +6845,7 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="Y8">
-        <x:v>12300</x:v>
+        <x:v>0.28792134831460675</x:v>
       </x:c>
       <x:c r="Z8">
         <x:v>71200</x:v>
@@ -5011,7 +6854,7 @@
         <x:v>395</x:v>
       </x:c>
       <x:c r="AB8">
-        <x:v>42720</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -5032,7 +6875,7 @@
         <x:v>105</x:v>
       </x:c>
       <x:c r="P9">
-        <x:v>6750</x:v>
+        <x:v>0.3729281767955801</x:v>
       </x:c>
       <x:c r="Q9">
         <x:v>4200</x:v>
@@ -5041,7 +6884,7 @@
         <x:v>120</x:v>
       </x:c>
       <x:c r="S9">
-        <x:v>2100</x:v>
+        <x:v>0.11602209944751381</x:v>
       </x:c>
       <x:c r="T9">
         <x:v>7500</x:v>
@@ -5050,7 +6893,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="V9">
-        <x:v>3750</x:v>
+        <x:v>0.20718232044198895</x:v>
       </x:c>
       <x:c r="W9">
         <x:v>11000</x:v>
@@ -5059,7 +6902,7 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="Y9">
-        <x:v>5500</x:v>
+        <x:v>0.30386740331491713</x:v>
       </x:c>
       <x:c r="Z9">
         <x:v>36200</x:v>
@@ -5068,13 +6911,13 @@
         <x:v>408</x:v>
       </x:c>
       <x:c r="AB9">
-        <x:v>18100</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="L10" t="inlineStr">
         <x:is>
-          <x:t>West</x:t>
+          <x:t>West Total</x:t>
         </x:is>
       </x:c>
       <x:c r="N10">
@@ -5084,7 +6927,7 @@
         <x:v>587</x:v>
       </x:c>
       <x:c r="P10">
-        <x:v>24650</x:v>
+        <x:v>0.35740176888502245</x:v>
       </x:c>
       <x:c r="Q10">
         <x:v>16300</x:v>
@@ -5093,7 +6936,7 @@
         <x:v>435</x:v>
       </x:c>
       <x:c r="S10">
-        <x:v>9040</x:v>
+        <x:v>0.131071480353777</x:v>
       </x:c>
       <x:c r="T10">
         <x:v>27100</x:v>
@@ -5102,7 +6945,7 @@
         <x:v>565</x:v>
       </x:c>
       <x:c r="V10">
-        <x:v>15230</x:v>
+        <x:v>0.22082064665796725</x:v>
       </x:c>
       <x:c r="W10">
         <x:v>36000</x:v>
@@ -5111,7 +6954,7 @@
         <x:v>506</x:v>
       </x:c>
       <x:c r="Y10">
-        <x:v>20050</x:v>
+        <x:v>0.2907061041032333</x:v>
       </x:c>
       <x:c r="Z10">
         <x:v>123700</x:v>
@@ -5120,7 +6963,7 @@
         <x:v>2093</x:v>
       </x:c>
       <x:c r="AB10">
-        <x:v>68970</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -5141,7 +6984,7 @@
         <x:v>210</x:v>
       </x:c>
       <x:c r="P11">
-        <x:v>1400</x:v>
+        <x:v>0.27184466019417475</x:v>
       </x:c>
       <x:c r="Q11">
         <x:v>2200</x:v>
@@ -5150,7 +6993,7 @@
         <x:v>190</x:v>
       </x:c>
       <x:c r="S11">
-        <x:v>1100</x:v>
+        <x:v>0.21359223300970873</x:v>
       </x:c>
       <x:c r="T11">
         <x:v>3500</x:v>
@@ -5159,7 +7002,7 @@
         <x:v>280</x:v>
       </x:c>
       <x:c r="V11">
-        <x:v>1750</x:v>
+        <x:v>0.33980582524271846</x:v>
       </x:c>
       <x:c r="W11">
         <x:v>1800</x:v>
@@ -5168,7 +7011,7 @@
         <x:v>240</x:v>
       </x:c>
       <x:c r="Y11">
-        <x:v>900</x:v>
+        <x:v>0.17475728155339806</x:v>
       </x:c>
       <x:c r="Z11">
         <x:v>10300</x:v>
@@ -5177,7 +7020,7 @@
         <x:v>920</x:v>
       </x:c>
       <x:c r="AB11">
-        <x:v>5150</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -5198,7 +7041,7 @@
         <x:v>165</x:v>
       </x:c>
       <x:c r="P12">
-        <x:v>8520</x:v>
+        <x:v>0.2272</x:v>
       </x:c>
       <x:c r="Q12">
         <x:v>7800</x:v>
@@ -5207,7 +7050,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="S12">
-        <x:v>4680</x:v>
+        <x:v>0.1248</x:v>
       </x:c>
       <x:c r="T12">
         <x:v>22000</x:v>
@@ -5216,7 +7059,7 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="V12">
-        <x:v>13200</x:v>
+        <x:v>0.352</x:v>
       </x:c>
       <x:c r="W12">
         <x:v>18500</x:v>
@@ -5225,7 +7068,7 @@
         <x:v>200</x:v>
       </x:c>
       <x:c r="Y12">
-        <x:v>11100</x:v>
+        <x:v>0.296</x:v>
       </x:c>
       <x:c r="Z12">
         <x:v>62500</x:v>
@@ -5234,7 +7077,7 @@
         <x:v>485</x:v>
       </x:c>
       <x:c r="AB12">
-        <x:v>37500</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -5255,7 +7098,7 @@
         <x:v>98</x:v>
       </x:c>
       <x:c r="P13">
-        <x:v>4400</x:v>
+        <x:v>0.3188405797101449</x:v>
       </x:c>
       <x:c r="Q13">
         <x:v>3100</x:v>
@@ -5264,7 +7107,7 @@
         <x:v>130</x:v>
       </x:c>
       <x:c r="S13">
-        <x:v>1550</x:v>
+        <x:v>0.11231884057971014</x:v>
       </x:c>
       <x:c r="T13">
         <x:v>6500</x:v>
@@ -5273,7 +7116,7 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="V13">
-        <x:v>3250</x:v>
+        <x:v>0.23550724637681159</x:v>
       </x:c>
       <x:c r="W13">
         <x:v>9200</x:v>
@@ -5282,7 +7125,7 @@
         <x:v>110</x:v>
       </x:c>
       <x:c r="Y13">
-        <x:v>4600</x:v>
+        <x:v>0.3333333333333333</x:v>
       </x:c>
       <x:c r="Z13">
         <x:v>27600</x:v>
@@ -5291,13 +7134,13 @@
         <x:v>416</x:v>
       </x:c>
       <x:c r="AB13">
-        <x:v>13800</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="L14" t="inlineStr">
         <x:is>
-          <x:t>South</x:t>
+          <x:t>South Total</x:t>
         </x:is>
       </x:c>
       <x:c r="N14">
@@ -5307,7 +7150,7 @@
         <x:v>473</x:v>
       </x:c>
       <x:c r="P14">
-        <x:v>14320</x:v>
+        <x:v>0.25367581930912314</x:v>
       </x:c>
       <x:c r="Q14">
         <x:v>13100</x:v>
@@ -5316,7 +7159,7 @@
         <x:v>368</x:v>
       </x:c>
       <x:c r="S14">
-        <x:v>7330</x:v>
+        <x:v>0.12984942426926482</x:v>
       </x:c>
       <x:c r="T14">
         <x:v>32000</x:v>
@@ -5325,7 +7168,7 @@
         <x:v>430</x:v>
       </x:c>
       <x:c r="V14">
-        <x:v>18200</x:v>
+        <x:v>0.3224092116917626</x:v>
       </x:c>
       <x:c r="W14">
         <x:v>29500</x:v>
@@ -5334,7 +7177,7 @@
         <x:v>550</x:v>
       </x:c>
       <x:c r="Y14">
-        <x:v>16600</x:v>
+        <x:v>0.2940655447298494</x:v>
       </x:c>
       <x:c r="Z14">
         <x:v>100400</x:v>
@@ -5343,7 +7186,7 @@
         <x:v>1821</x:v>
       </x:c>
       <x:c r="AB14">
-        <x:v>56450</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -5364,7 +7207,7 @@
         <x:v>220</x:v>
       </x:c>
       <x:c r="P15">
-        <x:v>1600</x:v>
+        <x:v>0.35555555555555557</x:v>
       </x:c>
       <x:c r="Q15">
         <x:v>1900</x:v>
@@ -5373,7 +7216,7 @@
         <x:v>160</x:v>
       </x:c>
       <x:c r="S15">
-        <x:v>950</x:v>
+        <x:v>0.2111111111111111</x:v>
       </x:c>
       <x:c r="T15">
         <x:v>1500</x:v>
@@ -5382,7 +7225,7 @@
         <x:v>180</x:v>
       </x:c>
       <x:c r="V15">
-        <x:v>750</x:v>
+        <x:v>0.16666666666666666</x:v>
       </x:c>
       <x:c r="W15">
         <x:v>2400</x:v>
@@ -5391,7 +7234,7 @@
         <x:v>200</x:v>
       </x:c>
       <x:c r="Y15">
-        <x:v>1200</x:v>
+        <x:v>0.26666666666666666</x:v>
       </x:c>
       <x:c r="Z15">
         <x:v>9000</x:v>
@@ -5400,7 +7243,7 @@
         <x:v>760</x:v>
       </x:c>
       <x:c r="AB15">
-        <x:v>4500</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -5421,7 +7264,7 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="P16">
-        <x:v>5700</x:v>
+        <x:v>0.1482059282371295</x:v>
       </x:c>
       <x:c r="Q16">
         <x:v>11200</x:v>
@@ -5430,7 +7273,7 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="S16">
-        <x:v>6720</x:v>
+        <x:v>0.1747269890795632</x:v>
       </x:c>
       <x:c r="T16">
         <x:v>22000</x:v>
@@ -5439,7 +7282,7 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="V16">
-        <x:v>13200</x:v>
+        <x:v>0.34321372854914195</x:v>
       </x:c>
       <x:c r="W16">
         <x:v>21400</x:v>
@@ -5448,7 +7291,7 @@
         <x:v>165</x:v>
       </x:c>
       <x:c r="Y16">
-        <x:v>12840</x:v>
+        <x:v>0.3338533541341654</x:v>
       </x:c>
       <x:c r="Z16">
         <x:v>64100</x:v>
@@ -5457,7 +7300,7 @@
         <x:v>470</x:v>
       </x:c>
       <x:c r="AB16">
-        <x:v>38460</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -5478,7 +7321,7 @@
         <x:v>95</x:v>
       </x:c>
       <x:c r="P17">
-        <x:v>3900</x:v>
+        <x:v>0.4020618556701031</x:v>
       </x:c>
       <x:c r="Q17">
         <x:v>1800</x:v>
@@ -5487,7 +7330,7 @@
         <x:v>110</x:v>
       </x:c>
       <x:c r="S17">
-        <x:v>900</x:v>
+        <x:v>0.09278350515463918</x:v>
       </x:c>
       <x:c r="T17">
         <x:v>5600</x:v>
@@ -5496,7 +7339,7 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="V17">
-        <x:v>2800</x:v>
+        <x:v>0.28865979381443296</x:v>
       </x:c>
       <x:c r="W17">
         <x:v>4200</x:v>
@@ -5505,7 +7348,7 @@
         <x:v>85</x:v>
       </x:c>
       <x:c r="Y17">
-        <x:v>2100</x:v>
+        <x:v>0.21649484536082475</x:v>
       </x:c>
       <x:c r="Z17">
         <x:v>19400</x:v>
@@ -5514,13 +7357,13 @@
         <x:v>360</x:v>
       </x:c>
       <x:c r="AB17">
-        <x:v>9700</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="L18" t="inlineStr">
         <x:is>
-          <x:t>North</x:t>
+          <x:t>North Total</x:t>
         </x:is>
       </x:c>
       <x:c r="N18">
@@ -5530,7 +7373,7 @@
         <x:v>377</x:v>
       </x:c>
       <x:c r="P18">
-        <x:v>11200</x:v>
+        <x:v>0.21268515001898974</x:v>
       </x:c>
       <x:c r="Q18">
         <x:v>14900</x:v>
@@ -5539,7 +7382,7 @@
         <x:v>420</x:v>
       </x:c>
       <x:c r="S18">
-        <x:v>8570</x:v>
+        <x:v>0.16274211925560197</x:v>
       </x:c>
       <x:c r="T18">
         <x:v>29100</x:v>
@@ -5548,7 +7391,7 @@
         <x:v>343</x:v>
       </x:c>
       <x:c r="V18">
-        <x:v>16750</x:v>
+        <x:v>0.31807823775161415</x:v>
       </x:c>
       <x:c r="W18">
         <x:v>28000</x:v>
@@ -5557,7 +7400,7 @@
         <x:v>450</x:v>
       </x:c>
       <x:c r="Y18">
-        <x:v>16140</x:v>
+        <x:v>0.30649449297379416</x:v>
       </x:c>
       <x:c r="Z18">
         <x:v>92500</x:v>
@@ -5566,7 +7409,7 @@
         <x:v>1590</x:v>
       </x:c>
       <x:c r="AB18">
-        <x:v>52660</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -5587,7 +7430,7 @@
         <x:v>250</x:v>
       </x:c>
       <x:c r="P19">
-        <x:v>800</x:v>
+        <x:v>0.2077922077922078</x:v>
       </x:c>
       <x:c r="Q19">
         <x:v>2800</x:v>
@@ -5596,7 +7439,7 @@
         <x:v>230</x:v>
       </x:c>
       <x:c r="S19">
-        <x:v>1400</x:v>
+        <x:v>0.36363636363636365</x:v>
       </x:c>
       <x:c r="T19">
         <x:v>2100</x:v>
@@ -5605,7 +7448,7 @@
         <x:v>170</x:v>
       </x:c>
       <x:c r="V19">
-        <x:v>1050</x:v>
+        <x:v>0.2727272727272727</x:v>
       </x:c>
       <x:c r="W19">
         <x:v>1200</x:v>
@@ -5614,7 +7457,7 @@
         <x:v>300</x:v>
       </x:c>
       <x:c r="Y19">
-        <x:v>600</x:v>
+        <x:v>0.15584415584415584</x:v>
       </x:c>
       <x:c r="Z19">
         <x:v>7700</x:v>
@@ -5623,7 +7466,7 @@
         <x:v>950</x:v>
       </x:c>
       <x:c r="AB19">
-        <x:v>3850</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -5644,7 +7487,7 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="P20">
-        <x:v>4920</x:v>
+        <x:v>0.17484008528784648</x:v>
       </x:c>
       <x:c r="Q20">
         <x:v>13800</x:v>
@@ -5653,7 +7496,7 @@
         <x:v>180</x:v>
       </x:c>
       <x:c r="S20">
-        <x:v>8280</x:v>
+        <x:v>0.2942430703624733</x:v>
       </x:c>
       <x:c r="T20">
         <x:v>19500</x:v>
@@ -5662,7 +7505,7 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="V20">
-        <x:v>11700</x:v>
+        <x:v>0.4157782515991471</x:v>
       </x:c>
       <x:c r="W20">
         <x:v>5400</x:v>
@@ -5671,7 +7514,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="Y20">
-        <x:v>3240</x:v>
+        <x:v>0.11513859275053305</x:v>
       </x:c>
       <x:c r="Z20">
         <x:v>46900</x:v>
@@ -5680,7 +7523,7 @@
         <x:v>332</x:v>
       </x:c>
       <x:c r="AB20">
-        <x:v>28140</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -5701,7 +7544,7 @@
         <x:v>105</x:v>
       </x:c>
       <x:c r="P21">
-        <x:v>1800</x:v>
+        <x:v>0.18848167539267016</x:v>
       </x:c>
       <x:c r="Q21">
         <x:v>5500</x:v>
@@ -5710,7 +7553,7 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="S21">
-        <x:v>2750</x:v>
+        <x:v>0.2879581151832461</x:v>
       </x:c>
       <x:c r="T21">
         <x:v>7200</x:v>
@@ -5719,7 +7562,7 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="V21">
-        <x:v>3600</x:v>
+        <x:v>0.3769633507853403</x:v>
       </x:c>
       <x:c r="W21">
         <x:v>2800</x:v>
@@ -5728,7 +7571,7 @@
         <x:v>140</x:v>
       </x:c>
       <x:c r="Y21">
-        <x:v>1400</x:v>
+        <x:v>0.14659685863874344</x:v>
       </x:c>
       <x:c r="Z21">
         <x:v>19100</x:v>
@@ -5737,13 +7580,13 @@
         <x:v>393</x:v>
       </x:c>
       <x:c r="AB21">
-        <x:v>9550</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="L22" t="inlineStr">
         <x:is>
-          <x:t>East</x:t>
+          <x:t>East Total</x:t>
         </x:is>
       </x:c>
       <x:c r="N22">
@@ -5753,7 +7596,7 @@
         <x:v>407</x:v>
       </x:c>
       <x:c r="P22">
-        <x:v>7520</x:v>
+        <x:v>0.18103033220991815</x:v>
       </x:c>
       <x:c r="Q22">
         <x:v>22100</x:v>
@@ -5762,7 +7605,7 @@
         <x:v>498</x:v>
       </x:c>
       <x:c r="S22">
-        <x:v>12430</x:v>
+        <x:v>0.2992296581608089</x:v>
       </x:c>
       <x:c r="T22">
         <x:v>28800</x:v>
@@ -5771,7 +7614,7 @@
         <x:v>295</x:v>
       </x:c>
       <x:c r="V22">
-        <x:v>16350</x:v>
+        <x:v>0.39359653346172363</x:v>
       </x:c>
       <x:c r="W22">
         <x:v>9400</x:v>
@@ -5780,7 +7623,7 @@
         <x:v>475</x:v>
       </x:c>
       <x:c r="Y22">
-        <x:v>5240</x:v>
+        <x:v>0.12614347616754934</x:v>
       </x:c>
       <x:c r="Z22">
         <x:v>73700</x:v>
@@ -5789,7 +7632,7 @@
         <x:v>1675</x:v>
       </x:c>
       <x:c r="AB22">
-        <x:v>41540</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -5805,7 +7648,7 @@
         <x:v>1844</x:v>
       </x:c>
       <x:c r="P23">
-        <x:v>57690</x:v>
+        <x:v>0.26268099444495036</x:v>
       </x:c>
       <x:c r="Q23">
         <x:v>66400</x:v>
@@ -5814,7 +7657,7 @@
         <x:v>1721</x:v>
       </x:c>
       <x:c r="S23">
-        <x:v>37370</x:v>
+        <x:v>0.1701575448501958</x:v>
       </x:c>
       <x:c r="T23">
         <x:v>117000</x:v>
@@ -5823,7 +7666,7 @@
         <x:v>1633</x:v>
       </x:c>
       <x:c r="V23">
-        <x:v>66530</x:v>
+        <x:v>0.30293233767416444</x:v>
       </x:c>
       <x:c r="W23">
         <x:v>102900</x:v>
@@ -5832,7 +7675,7 @@
         <x:v>1981</x:v>
       </x:c>
       <x:c r="Y23">
-        <x:v>58030</x:v>
+        <x:v>0.26422912303068935</x:v>
       </x:c>
       <x:c r="Z23">
         <x:v>390300</x:v>
@@ -5841,7 +7684,7 @@
         <x:v>7179</x:v>
       </x:c>
       <x:c r="AB23">
-        <x:v>219620</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5909,16 +7752,16 @@
         </x:is>
       </x:c>
       <x:c r="M5">
-        <x:v>19100</x:v>
+        <x:v>0.18670576735092864</x:v>
       </x:c>
       <x:c r="N5">
-        <x:v>46900</x:v>
+        <x:v>0.191663261136085</x:v>
       </x:c>
       <x:c r="O5">
-        <x:v>7700</x:v>
+        <x:v>0.17782909930715934</x:v>
       </x:c>
       <x:c r="P5">
-        <x:v>73700</x:v>
+        <x:v>0.18882910581603896</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -5928,16 +7771,16 @@
         </x:is>
       </x:c>
       <x:c r="M6">
-        <x:v>19400</x:v>
+        <x:v>0.18963831867057673</x:v>
       </x:c>
       <x:c r="N6">
-        <x:v>64100</x:v>
+        <x:v>0.2619534123416428</x:v>
       </x:c>
       <x:c r="O6">
-        <x:v>9000</x:v>
+        <x:v>0.20785219399538107</x:v>
       </x:c>
       <x:c r="P6">
-        <x:v>92500</x:v>
+        <x:v>0.23699718165513708</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -5947,16 +7790,16 @@
         </x:is>
       </x:c>
       <x:c r="M7">
-        <x:v>27600</x:v>
+        <x:v>0.2697947214076246</x:v>
       </x:c>
       <x:c r="N7">
-        <x:v>62500</x:v>
+        <x:v>0.25541479362484676</x:v>
       </x:c>
       <x:c r="O7">
-        <x:v>10300</x:v>
+        <x:v>0.23787528868360278</x:v>
       </x:c>
       <x:c r="P7">
-        <x:v>100400</x:v>
+        <x:v>0.25723802203433255</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -5966,16 +7809,16 @@
         </x:is>
       </x:c>
       <x:c r="M8">
-        <x:v>36200</x:v>
+        <x:v>0.35386119257087</x:v>
       </x:c>
       <x:c r="N8">
-        <x:v>71200</x:v>
+        <x:v>0.2909685328974254</x:v>
       </x:c>
       <x:c r="O8">
-        <x:v>16300</x:v>
+        <x:v>0.37644341801385683</x:v>
       </x:c>
       <x:c r="P8">
-        <x:v>123700</x:v>
+        <x:v>0.31693569049449144</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -5985,16 +7828,16 @@
         </x:is>
       </x:c>
       <x:c r="M9">
-        <x:v>102300</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="N9">
-        <x:v>244700</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="O9">
-        <x:v>43300</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="P9">
-        <x:v>390300</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -6134,7 +7977,7 @@
     <x:row r="8">
       <x:c r="L8" t="inlineStr">
         <x:is>
-          <x:t>Food</x:t>
+          <x:t>Food Total</x:t>
         </x:is>
       </x:c>
       <x:c r="N8">
@@ -6227,7 +8070,7 @@
     <x:row r="12">
       <x:c r="L12" t="inlineStr">
         <x:is>
-          <x:t>Electronics</x:t>
+          <x:t>Electronics Total</x:t>
         </x:is>
       </x:c>
       <x:c r="N12">
@@ -6320,7 +8163,7 @@
     <x:row r="16">
       <x:c r="L16" t="inlineStr">
         <x:is>
-          <x:t>Clothing</x:t>
+          <x:t>Clothing Total</x:t>
         </x:is>
       </x:c>
       <x:c r="N16">
@@ -6396,16 +8239,6 @@
           <x:t>Q4</x:t>
         </x:is>
       </x:c>
-      <x:c r="U2" t="inlineStr">
-        <x:is>
-          <x:t>Total Sum of Sales</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="V2" t="inlineStr">
-        <x:is>
-          <x:t>Total Sum of Quantity</x:t>
-        </x:is>
-      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="L3" t="inlineStr">
@@ -6453,6 +8286,16 @@
           <x:t>Sum of Quantity</x:t>
         </x:is>
       </x:c>
+      <x:c r="U3" t="inlineStr">
+        <x:is>
+          <x:t>Total Sum of Sales</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="V3" t="inlineStr">
+        <x:is>
+          <x:t>Total Sum of Quantity</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="L4" t="inlineStr">
@@ -6461,31 +8304,31 @@
         </x:is>
       </x:c>
       <x:c r="M4">
-        <x:v>61400</x:v>
+        <x:v>0.15731488598513962</x:v>
       </x:c>
       <x:c r="N4">
         <x:v>698</x:v>
       </x:c>
       <x:c r="O4">
-        <x:v>42900</x:v>
+        <x:v>0.10991544965411222</x:v>
       </x:c>
       <x:c r="P4">
         <x:v>1251</x:v>
       </x:c>
       <x:c r="Q4">
-        <x:v>41700</x:v>
+        <x:v>0.10684089162182936</x:v>
       </x:c>
       <x:c r="R4">
         <x:v>433</x:v>
       </x:c>
       <x:c r="S4">
-        <x:v>47100</x:v>
+        <x:v>0.12067640276710223</x:v>
       </x:c>
       <x:c r="T4">
         <x:v>1483</x:v>
       </x:c>
       <x:c r="U4">
-        <x:v>193100</x:v>
+        <x:v>0.49474763002818345</x:v>
       </x:c>
       <x:c r="V4">
         <x:v>3865</x:v>
@@ -6498,31 +8341,31 @@
         </x:is>
       </x:c>
       <x:c r="M5">
-        <x:v>41500</x:v>
+        <x:v>0.10632846528311556</x:v>
       </x:c>
       <x:c r="N5">
         <x:v>1283</x:v>
       </x:c>
       <x:c r="O5">
-        <x:v>74100</x:v>
+        <x:v>0.18985395849346656</x:v>
       </x:c>
       <x:c r="P5">
         <x:v>382</x:v>
       </x:c>
       <x:c r="Q5">
-        <x:v>24700</x:v>
+        <x:v>0.06328465283115552</x:v>
       </x:c>
       <x:c r="R5">
         <x:v>1288</x:v>
       </x:c>
       <x:c r="S5">
-        <x:v>56900</x:v>
+        <x:v>0.14578529336407892</x:v>
       </x:c>
       <x:c r="T5">
         <x:v>361</x:v>
       </x:c>
       <x:c r="U5">
-        <x:v>197200</x:v>
+        <x:v>0.5052523699718166</x:v>
       </x:c>
       <x:c r="V5">
         <x:v>3314</x:v>
@@ -6535,31 +8378,31 @@
         </x:is>
       </x:c>
       <x:c r="M6">
-        <x:v>102900</x:v>
+        <x:v>0.26364335126825517</x:v>
       </x:c>
       <x:c r="N6">
         <x:v>1981</x:v>
       </x:c>
       <x:c r="O6">
-        <x:v>117000</x:v>
+        <x:v>0.2997694081475788</x:v>
       </x:c>
       <x:c r="P6">
         <x:v>1633</x:v>
       </x:c>
       <x:c r="Q6">
-        <x:v>66400</x:v>
+        <x:v>0.1701255444529849</x:v>
       </x:c>
       <x:c r="R6">
         <x:v>1721</x:v>
       </x:c>
       <x:c r="S6">
-        <x:v>104000</x:v>
+        <x:v>0.26646169613118115</x:v>
       </x:c>
       <x:c r="T6">
         <x:v>1844</x:v>
       </x:c>
       <x:c r="U6">
-        <x:v>390300</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="V6">
         <x:v>7179</x:v>
@@ -6607,16 +8450,6 @@
           <x:t>Food</x:t>
         </x:is>
       </x:c>
-      <x:c r="T4" t="inlineStr">
-        <x:is>
-          <x:t>Total Sum of Sales</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="U4" t="inlineStr">
-        <x:is>
-          <x:t>Total Sum of Cost</x:t>
-        </x:is>
-      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="L5" t="inlineStr">
@@ -6659,6 +8492,16 @@
           <x:t>Sum of Cost</x:t>
         </x:is>
       </x:c>
+      <x:c r="T5" t="inlineStr">
+        <x:is>
+          <x:t>Total Sum of Sales</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="U5" t="inlineStr">
+        <x:is>
+          <x:t>Total Sum of Cost</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="L6" t="inlineStr">
@@ -6675,13 +8518,13 @@
         <x:v>33300</x:v>
       </x:c>
       <x:c r="Q6">
-        <x:v>19980</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="T6">
         <x:v>33300</x:v>
       </x:c>
       <x:c r="U6">
-        <x:v>19980</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -6694,19 +8537,19 @@
         <x:v>7800</x:v>
       </x:c>
       <x:c r="O7">
-        <x:v>3900</x:v>
+        <x:v>0.11839708561020036</x:v>
       </x:c>
       <x:c r="P7">
         <x:v>48400</x:v>
       </x:c>
       <x:c r="Q7">
-        <x:v>29040</x:v>
+        <x:v>0.8816029143897997</x:v>
       </x:c>
       <x:c r="T7">
         <x:v>56200</x:v>
       </x:c>
       <x:c r="U7">
-        <x:v>32940</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -6719,13 +8562,13 @@
         <x:v>54700</x:v>
       </x:c>
       <x:c r="Q8">
-        <x:v>32820</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="T8">
         <x:v>54700</x:v>
       </x:c>
       <x:c r="U8">
-        <x:v>32820</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -6738,56 +8581,56 @@
         <x:v>13500</x:v>
       </x:c>
       <x:c r="O9">
-        <x:v>6750</x:v>
+        <x:v>0.14352540931320434</x:v>
       </x:c>
       <x:c r="P9">
         <x:v>62300</x:v>
       </x:c>
       <x:c r="Q9">
-        <x:v>37380</x:v>
+        <x:v>0.7948118222411227</x:v>
       </x:c>
       <x:c r="R9">
         <x:v>5800</x:v>
       </x:c>
       <x:c r="S9">
-        <x:v>2900</x:v>
+        <x:v>0.06166276844567298</x:v>
       </x:c>
       <x:c r="T9">
         <x:v>81600</x:v>
       </x:c>
       <x:c r="U9">
-        <x:v>47030</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="L10" t="inlineStr">
         <x:is>
-          <x:t>High</x:t>
+          <x:t>High Total</x:t>
         </x:is>
       </x:c>
       <x:c r="N10">
         <x:v>21300</x:v>
       </x:c>
       <x:c r="O10">
-        <x:v>10650</x:v>
+        <x:v>0.08021390374331551</x:v>
       </x:c>
       <x:c r="P10">
         <x:v>198700</x:v>
       </x:c>
       <x:c r="Q10">
-        <x:v>119220</x:v>
+        <x:v>0.8979438126082699</x:v>
       </x:c>
       <x:c r="R10">
         <x:v>5800</x:v>
       </x:c>
       <x:c r="S10">
-        <x:v>2900</x:v>
+        <x:v>0.021842283648414552</x:v>
       </x:c>
       <x:c r="T10">
         <x:v>225800</x:v>
       </x:c>
       <x:c r="U10">
-        <x:v>132770</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="11"/>
@@ -6806,19 +8649,19 @@
         <x:v>6400</x:v>
       </x:c>
       <x:c r="O12">
-        <x:v>3200</x:v>
+        <x:v>0.6956521739130435</x:v>
       </x:c>
       <x:c r="R12">
         <x:v>2800</x:v>
       </x:c>
       <x:c r="S12">
-        <x:v>1400</x:v>
+        <x:v>0.30434782608695654</x:v>
       </x:c>
       <x:c r="T12">
         <x:v>9200</x:v>
       </x:c>
       <x:c r="U12">
-        <x:v>4600</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -6831,19 +8674,19 @@
         <x:v>6000</x:v>
       </x:c>
       <x:c r="O13">
-        <x:v>3000</x:v>
+        <x:v>0.6060606060606061</x:v>
       </x:c>
       <x:c r="R13">
         <x:v>3900</x:v>
       </x:c>
       <x:c r="S13">
-        <x:v>1950</x:v>
+        <x:v>0.3939393939393939</x:v>
       </x:c>
       <x:c r="T13">
         <x:v>9900</x:v>
       </x:c>
       <x:c r="U13">
-        <x:v>4950</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -6856,19 +8699,19 @@
         <x:v>9600</x:v>
       </x:c>
       <x:c r="O14">
-        <x:v>4800</x:v>
+        <x:v>0.7058823529411765</x:v>
       </x:c>
       <x:c r="R14">
         <x:v>4000</x:v>
       </x:c>
       <x:c r="S14">
-        <x:v>2000</x:v>
+        <x:v>0.29411764705882354</x:v>
       </x:c>
       <x:c r="T14">
         <x:v>13600</x:v>
       </x:c>
       <x:c r="U14">
-        <x:v>6800</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -6881,44 +8724,44 @@
         <x:v>4200</x:v>
       </x:c>
       <x:c r="O15">
-        <x:v>2100</x:v>
+        <x:v>0.5675675675675675</x:v>
       </x:c>
       <x:c r="R15">
         <x:v>3200</x:v>
       </x:c>
       <x:c r="S15">
-        <x:v>1600</x:v>
+        <x:v>0.43243243243243246</x:v>
       </x:c>
       <x:c r="T15">
         <x:v>7400</x:v>
       </x:c>
       <x:c r="U15">
-        <x:v>3700</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="L16" t="inlineStr">
         <x:is>
-          <x:t>Low</x:t>
+          <x:t>Low Total</x:t>
         </x:is>
       </x:c>
       <x:c r="N16">
         <x:v>26200</x:v>
       </x:c>
       <x:c r="O16">
-        <x:v>13100</x:v>
+        <x:v>0.6533665835411472</x:v>
       </x:c>
       <x:c r="R16">
         <x:v>13900</x:v>
       </x:c>
       <x:c r="S16">
-        <x:v>6950</x:v>
+        <x:v>0.34663341645885287</x:v>
       </x:c>
       <x:c r="T16">
         <x:v>40100</x:v>
       </x:c>
       <x:c r="U16">
-        <x:v>20050</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="17"/>
@@ -6937,25 +8780,25 @@
         <x:v>12700</x:v>
       </x:c>
       <x:c r="O18">
-        <x:v>6350</x:v>
+        <x:v>0.3744103773584906</x:v>
       </x:c>
       <x:c r="P18">
         <x:v>13600</x:v>
       </x:c>
       <x:c r="Q18">
-        <x:v>8160</x:v>
+        <x:v>0.4811320754716981</x:v>
       </x:c>
       <x:c r="R18">
         <x:v>4900</x:v>
       </x:c>
       <x:c r="S18">
-        <x:v>2450</x:v>
+        <x:v>0.14445754716981132</x:v>
       </x:c>
       <x:c r="T18">
         <x:v>31200</x:v>
       </x:c>
       <x:c r="U18">
-        <x:v>16960</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -6968,25 +8811,25 @@
         <x:v>5600</x:v>
       </x:c>
       <x:c r="O19">
-        <x:v>2800</x:v>
+        <x:v>0.1895734597156398</x:v>
       </x:c>
       <x:c r="P19">
         <x:v>15700</x:v>
       </x:c>
       <x:c r="Q19">
-        <x:v>9420</x:v>
+        <x:v>0.6377792823290453</x:v>
       </x:c>
       <x:c r="R19">
         <x:v>5100</x:v>
       </x:c>
       <x:c r="S19">
-        <x:v>2550</x:v>
+        <x:v>0.17264725795531483</x:v>
       </x:c>
       <x:c r="T19">
         <x:v>26400</x:v>
       </x:c>
       <x:c r="U19">
-        <x:v>14770</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -6999,25 +8842,25 @@
         <x:v>18000</x:v>
       </x:c>
       <x:c r="O20">
-        <x:v>9000</x:v>
+        <x:v>0.5347593582887701</x:v>
       </x:c>
       <x:c r="P20">
         <x:v>7800</x:v>
       </x:c>
       <x:c r="Q20">
-        <x:v>4680</x:v>
+        <x:v>0.27807486631016043</x:v>
       </x:c>
       <x:c r="R20">
         <x:v>6300</x:v>
       </x:c>
       <x:c r="S20">
-        <x:v>3150</x:v>
+        <x:v>0.18716577540106952</x:v>
       </x:c>
       <x:c r="T20">
         <x:v>32100</x:v>
       </x:c>
       <x:c r="U20">
-        <x:v>16830</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -7030,56 +8873,56 @@
         <x:v>18500</x:v>
       </x:c>
       <x:c r="O21">
-        <x:v>9250</x:v>
+        <x:v>0.5071271929824561</x:v>
       </x:c>
       <x:c r="P21">
         <x:v>8900</x:v>
       </x:c>
       <x:c r="Q21">
-        <x:v>5340</x:v>
+        <x:v>0.29276315789473684</x:v>
       </x:c>
       <x:c r="R21">
         <x:v>7300</x:v>
       </x:c>
       <x:c r="S21">
-        <x:v>3650</x:v>
+        <x:v>0.20010964912280702</x:v>
       </x:c>
       <x:c r="T21">
         <x:v>34700</x:v>
       </x:c>
       <x:c r="U21">
-        <x:v>18240</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="L22" t="inlineStr">
         <x:is>
-          <x:t>Medium</x:t>
+          <x:t>Medium Total</x:t>
         </x:is>
       </x:c>
       <x:c r="N22">
         <x:v>54800</x:v>
       </x:c>
       <x:c r="O22">
-        <x:v>27400</x:v>
+        <x:v>0.4101796407185629</x:v>
       </x:c>
       <x:c r="P22">
         <x:v>46000</x:v>
       </x:c>
       <x:c r="Q22">
-        <x:v>27600</x:v>
+        <x:v>0.41317365269461076</x:v>
       </x:c>
       <x:c r="R22">
         <x:v>23600</x:v>
       </x:c>
       <x:c r="S22">
-        <x:v>11800</x:v>
+        <x:v>0.17664670658682635</x:v>
       </x:c>
       <x:c r="T22">
         <x:v>124400</x:v>
       </x:c>
       <x:c r="U22">
-        <x:v>66800</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="23"/>
@@ -7093,25 +8936,25 @@
         <x:v>102300</x:v>
       </x:c>
       <x:c r="O24">
-        <x:v>51150</x:v>
+        <x:v>0.23290228576632366</x:v>
       </x:c>
       <x:c r="P24">
         <x:v>244700</x:v>
       </x:c>
       <x:c r="Q24">
-        <x:v>146820</x:v>
+        <x:v>0.6685183498770604</x:v>
       </x:c>
       <x:c r="R24">
         <x:v>43300</x:v>
       </x:c>
       <x:c r="S24">
-        <x:v>21650</x:v>
+        <x:v>0.09857936435661598</x:v>
       </x:c>
       <x:c r="T24">
         <x:v>390300</x:v>
       </x:c>
       <x:c r="U24">
-        <x:v>219620</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -8231,7 +10074,7 @@
 </file>
 
 <file path=pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:pivotCacheDefinition xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r:id="R6b9f2919a2f74457" createdVersion="3" refreshedVersion="3" minRefreshableVersion="3" recordCount="50">
+<x:pivotCacheDefinition xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r:id="Red8fb75acfd44546" createdVersion="3" refreshedVersion="3" minRefreshableVersion="3" recordCount="50">
   <x:cacheSource type="worksheet">
     <x:worksheetSource ref="A1:J51" sheet="Sheet1"/>
   </x:cacheSource>
@@ -8294,540 +10137,15 @@
         <x:s v="High"/>
       </x:sharedItems>
     </x:cacheField>
-    <x:cacheField name="Date" numFmtId="0">
+    <x:cacheField name="Date" numFmtId="164">
       <x:sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="45301" maxValue="46001"/>
     </x:cacheField>
   </x:cacheFields>
 </x:pivotCacheDefinition>
 </file>
 
-<file path=pivotCache/pivotCacheDefinition10.xml><?xml version="1.0" encoding="utf-8"?>
-<x:pivotCacheDefinition xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r:id="R024eabaf9e13449b" createdVersion="3" refreshedVersion="3" minRefreshableVersion="3" recordCount="50">
-  <x:cacheSource type="worksheet">
-    <x:worksheetSource ref="A1:J51" sheet="Sheet1"/>
-  </x:cacheSource>
-  <x:cacheFields count="10">
-    <x:cacheField name="Region" numFmtId="0">
-      <x:sharedItems count="4">
-        <x:s v="West"/>
-        <x:s v="South"/>
-        <x:s v="North"/>
-        <x:s v="East"/>
-      </x:sharedItems>
-    </x:cacheField>
-    <x:cacheField name="Category" numFmtId="0">
-      <x:sharedItems count="3">
-        <x:s v="Food"/>
-        <x:s v="Electronics"/>
-        <x:s v="Clothing"/>
-      </x:sharedItems>
-    </x:cacheField>
-    <x:cacheField name="Product" numFmtId="0">
-      <x:sharedItems count="9">
-        <x:s v="Tablet"/>
-        <x:s v="Snacks"/>
-        <x:s v="Shoes"/>
-        <x:s v="Phone"/>
-        <x:s v="Laptop"/>
-        <x:s v="Juice"/>
-        <x:s v="Jacket"/>
-        <x:s v="Hat"/>
-        <x:s v="Coffee"/>
-      </x:sharedItems>
-    </x:cacheField>
-    <x:cacheField name="Quarter" numFmtId="0">
-      <x:sharedItems count="4">
-        <x:s v="Q4"/>
-        <x:s v="Q3"/>
-        <x:s v="Q2"/>
-        <x:s v="Q1"/>
-      </x:sharedItems>
-    </x:cacheField>
-    <x:cacheField name="Sales" numFmtId="0">
-      <x:sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="1200" maxValue="25000"/>
-    </x:cacheField>
-    <x:cacheField name="Quantity" numFmtId="0">
-      <x:sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="35" maxValue="400"/>
-    </x:cacheField>
-    <x:cacheField name="Cost" numFmtId="0">
-      <x:sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="600" maxValue="15000"/>
-    </x:cacheField>
-    <x:cacheField name="Channel" numFmtId="0">
-      <x:sharedItems count="2">
-        <x:s v="Retail"/>
-        <x:s v="Online"/>
-      </x:sharedItems>
-    </x:cacheField>
-    <x:cacheField name="Priority" numFmtId="0">
-      <x:sharedItems count="3">
-        <x:s v="Medium"/>
-        <x:s v="Low"/>
-        <x:s v="High"/>
-      </x:sharedItems>
-    </x:cacheField>
-    <x:cacheField name="Date" numFmtId="0">
-      <x:sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="45301" maxValue="46001"/>
-    </x:cacheField>
-  </x:cacheFields>
-</x:pivotCacheDefinition>
-</file>
-
-<file path=pivotCache/pivotCacheDefinition11.xml><?xml version="1.0" encoding="utf-8"?>
-<x:pivotCacheDefinition xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r:id="R854ed2f60322431a" createdVersion="3" refreshedVersion="3" minRefreshableVersion="3" recordCount="12">
-  <x:cacheSource type="worksheet">
-    <x:worksheetSource ref="A1:C13" sheet="CNData"/>
-  </x:cacheSource>
-  <x:cacheFields count="3">
-    <x:cacheField name="地区" numFmtId="0">
-      <x:sharedItems count="4">
-        <x:s v="华北"/>
-        <x:s v="华东"/>
-        <x:s v="华南"/>
-        <x:s v="西南"/>
-      </x:sharedItems>
-    </x:cacheField>
-    <x:cacheField name="品类" numFmtId="0">
-      <x:sharedItems count="3">
-        <x:s v="电子产品"/>
-        <x:s v="服装"/>
-        <x:s v="食品"/>
-      </x:sharedItems>
-    </x:cacheField>
-    <x:cacheField name="销售额" numFmtId="0">
-      <x:sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="2900" maxValue="22000"/>
-    </x:cacheField>
-  </x:cacheFields>
-</x:pivotCacheDefinition>
-</file>
-
 <file path=pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:pivotCacheDefinition xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r:id="Ra3b99a11ea384c4d" createdVersion="3" refreshedVersion="3" minRefreshableVersion="3" recordCount="50">
-  <x:cacheSource type="worksheet">
-    <x:worksheetSource ref="A1:J51" sheet="Sheet1"/>
-  </x:cacheSource>
-  <x:cacheFields count="10">
-    <x:cacheField name="Region" numFmtId="0">
-      <x:sharedItems count="4">
-        <x:s v="East"/>
-        <x:s v="North"/>
-        <x:s v="South"/>
-        <x:s v="West"/>
-      </x:sharedItems>
-    </x:cacheField>
-    <x:cacheField name="Category" numFmtId="0">
-      <x:sharedItems count="3">
-        <x:s v="Clothing"/>
-        <x:s v="Electronics"/>
-        <x:s v="Food"/>
-      </x:sharedItems>
-    </x:cacheField>
-    <x:cacheField name="Product" numFmtId="0">
-      <x:sharedItems count="9">
-        <x:s v="Coffee"/>
-        <x:s v="Hat"/>
-        <x:s v="Jacket"/>
-        <x:s v="Juice"/>
-        <x:s v="Laptop"/>
-        <x:s v="Phone"/>
-        <x:s v="Shoes"/>
-        <x:s v="Snacks"/>
-        <x:s v="Tablet"/>
-      </x:sharedItems>
-    </x:cacheField>
-    <x:cacheField name="Quarter" numFmtId="0">
-      <x:sharedItems count="4">
-        <x:s v="Q1"/>
-        <x:s v="Q2"/>
-        <x:s v="Q3"/>
-        <x:s v="Q4"/>
-      </x:sharedItems>
-    </x:cacheField>
-    <x:cacheField name="Sales" numFmtId="0">
-      <x:sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="1200" maxValue="25000"/>
-    </x:cacheField>
-    <x:cacheField name="Quantity" numFmtId="0">
-      <x:sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="35" maxValue="400"/>
-    </x:cacheField>
-    <x:cacheField name="Cost" numFmtId="0">
-      <x:sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="600" maxValue="15000"/>
-    </x:cacheField>
-    <x:cacheField name="Channel" numFmtId="0">
-      <x:sharedItems count="2">
-        <x:s v="Online"/>
-        <x:s v="Retail"/>
-      </x:sharedItems>
-    </x:cacheField>
-    <x:cacheField name="Priority" numFmtId="0">
-      <x:sharedItems count="3">
-        <x:s v="High"/>
-        <x:s v="Low"/>
-        <x:s v="Medium"/>
-      </x:sharedItems>
-    </x:cacheField>
-    <x:cacheField name="Date" numFmtId="0">
-      <x:sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="45301" maxValue="46001"/>
-    </x:cacheField>
-  </x:cacheFields>
-</x:pivotCacheDefinition>
-</file>
-
-<file path=pivotCache/pivotCacheDefinition3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:pivotCacheDefinition xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r:id="R39695bd9c616481b" createdVersion="3" refreshedVersion="3" minRefreshableVersion="3" recordCount="50">
-  <x:cacheSource type="worksheet">
-    <x:worksheetSource ref="A1:J51" sheet="Sheet1"/>
-  </x:cacheSource>
-  <x:cacheFields count="10">
-    <x:cacheField name="Region" numFmtId="0">
-      <x:sharedItems count="4">
-        <x:s v="West"/>
-        <x:s v="South"/>
-        <x:s v="North"/>
-        <x:s v="East"/>
-      </x:sharedItems>
-    </x:cacheField>
-    <x:cacheField name="Category" numFmtId="0">
-      <x:sharedItems count="3">
-        <x:s v="Food"/>
-        <x:s v="Electronics"/>
-        <x:s v="Clothing"/>
-      </x:sharedItems>
-    </x:cacheField>
-    <x:cacheField name="Product" numFmtId="0">
-      <x:sharedItems count="9">
-        <x:s v="Tablet"/>
-        <x:s v="Snacks"/>
-        <x:s v="Shoes"/>
-        <x:s v="Phone"/>
-        <x:s v="Laptop"/>
-        <x:s v="Juice"/>
-        <x:s v="Jacket"/>
-        <x:s v="Hat"/>
-        <x:s v="Coffee"/>
-      </x:sharedItems>
-    </x:cacheField>
-    <x:cacheField name="Quarter" numFmtId="0">
-      <x:sharedItems count="4">
-        <x:s v="Q4"/>
-        <x:s v="Q3"/>
-        <x:s v="Q2"/>
-        <x:s v="Q1"/>
-      </x:sharedItems>
-    </x:cacheField>
-    <x:cacheField name="Sales" numFmtId="0">
-      <x:sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="1200" maxValue="25000"/>
-    </x:cacheField>
-    <x:cacheField name="Quantity" numFmtId="0">
-      <x:sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="35" maxValue="400"/>
-    </x:cacheField>
-    <x:cacheField name="Cost" numFmtId="0">
-      <x:sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="600" maxValue="15000"/>
-    </x:cacheField>
-    <x:cacheField name="Channel" numFmtId="0">
-      <x:sharedItems count="2">
-        <x:s v="Retail"/>
-        <x:s v="Online"/>
-      </x:sharedItems>
-    </x:cacheField>
-    <x:cacheField name="Priority" numFmtId="0">
-      <x:sharedItems count="3">
-        <x:s v="Medium"/>
-        <x:s v="Low"/>
-        <x:s v="High"/>
-      </x:sharedItems>
-    </x:cacheField>
-    <x:cacheField name="Date" numFmtId="0">
-      <x:sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="45301" maxValue="46001"/>
-    </x:cacheField>
-  </x:cacheFields>
-</x:pivotCacheDefinition>
-</file>
-
-<file path=pivotCache/pivotCacheDefinition4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:pivotCacheDefinition xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r:id="Rff860f48b77c44d7" createdVersion="3" refreshedVersion="3" minRefreshableVersion="3" recordCount="50">
-  <x:cacheSource type="worksheet">
-    <x:worksheetSource ref="A1:J51" sheet="Sheet1"/>
-  </x:cacheSource>
-  <x:cacheFields count="10">
-    <x:cacheField name="Region" numFmtId="0">
-      <x:sharedItems count="4">
-        <x:s v="East"/>
-        <x:s v="North"/>
-        <x:s v="South"/>
-        <x:s v="West"/>
-      </x:sharedItems>
-    </x:cacheField>
-    <x:cacheField name="Category" numFmtId="0">
-      <x:sharedItems count="3">
-        <x:s v="Clothing"/>
-        <x:s v="Electronics"/>
-        <x:s v="Food"/>
-      </x:sharedItems>
-    </x:cacheField>
-    <x:cacheField name="Product" numFmtId="0">
-      <x:sharedItems count="9">
-        <x:s v="Coffee"/>
-        <x:s v="Hat"/>
-        <x:s v="Jacket"/>
-        <x:s v="Juice"/>
-        <x:s v="Laptop"/>
-        <x:s v="Phone"/>
-        <x:s v="Shoes"/>
-        <x:s v="Snacks"/>
-        <x:s v="Tablet"/>
-      </x:sharedItems>
-    </x:cacheField>
-    <x:cacheField name="Quarter" numFmtId="0">
-      <x:sharedItems count="4">
-        <x:s v="Q1"/>
-        <x:s v="Q2"/>
-        <x:s v="Q3"/>
-        <x:s v="Q4"/>
-      </x:sharedItems>
-    </x:cacheField>
-    <x:cacheField name="Sales" numFmtId="0">
-      <x:sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="1200" maxValue="25000"/>
-    </x:cacheField>
-    <x:cacheField name="Quantity" numFmtId="0">
-      <x:sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="35" maxValue="400"/>
-    </x:cacheField>
-    <x:cacheField name="Cost" numFmtId="0">
-      <x:sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="600" maxValue="15000"/>
-    </x:cacheField>
-    <x:cacheField name="Channel" numFmtId="0">
-      <x:sharedItems count="2">
-        <x:s v="Online"/>
-        <x:s v="Retail"/>
-      </x:sharedItems>
-    </x:cacheField>
-    <x:cacheField name="Priority" numFmtId="0">
-      <x:sharedItems count="3">
-        <x:s v="High"/>
-        <x:s v="Low"/>
-        <x:s v="Medium"/>
-      </x:sharedItems>
-    </x:cacheField>
-    <x:cacheField name="Date" numFmtId="0">
-      <x:sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="45301" maxValue="46001"/>
-    </x:cacheField>
-  </x:cacheFields>
-</x:pivotCacheDefinition>
-</file>
-
-<file path=pivotCache/pivotCacheDefinition5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:pivotCacheDefinition xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r:id="Rf7e4111ca9cc4591" createdVersion="3" refreshedVersion="3" minRefreshableVersion="3" recordCount="50">
-  <x:cacheSource type="worksheet">
-    <x:worksheetSource ref="A1:J51" sheet="Sheet1"/>
-  </x:cacheSource>
-  <x:cacheFields count="10">
-    <x:cacheField name="Region" numFmtId="0">
-      <x:sharedItems count="4">
-        <x:s v="East"/>
-        <x:s v="North"/>
-        <x:s v="South"/>
-        <x:s v="West"/>
-      </x:sharedItems>
-    </x:cacheField>
-    <x:cacheField name="Category" numFmtId="0">
-      <x:sharedItems count="3">
-        <x:s v="Clothing"/>
-        <x:s v="Electronics"/>
-        <x:s v="Food"/>
-      </x:sharedItems>
-    </x:cacheField>
-    <x:cacheField name="Product" numFmtId="0">
-      <x:sharedItems count="9">
-        <x:s v="Coffee"/>
-        <x:s v="Hat"/>
-        <x:s v="Jacket"/>
-        <x:s v="Juice"/>
-        <x:s v="Laptop"/>
-        <x:s v="Phone"/>
-        <x:s v="Shoes"/>
-        <x:s v="Snacks"/>
-        <x:s v="Tablet"/>
-      </x:sharedItems>
-    </x:cacheField>
-    <x:cacheField name="Quarter" numFmtId="0">
-      <x:sharedItems count="4">
-        <x:s v="Q1"/>
-        <x:s v="Q2"/>
-        <x:s v="Q3"/>
-        <x:s v="Q4"/>
-      </x:sharedItems>
-    </x:cacheField>
-    <x:cacheField name="Sales" numFmtId="0">
-      <x:sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="1200" maxValue="25000"/>
-    </x:cacheField>
-    <x:cacheField name="Quantity" numFmtId="0">
-      <x:sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="35" maxValue="400"/>
-    </x:cacheField>
-    <x:cacheField name="Cost" numFmtId="0">
-      <x:sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="600" maxValue="15000"/>
-    </x:cacheField>
-    <x:cacheField name="Channel" numFmtId="0">
-      <x:sharedItems count="2">
-        <x:s v="Online"/>
-        <x:s v="Retail"/>
-      </x:sharedItems>
-    </x:cacheField>
-    <x:cacheField name="Priority" numFmtId="0">
-      <x:sharedItems count="3">
-        <x:s v="High"/>
-        <x:s v="Low"/>
-        <x:s v="Medium"/>
-      </x:sharedItems>
-    </x:cacheField>
-    <x:cacheField name="Date" numFmtId="0">
-      <x:sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="45301" maxValue="46001"/>
-    </x:cacheField>
-  </x:cacheFields>
-</x:pivotCacheDefinition>
-</file>
-
-<file path=pivotCache/pivotCacheDefinition6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:pivotCacheDefinition xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r:id="R53c311d18bd646a6" createdVersion="3" refreshedVersion="3" minRefreshableVersion="3" recordCount="50">
-  <x:cacheSource type="worksheet">
-    <x:worksheetSource ref="A1:J51" sheet="Sheet1"/>
-  </x:cacheSource>
-  <x:cacheFields count="10">
-    <x:cacheField name="Region" numFmtId="0">
-      <x:sharedItems count="4">
-        <x:s v="West"/>
-        <x:s v="South"/>
-        <x:s v="North"/>
-        <x:s v="East"/>
-      </x:sharedItems>
-    </x:cacheField>
-    <x:cacheField name="Category" numFmtId="0">
-      <x:sharedItems count="3">
-        <x:s v="Food"/>
-        <x:s v="Electronics"/>
-        <x:s v="Clothing"/>
-      </x:sharedItems>
-    </x:cacheField>
-    <x:cacheField name="Product" numFmtId="0">
-      <x:sharedItems count="9">
-        <x:s v="Tablet"/>
-        <x:s v="Snacks"/>
-        <x:s v="Shoes"/>
-        <x:s v="Phone"/>
-        <x:s v="Laptop"/>
-        <x:s v="Juice"/>
-        <x:s v="Jacket"/>
-        <x:s v="Hat"/>
-        <x:s v="Coffee"/>
-      </x:sharedItems>
-    </x:cacheField>
-    <x:cacheField name="Quarter" numFmtId="0">
-      <x:sharedItems count="4">
-        <x:s v="Q4"/>
-        <x:s v="Q3"/>
-        <x:s v="Q2"/>
-        <x:s v="Q1"/>
-      </x:sharedItems>
-    </x:cacheField>
-    <x:cacheField name="Sales" numFmtId="0">
-      <x:sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="1200" maxValue="25000"/>
-    </x:cacheField>
-    <x:cacheField name="Quantity" numFmtId="0">
-      <x:sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="35" maxValue="400"/>
-    </x:cacheField>
-    <x:cacheField name="Cost" numFmtId="0">
-      <x:sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="600" maxValue="15000"/>
-    </x:cacheField>
-    <x:cacheField name="Channel" numFmtId="0">
-      <x:sharedItems count="2">
-        <x:s v="Retail"/>
-        <x:s v="Online"/>
-      </x:sharedItems>
-    </x:cacheField>
-    <x:cacheField name="Priority" numFmtId="0">
-      <x:sharedItems count="3">
-        <x:s v="Medium"/>
-        <x:s v="Low"/>
-        <x:s v="High"/>
-      </x:sharedItems>
-    </x:cacheField>
-    <x:cacheField name="Date" numFmtId="0">
-      <x:sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="45301" maxValue="46001"/>
-    </x:cacheField>
-  </x:cacheFields>
-</x:pivotCacheDefinition>
-</file>
-
-<file path=pivotCache/pivotCacheDefinition7.xml><?xml version="1.0" encoding="utf-8"?>
-<x:pivotCacheDefinition xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r:id="R31f3bb7d86364277" createdVersion="3" refreshedVersion="3" minRefreshableVersion="3" recordCount="50">
-  <x:cacheSource type="worksheet">
-    <x:worksheetSource ref="A1:J51" sheet="Sheet1"/>
-  </x:cacheSource>
-  <x:cacheFields count="10">
-    <x:cacheField name="Region" numFmtId="0">
-      <x:sharedItems count="4">
-        <x:s v="East"/>
-        <x:s v="North"/>
-        <x:s v="South"/>
-        <x:s v="West"/>
-      </x:sharedItems>
-    </x:cacheField>
-    <x:cacheField name="Category" numFmtId="0">
-      <x:sharedItems count="3">
-        <x:s v="Clothing"/>
-        <x:s v="Electronics"/>
-        <x:s v="Food"/>
-      </x:sharedItems>
-    </x:cacheField>
-    <x:cacheField name="Product" numFmtId="0">
-      <x:sharedItems count="9">
-        <x:s v="Coffee"/>
-        <x:s v="Hat"/>
-        <x:s v="Jacket"/>
-        <x:s v="Juice"/>
-        <x:s v="Laptop"/>
-        <x:s v="Phone"/>
-        <x:s v="Shoes"/>
-        <x:s v="Snacks"/>
-        <x:s v="Tablet"/>
-      </x:sharedItems>
-    </x:cacheField>
-    <x:cacheField name="Quarter" numFmtId="0">
-      <x:sharedItems count="4">
-        <x:s v="Q1"/>
-        <x:s v="Q2"/>
-        <x:s v="Q3"/>
-        <x:s v="Q4"/>
-      </x:sharedItems>
-    </x:cacheField>
-    <x:cacheField name="Sales" numFmtId="0">
-      <x:sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="1200" maxValue="25000"/>
-    </x:cacheField>
-    <x:cacheField name="Quantity" numFmtId="0">
-      <x:sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="35" maxValue="400"/>
-    </x:cacheField>
-    <x:cacheField name="Cost" numFmtId="0">
-      <x:sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="600" maxValue="15000"/>
-    </x:cacheField>
-    <x:cacheField name="Channel" numFmtId="0">
-      <x:sharedItems count="2">
-        <x:s v="Online"/>
-        <x:s v="Retail"/>
-      </x:sharedItems>
-    </x:cacheField>
-    <x:cacheField name="Priority" numFmtId="0">
-      <x:sharedItems count="3">
-        <x:s v="High"/>
-        <x:s v="Low"/>
-        <x:s v="Medium"/>
-      </x:sharedItems>
-    </x:cacheField>
-    <x:cacheField name="Date" numFmtId="0">
-      <x:sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="45301" maxValue="46001"/>
-    </x:cacheField>
-  </x:cacheFields>
-</x:pivotCacheDefinition>
-</file>
-
-<file path=pivotCache/pivotCacheDefinition8.xml><?xml version="1.0" encoding="utf-8"?>
-<x:pivotCacheDefinition xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r:id="R0b84972852b7404d" createdVersion="3" refreshedVersion="3" minRefreshableVersion="3" recordCount="50">
+<x:pivotCacheDefinition xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r:id="R4f7a4f28d64d4901" createdVersion="3" refreshedVersion="3" minRefreshableVersion="3" recordCount="50">
   <x:cacheSource type="worksheet">
     <x:worksheetSource ref="A1:J51" sheet="Sheet1"/>
   </x:cacheSource>
@@ -8973,8 +10291,8 @@
 </x:pivotCacheDefinition>
 </file>
 
-<file path=pivotCache/pivotCacheDefinition9.xml><?xml version="1.0" encoding="utf-8"?>
-<x:pivotCacheDefinition xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r:id="R8df04f5d2b074a21" createdVersion="3" refreshedVersion="3" minRefreshableVersion="3" recordCount="29">
+<file path=pivotCache/pivotCacheDefinition3.xml><?xml version="1.0" encoding="utf-8"?>
+<x:pivotCacheDefinition xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r:id="R237c8f12fa054355" createdVersion="3" refreshedVersion="3" minRefreshableVersion="3" recordCount="29">
   <x:cacheSource type="worksheet">
     <x:worksheetSource ref="A1:J51" sheet="Sheet1"/>
   </x:cacheSource>
@@ -9032,13 +10350,114 @@
         <x:s v="High"/>
       </x:sharedItems>
     </x:cacheField>
-    <x:cacheField name="Date" numFmtId="0">
+    <x:cacheField name="Date" numFmtId="164">
       <x:sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="45301" maxValue="45979"/>
     </x:cacheField>
   </x:cacheFields>
 </x:pivotCacheDefinition>
 </file>
 
+<file path=pivotCache/pivotCacheDefinition4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:pivotCacheDefinition xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r:id="R341dfe75eff34ca9" createdVersion="3" refreshedVersion="3" minRefreshableVersion="3" recordCount="12">
+  <x:cacheSource type="worksheet">
+    <x:worksheetSource ref="A1:C13" sheet="CNData"/>
+  </x:cacheSource>
+  <x:cacheFields count="3">
+    <x:cacheField name="地区" numFmtId="0">
+      <x:sharedItems count="4">
+        <x:s v="华北"/>
+        <x:s v="华东"/>
+        <x:s v="华南"/>
+        <x:s v="西南"/>
+      </x:sharedItems>
+    </x:cacheField>
+    <x:cacheField name="品类" numFmtId="0">
+      <x:sharedItems count="3">
+        <x:s v="电子产品"/>
+        <x:s v="服装"/>
+        <x:s v="食品"/>
+      </x:sharedItems>
+    </x:cacheField>
+    <x:cacheField name="销售额" numFmtId="0">
+      <x:sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="2900" maxValue="22000"/>
+    </x:cacheField>
+  </x:cacheFields>
+</x:pivotCacheDefinition>
+</file>
+
+<file path=pivotCache/pivotCacheDefinition5.xml><?xml version="1.0" encoding="utf-8"?>
+<x:pivotCacheDefinition xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r:id="R6b0d5e0431424bc7" refreshOnLoad="1" createdVersion="3" refreshedVersion="3" minRefreshableVersion="3" recordCount="50">
+  <x:cacheSource type="worksheet">
+    <x:worksheetSource ref="A1:J51" sheet="Sheet1"/>
+  </x:cacheSource>
+  <x:cacheFields count="12">
+    <x:cacheField name="Region" numFmtId="0">
+      <x:sharedItems count="4">
+        <x:s v="East"/>
+        <x:s v="North"/>
+        <x:s v="South"/>
+        <x:s v="West"/>
+      </x:sharedItems>
+    </x:cacheField>
+    <x:cacheField name="Category" numFmtId="0">
+      <x:sharedItems count="3">
+        <x:s v="Clothing"/>
+        <x:s v="Electronics"/>
+        <x:s v="Food"/>
+      </x:sharedItems>
+    </x:cacheField>
+    <x:cacheField name="Product" numFmtId="0">
+      <x:sharedItems count="9">
+        <x:s v="Coffee"/>
+        <x:s v="Hat"/>
+        <x:s v="Jacket"/>
+        <x:s v="Juice"/>
+        <x:s v="Laptop"/>
+        <x:s v="Phone"/>
+        <x:s v="Shoes"/>
+        <x:s v="Snacks"/>
+        <x:s v="Tablet"/>
+      </x:sharedItems>
+    </x:cacheField>
+    <x:cacheField name="Quarter" numFmtId="0">
+      <x:sharedItems count="4">
+        <x:s v="Q1"/>
+        <x:s v="Q2"/>
+        <x:s v="Q3"/>
+        <x:s v="Q4"/>
+      </x:sharedItems>
+    </x:cacheField>
+    <x:cacheField name="Sales" numFmtId="0">
+      <x:sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="1200" maxValue="25000"/>
+    </x:cacheField>
+    <x:cacheField name="Quantity" numFmtId="0">
+      <x:sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="35" maxValue="400"/>
+    </x:cacheField>
+    <x:cacheField name="Cost" numFmtId="0">
+      <x:sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="600" maxValue="15000"/>
+    </x:cacheField>
+    <x:cacheField name="Channel" numFmtId="0">
+      <x:sharedItems count="2">
+        <x:s v="Online"/>
+        <x:s v="Retail"/>
+      </x:sharedItems>
+    </x:cacheField>
+    <x:cacheField name="Priority" numFmtId="0">
+      <x:sharedItems count="3">
+        <x:s v="High"/>
+        <x:s v="Low"/>
+        <x:s v="Medium"/>
+      </x:sharedItems>
+    </x:cacheField>
+    <x:cacheField name="Date" numFmtId="164">
+      <x:sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="45301" maxValue="46001"/>
+    </x:cacheField>
+    <x:cacheField name="Margin" numFmtId="0" formula="Sales-Cost" databaseField="0"/>
+    <x:cacheField name="Tax" numFmtId="0" formula="Sales*0.1" databaseField="0"/>
+  </x:cacheFields>
+</x:pivotCacheDefinition>
+</file>
+
 <file path=pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:pivotCacheRecords xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50">
   <x:r>
@@ -9644,737 +11063,67 @@
 </x:pivotCacheRecords>
 </file>
 
-<file path=pivotCache/pivotCacheRecords10.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=pivotCache/pivotCacheRecords2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:pivotCacheRecords xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50">
   <x:r>
-    <x:x v="2"/>
+    <x:x v="1"/>
     <x:x v="1"/>
     <x:x v="4"/>
-    <x:x v="3"/>
+    <x:x v="0"/>
     <x:n v="12500"/>
     <x:n v="45"/>
     <x:n v="7500"/>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:n v="45672"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="1"/>
-    <x:x v="3"/>
-    <x:x v="3"/>
+    <x:x v="0"/>
+    <x:x v="0"/>
+    <x:x v="0"/>
+  </x:r>
+  <x:r>
+    <x:x v="1"/>
+    <x:x v="1"/>
+    <x:x v="5"/>
+    <x:x v="0"/>
     <x:n v="8900"/>
     <x:n v="120"/>
     <x:n v="5340"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:n v="45698"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
+    <x:x v="1"/>
+    <x:x v="0"/>
+    <x:x v="1"/>
+  </x:r>
+  <x:r>
+    <x:x v="1"/>
+    <x:x v="1"/>
+    <x:x v="8"/>
+    <x:x v="1"/>
     <x:n v="6200"/>
     <x:n v="38"/>
     <x:n v="3720"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:n v="45767"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
+    <x:x v="0"/>
+    <x:x v="2"/>
+    <x:x v="2"/>
+  </x:r>
+  <x:r>
+    <x:x v="1"/>
     <x:x v="1"/>
     <x:x v="4"/>
-    <x:x v="2"/>
+    <x:x v="1"/>
     <x:n v="15800"/>
     <x:n v="55"/>
     <x:n v="9480"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:n v="45785"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="1"/>
+    <x:x v="1"/>
+    <x:x v="0"/>
     <x:x v="3"/>
-    <x:x v="1"/>
+  </x:r>
+  <x:r>
+    <x:x v="1"/>
+    <x:x v="1"/>
+    <x:x v="5"/>
+    <x:x v="2"/>
     <x:n v="11200"/>
     <x:n v="150"/>
     <x:n v="6720"/>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:n v="45850"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:n v="9500"/>
-    <x:n v="62"/>
-    <x:n v="5700"/>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:n v="45935"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="2"/>
-    <x:x v="6"/>
-    <x:x v="3"/>
-    <x:n v="4200"/>
-    <x:n v="85"/>
-    <x:n v="2100"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:n v="45679"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="2"/>
-    <x:x v="2"/>
-    <x:x v="2"/>
-    <x:n v="5600"/>
-    <x:n v="70"/>
-    <x:n v="2800"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:n v="45762"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="2"/>
-    <x:x v="7"/>
-    <x:x v="1"/>
-    <x:n v="1800"/>
-    <x:n v="110"/>
-    <x:n v="900"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:n v="45872"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="2"/>
-    <x:x v="6"/>
-    <x:x v="0"/>
-    <x:n v="7800"/>
-    <x:n v="95"/>
-    <x:n v="3900"/>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:n v="45979"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="0"/>
-    <x:x v="8"/>
-    <x:x v="3"/>
-    <x:n v="2400"/>
-    <x:n v="200"/>
-    <x:n v="1200"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:n v="45717"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:n v="1500"/>
-    <x:n v="180"/>
-    <x:n v="750"/>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:n v="45818"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="0"/>
-    <x:x v="5"/>
-    <x:x v="1"/>
-    <x:n v="1900"/>
-    <x:n v="160"/>
-    <x:n v="950"/>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:n v="45920"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="0"/>
-    <x:x v="8"/>
-    <x:x v="0"/>
-    <x:n v="3200"/>
-    <x:n v="220"/>
-    <x:n v="1600"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:n v="45992"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:x v="3"/>
-    <x:x v="3"/>
-    <x:n v="18500"/>
-    <x:n v="200"/>
-    <x:n v="11100"/>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:n v="45311"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="1"/>
+    <x:x v="0"/>
+    <x:x v="0"/>
     <x:x v="4"/>
-    <x:x v="2"/>
-    <x:n v="22000"/>
-    <x:n v="72"/>
-    <x:n v="13200"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:n v="45427"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:n v="7800"/>
-    <x:n v="48"/>
-    <x:n v="4680"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:n v="45526"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:x v="3"/>
-    <x:x v="0"/>
-    <x:n v="14200"/>
-    <x:n v="165"/>
-    <x:n v="8520"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:n v="45626"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:x v="2"/>
-    <x:x v="3"/>
-    <x:n v="9200"/>
-    <x:n v="110"/>
-    <x:n v="4600"/>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:n v="45336"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:x v="6"/>
-    <x:x v="2"/>
-    <x:n v="6500"/>
-    <x:n v="78"/>
-    <x:n v="3250"/>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:n v="45444"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:x v="7"/>
-    <x:x v="1"/>
-    <x:n v="3100"/>
-    <x:n v="130"/>
-    <x:n v="1550"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:n v="45545"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:x v="2"/>
-    <x:x v="0"/>
-    <x:n v="8800"/>
-    <x:n v="98"/>
-    <x:n v="4400"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:n v="45646"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:x v="5"/>
-    <x:x v="3"/>
-    <x:n v="1800"/>
-    <x:n v="240"/>
-    <x:n v="900"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:n v="45359"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:x v="8"/>
-    <x:x v="2"/>
-    <x:n v="3500"/>
-    <x:n v="280"/>
-    <x:n v="1750"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:n v="45407"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:n v="2200"/>
-    <x:n v="190"/>
-    <x:n v="1100"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:n v="45487"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:x v="5"/>
-    <x:x v="0"/>
-    <x:n v="2800"/>
-    <x:n v="210"/>
-    <x:n v="1400"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:n v="45583"/>
-  </x:r>
-  <x:r>
-    <x:x v="3"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:x v="3"/>
-    <x:n v="5400"/>
-    <x:n v="35"/>
-    <x:n v="3240"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:n v="45716"/>
-  </x:r>
-  <x:r>
-    <x:x v="3"/>
-    <x:x v="1"/>
-    <x:x v="4"/>
-    <x:x v="2"/>
-    <x:n v="19500"/>
-    <x:n v="65"/>
-    <x:n v="11700"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:n v="45797"/>
-  </x:r>
-  <x:r>
-    <x:x v="3"/>
-    <x:x v="1"/>
-    <x:x v="3"/>
-    <x:x v="1"/>
-    <x:n v="13800"/>
-    <x:n v="180"/>
-    <x:n v="8280"/>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:n v="45884"/>
-  </x:r>
-  <x:r>
-    <x:x v="3"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:n v="8200"/>
-    <x:n v="52"/>
-    <x:n v="4920"/>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:n v="45963"/>
-  </x:r>
-  <x:r>
-    <x:x v="3"/>
-    <x:x v="2"/>
-    <x:x v="7"/>
-    <x:x v="3"/>
-    <x:n v="2800"/>
-    <x:n v="140"/>
-    <x:n v="1400"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:n v="45662"/>
-  </x:r>
-  <x:r>
-    <x:x v="3"/>
-    <x:x v="2"/>
-    <x:x v="6"/>
-    <x:x v="2"/>
-    <x:n v="7200"/>
-    <x:n v="60"/>
-    <x:n v="3600"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:n v="45826"/>
-  </x:r>
-  <x:r>
-    <x:x v="3"/>
-    <x:x v="2"/>
-    <x:x v="2"/>
-    <x:x v="1"/>
-    <x:n v="5500"/>
-    <x:n v="88"/>
-    <x:n v="2750"/>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:n v="45925"/>
-  </x:r>
-  <x:r>
-    <x:x v="3"/>
-    <x:x v="2"/>
-    <x:x v="7"/>
-    <x:x v="0"/>
-    <x:n v="3600"/>
-    <x:n v="105"/>
-    <x:n v="1800"/>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:n v="46001"/>
-  </x:r>
-  <x:r>
-    <x:x v="3"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:x v="3"/>
-    <x:n v="1200"/>
-    <x:n v="300"/>
-    <x:n v="600"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:n v="45731"/>
-  </x:r>
-  <x:r>
-    <x:x v="3"/>
-    <x:x v="0"/>
-    <x:x v="5"/>
-    <x:x v="2"/>
-    <x:n v="2100"/>
-    <x:n v="170"/>
-    <x:n v="1050"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:n v="45777"/>
-  </x:r>
-  <x:r>
-    <x:x v="3"/>
-    <x:x v="0"/>
-    <x:x v="8"/>
-    <x:x v="1"/>
-    <x:n v="2800"/>
-    <x:n v="230"/>
-    <x:n v="1400"/>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:n v="45860"/>
-  </x:r>
-  <x:r>
-    <x:x v="3"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:n v="1600"/>
-    <x:n v="250"/>
-    <x:n v="800"/>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:n v="45958"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:x v="4"/>
-    <x:x v="3"/>
-    <x:n v="20500"/>
-    <x:n v="68"/>
-    <x:n v="12300"/>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:n v="45301"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:x v="3"/>
-    <x:x v="2"/>
-    <x:n v="16800"/>
-    <x:n v="190"/>
-    <x:n v="10080"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:n v="45387"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:n v="8900"/>
-    <x:n v="55"/>
-    <x:n v="5340"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:n v="45516"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:x v="4"/>
-    <x:x v="0"/>
-    <x:n v="25000"/>
-    <x:n v="82"/>
-    <x:n v="15000"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:n v="45611"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:x v="6"/>
-    <x:x v="3"/>
-    <x:n v="11000"/>
-    <x:n v="88"/>
-    <x:n v="5500"/>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:n v="45344"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:x v="2"/>
-    <x:x v="2"/>
-    <x:n v="7500"/>
-    <x:n v="95"/>
-    <x:n v="3750"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:n v="45442"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:x v="7"/>
-    <x:x v="1"/>
-    <x:n v="4200"/>
-    <x:n v="120"/>
-    <x:n v="2100"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:n v="45543"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:x v="6"/>
-    <x:x v="0"/>
-    <x:n v="13500"/>
-    <x:n v="105"/>
-    <x:n v="6750"/>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:n v="45627"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:x v="8"/>
-    <x:x v="3"/>
-    <x:n v="4500"/>
-    <x:n v="350"/>
-    <x:n v="2250"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:n v="45369"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:n v="2800"/>
-    <x:n v="280"/>
-    <x:n v="1400"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:n v="45465"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:x v="5"/>
-    <x:x v="1"/>
-    <x:n v="3200"/>
-    <x:n v="260"/>
-    <x:n v="1600"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:n v="45503"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:x v="8"/>
-    <x:x v="0"/>
-    <x:n v="5800"/>
-    <x:n v="400"/>
-    <x:n v="2900"/>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:n v="45590"/>
-  </x:r>
-</x:pivotCacheRecords>
-</file>
-
-<file path=pivotCache/pivotCacheRecords11.xml><?xml version="1.0" encoding="utf-8"?>
-<x:pivotCacheRecords xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12">
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:n v="18000"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:n v="9500"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:n v="4200"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="0"/>
-    <x:n v="22000"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="1"/>
-    <x:n v="12000"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="2"/>
-    <x:n v="5800"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:n v="15000"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:n v="7800"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:n v="3600"/>
-  </x:r>
-  <x:r>
-    <x:x v="3"/>
-    <x:x v="0"/>
-    <x:n v="11000"/>
-  </x:r>
-  <x:r>
-    <x:x v="3"/>
-    <x:x v="1"/>
-    <x:n v="6500"/>
-  </x:r>
-  <x:r>
-    <x:x v="3"/>
-    <x:x v="2"/>
-    <x:n v="2900"/>
-  </x:r>
-</x:pivotCacheRecords>
-</file>
-
-<file path=pivotCache/pivotCacheRecords2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:pivotCacheRecords xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50">
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:x v="4"/>
-    <x:x v="0"/>
-    <x:n v="12500"/>
-    <x:n v="45"/>
-    <x:n v="7500"/>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:n v="45672"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:x v="5"/>
-    <x:x v="0"/>
-    <x:n v="8900"/>
-    <x:n v="120"/>
-    <x:n v="5340"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:n v="45698"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:x v="8"/>
-    <x:x v="1"/>
-    <x:n v="6200"/>
-    <x:n v="38"/>
-    <x:n v="3720"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:n v="45767"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:x v="4"/>
-    <x:x v="1"/>
-    <x:n v="15800"/>
-    <x:n v="55"/>
-    <x:n v="9480"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:n v="45785"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:x v="5"/>
-    <x:x v="2"/>
-    <x:n v="11200"/>
-    <x:n v="150"/>
-    <x:n v="6720"/>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:n v="45850"/>
   </x:r>
   <x:r>
     <x:x v="1"/>
@@ -10386,7 +11135,7 @@
     <x:n v="5700"/>
     <x:x v="1"/>
     <x:x v="2"/>
-    <x:n v="45935"/>
+    <x:x v="5"/>
   </x:r>
   <x:r>
     <x:x v="1"/>
@@ -10398,7 +11147,7 @@
     <x:n v="2100"/>
     <x:x v="1"/>
     <x:x v="1"/>
-    <x:n v="45679"/>
+    <x:x v="6"/>
   </x:r>
   <x:r>
     <x:x v="1"/>
@@ -10410,7 +11159,7 @@
     <x:n v="2800"/>
     <x:x v="0"/>
     <x:x v="2"/>
-    <x:n v="45762"/>
+    <x:x v="7"/>
   </x:r>
   <x:r>
     <x:x v="1"/>
@@ -10422,7 +11171,7 @@
     <x:n v="900"/>
     <x:x v="1"/>
     <x:x v="1"/>
-    <x:n v="45872"/>
+    <x:x v="8"/>
   </x:r>
   <x:r>
     <x:x v="1"/>
@@ -10434,7 +11183,7 @@
     <x:n v="3900"/>
     <x:x v="0"/>
     <x:x v="0"/>
-    <x:n v="45979"/>
+    <x:x v="9"/>
   </x:r>
   <x:r>
     <x:x v="1"/>
@@ -10446,7 +11195,7 @@
     <x:n v="1200"/>
     <x:x v="1"/>
     <x:x v="1"/>
-    <x:n v="45717"/>
+    <x:x v="10"/>
   </x:r>
   <x:r>
     <x:x v="1"/>
@@ -10458,7 +11207,7 @@
     <x:n v="750"/>
     <x:x v="0"/>
     <x:x v="1"/>
-    <x:n v="45818"/>
+    <x:x v="11"/>
   </x:r>
   <x:r>
     <x:x v="1"/>
@@ -10470,7 +11219,7 @@
     <x:n v="950"/>
     <x:x v="1"/>
     <x:x v="2"/>
-    <x:n v="45920"/>
+    <x:x v="12"/>
   </x:r>
   <x:r>
     <x:x v="1"/>
@@ -10482,7 +11231,7 @@
     <x:n v="1600"/>
     <x:x v="0"/>
     <x:x v="2"/>
-    <x:n v="45992"/>
+    <x:x v="13"/>
   </x:r>
   <x:r>
     <x:x v="2"/>
@@ -10494,7 +11243,7 @@
     <x:n v="11100"/>
     <x:x v="0"/>
     <x:x v="0"/>
-    <x:n v="45311"/>
+    <x:x v="14"/>
   </x:r>
   <x:r>
     <x:x v="2"/>
@@ -10506,7 +11255,7 @@
     <x:n v="13200"/>
     <x:x v="1"/>
     <x:x v="0"/>
-    <x:n v="45427"/>
+    <x:x v="15"/>
   </x:r>
   <x:r>
     <x:x v="2"/>
@@ -10518,7 +11267,7 @@
     <x:n v="4680"/>
     <x:x v="0"/>
     <x:x v="2"/>
-    <x:n v="45526"/>
+    <x:x v="16"/>
   </x:r>
   <x:r>
     <x:x v="2"/>
@@ -10530,7 +11279,7 @@
     <x:n v="8520"/>
     <x:x v="1"/>
     <x:x v="0"/>
-    <x:n v="45626"/>
+    <x:x v="17"/>
   </x:r>
   <x:r>
     <x:x v="2"/>
@@ -10542,7 +11291,7 @@
     <x:n v="4600"/>
     <x:x v="1"/>
     <x:x v="2"/>
-    <x:n v="45336"/>
+    <x:x v="18"/>
   </x:r>
   <x:r>
     <x:x v="2"/>
@@ -10554,7 +11303,7 @@
     <x:n v="3250"/>
     <x:x v="0"/>
     <x:x v="1"/>
-    <x:n v="45444"/>
+    <x:x v="19"/>
   </x:r>
   <x:r>
     <x:x v="2"/>
@@ -10566,7 +11315,7 @@
     <x:n v="1550"/>
     <x:x v="1"/>
     <x:x v="1"/>
-    <x:n v="45545"/>
+    <x:x v="20"/>
   </x:r>
   <x:r>
     <x:x v="2"/>
@@ -10578,7 +11327,7 @@
     <x:n v="4400"/>
     <x:x v="0"/>
     <x:x v="2"/>
-    <x:n v="45646"/>
+    <x:x v="21"/>
   </x:r>
   <x:r>
     <x:x v="2"/>
@@ -10590,7 +11339,7 @@
     <x:n v="900"/>
     <x:x v="1"/>
     <x:x v="1"/>
-    <x:n v="45359"/>
+    <x:x v="22"/>
   </x:r>
   <x:r>
     <x:x v="2"/>
@@ -10602,7 +11351,7 @@
     <x:n v="1750"/>
     <x:x v="0"/>
     <x:x v="2"/>
-    <x:n v="45407"/>
+    <x:x v="23"/>
   </x:r>
   <x:r>
     <x:x v="2"/>
@@ -10614,7 +11363,7 @@
     <x:n v="1100"/>
     <x:x v="1"/>
     <x:x v="1"/>
-    <x:n v="45487"/>
+    <x:x v="24"/>
   </x:r>
   <x:r>
     <x:x v="2"/>
@@ -10626,7 +11375,7 @@
     <x:n v="1400"/>
     <x:x v="0"/>
     <x:x v="2"/>
-    <x:n v="45583"/>
+    <x:x v="25"/>
   </x:r>
   <x:r>
     <x:x v="0"/>
@@ -10638,7 +11387,7 @@
     <x:n v="3240"/>
     <x:x v="0"/>
     <x:x v="2"/>
-    <x:n v="45716"/>
+    <x:x v="26"/>
   </x:r>
   <x:r>
     <x:x v="0"/>
@@ -10650,7 +11399,7 @@
     <x:n v="11700"/>
     <x:x v="1"/>
     <x:x v="0"/>
-    <x:n v="45797"/>
+    <x:x v="27"/>
   </x:r>
   <x:r>
     <x:x v="0"/>
@@ -10662,7 +11411,7 @@
     <x:n v="8280"/>
     <x:x v="0"/>
     <x:x v="0"/>
-    <x:n v="45884"/>
+    <x:x v="28"/>
   </x:r>
   <x:r>
     <x:x v="0"/>
@@ -10674,7 +11423,7 @@
     <x:n v="4920"/>
     <x:x v="1"/>
     <x:x v="2"/>
-    <x:n v="45963"/>
+    <x:x v="29"/>
   </x:r>
   <x:r>
     <x:x v="0"/>
@@ -10686,7 +11435,7 @@
     <x:n v="1400"/>
     <x:x v="1"/>
     <x:x v="1"/>
-    <x:n v="45662"/>
+    <x:x v="30"/>
   </x:r>
   <x:r>
     <x:x v="0"/>
@@ -10698,7 +11447,7 @@
     <x:n v="3600"/>
     <x:x v="0"/>
     <x:x v="2"/>
-    <x:n v="45826"/>
+    <x:x v="31"/>
   </x:r>
   <x:r>
     <x:x v="0"/>
@@ -10710,7 +11459,7 @@
     <x:n v="2750"/>
     <x:x v="1"/>
     <x:x v="2"/>
-    <x:n v="45925"/>
+    <x:x v="32"/>
   </x:r>
   <x:r>
     <x:x v="0"/>
@@ -10722,7 +11471,7 @@
     <x:n v="1800"/>
     <x:x v="0"/>
     <x:x v="1"/>
-    <x:n v="46001"/>
+    <x:x v="33"/>
   </x:r>
   <x:r>
     <x:x v="0"/>
@@ -10734,7 +11483,7 @@
     <x:n v="600"/>
     <x:x v="1"/>
     <x:x v="1"/>
-    <x:n v="45731"/>
+    <x:x v="34"/>
   </x:r>
   <x:r>
     <x:x v="0"/>
@@ -10746,7 +11495,7 @@
     <x:n v="1050"/>
     <x:x v="0"/>
     <x:x v="2"/>
-    <x:n v="45777"/>
+    <x:x v="35"/>
   </x:r>
   <x:r>
     <x:x v="0"/>
@@ -10758,7 +11507,7 @@
     <x:n v="1400"/>
     <x:x v="1"/>
     <x:x v="2"/>
-    <x:n v="45860"/>
+    <x:x v="36"/>
   </x:r>
   <x:r>
     <x:x v="0"/>
@@ -10770,7 +11519,7 @@
     <x:n v="800"/>
     <x:x v="0"/>
     <x:x v="1"/>
-    <x:n v="45958"/>
+    <x:x v="37"/>
   </x:r>
   <x:r>
     <x:x v="3"/>
@@ -10782,7 +11531,7 @@
     <x:n v="12300"/>
     <x:x v="0"/>
     <x:x v="0"/>
-    <x:n v="45301"/>
+    <x:x v="38"/>
   </x:r>
   <x:r>
     <x:x v="3"/>
@@ -10794,7 +11543,7 @@
     <x:n v="10080"/>
     <x:x v="1"/>
     <x:x v="0"/>
-    <x:n v="45387"/>
+    <x:x v="39"/>
   </x:r>
   <x:r>
     <x:x v="3"/>
@@ -10806,7 +11555,7 @@
     <x:n v="5340"/>
     <x:x v="0"/>
     <x:x v="2"/>
-    <x:n v="45516"/>
+    <x:x v="40"/>
   </x:r>
   <x:r>
     <x:x v="3"/>
@@ -10818,7 +11567,7 @@
     <x:n v="15000"/>
     <x:x v="1"/>
     <x:x v="0"/>
-    <x:n v="45611"/>
+    <x:x v="41"/>
   </x:r>
   <x:r>
     <x:x v="3"/>
@@ -10830,7 +11579,7 @@
     <x:n v="5500"/>
     <x:x v="1"/>
     <x:x v="2"/>
-    <x:n v="45344"/>
+    <x:x v="42"/>
   </x:r>
   <x:r>
     <x:x v="3"/>
@@ -10842,7 +11591,7 @@
     <x:n v="3750"/>
     <x:x v="0"/>
     <x:x v="2"/>
-    <x:n v="45442"/>
+    <x:x v="43"/>
   </x:r>
   <x:r>
     <x:x v="3"/>
@@ -10854,7 +11603,7 @@
     <x:n v="2100"/>
     <x:x v="1"/>
     <x:x v="1"/>
-    <x:n v="45543"/>
+    <x:x v="44"/>
   </x:r>
   <x:r>
     <x:x v="3"/>
@@ -10866,7 +11615,7 @@
     <x:n v="6750"/>
     <x:x v="0"/>
     <x:x v="0"/>
-    <x:n v="45627"/>
+    <x:x v="45"/>
   </x:r>
   <x:r>
     <x:x v="3"/>
@@ -10878,7 +11627,7 @@
     <x:n v="2250"/>
     <x:x v="0"/>
     <x:x v="2"/>
-    <x:n v="45369"/>
+    <x:x v="46"/>
   </x:r>
   <x:r>
     <x:x v="3"/>
@@ -10890,7 +11639,7 @@
     <x:n v="1400"/>
     <x:x v="0"/>
     <x:x v="2"/>
-    <x:n v="45465"/>
+    <x:x v="47"/>
   </x:r>
   <x:r>
     <x:x v="3"/>
@@ -10902,7 +11651,7 @@
     <x:n v="1600"/>
     <x:x v="1"/>
     <x:x v="1"/>
-    <x:n v="45503"/>
+    <x:x v="48"/>
   </x:r>
   <x:r>
     <x:x v="3"/>
@@ -10914,17 +11663,17 @@
     <x:n v="2900"/>
     <x:x v="0"/>
     <x:x v="0"/>
-    <x:n v="45590"/>
+    <x:x v="49"/>
   </x:r>
 </x:pivotCacheRecords>
 </file>
 
 <file path=pivotCache/pivotCacheRecords3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:pivotCacheRecords xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50">
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="1"/>
-    <x:x v="4"/>
+<x:pivotCacheRecords xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29">
+  <x:r>
+    <x:x v="2"/>
+    <x:x v="0"/>
+    <x:x v="3"/>
     <x:x v="3"/>
     <x:n v="12500"/>
     <x:n v="45"/>
@@ -10935,8 +11684,8 @@
   </x:r>
   <x:r>
     <x:x v="2"/>
-    <x:x v="1"/>
-    <x:x v="3"/>
+    <x:x v="0"/>
+    <x:x v="2"/>
     <x:x v="3"/>
     <x:n v="8900"/>
     <x:n v="120"/>
@@ -10947,7 +11696,7 @@
   </x:r>
   <x:r>
     <x:x v="2"/>
-    <x:x v="1"/>
+    <x:x v="0"/>
     <x:x v="0"/>
     <x:x v="2"/>
     <x:n v="6200"/>
@@ -10959,8 +11708,8 @@
   </x:r>
   <x:r>
     <x:x v="2"/>
-    <x:x v="1"/>
-    <x:x v="4"/>
+    <x:x v="0"/>
+    <x:x v="3"/>
     <x:x v="2"/>
     <x:n v="15800"/>
     <x:n v="55"/>
@@ -10971,8 +11720,8 @@
   </x:r>
   <x:r>
     <x:x v="2"/>
-    <x:x v="1"/>
-    <x:x v="3"/>
+    <x:x v="0"/>
+    <x:x v="2"/>
     <x:x v="1"/>
     <x:n v="11200"/>
     <x:n v="150"/>
@@ -10983,7 +11732,7 @@
   </x:r>
   <x:r>
     <x:x v="2"/>
-    <x:x v="1"/>
+    <x:x v="0"/>
     <x:x v="0"/>
     <x:x v="0"/>
     <x:n v="9500"/>
@@ -10995,8 +11744,8 @@
   </x:r>
   <x:r>
     <x:x v="2"/>
-    <x:x v="2"/>
-    <x:x v="6"/>
+    <x:x v="1"/>
+    <x:x v="4"/>
     <x:x v="3"/>
     <x:n v="4200"/>
     <x:n v="85"/>
@@ -11007,8 +11756,8 @@
   </x:r>
   <x:r>
     <x:x v="2"/>
-    <x:x v="2"/>
-    <x:x v="2"/>
+    <x:x v="1"/>
+    <x:x v="1"/>
     <x:x v="2"/>
     <x:n v="5600"/>
     <x:n v="70"/>
@@ -11019,20 +11768,8 @@
   </x:r>
   <x:r>
     <x:x v="2"/>
-    <x:x v="2"/>
-    <x:x v="7"/>
-    <x:x v="1"/>
-    <x:n v="1800"/>
-    <x:n v="110"/>
-    <x:n v="900"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:n v="45872"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="2"/>
-    <x:x v="6"/>
+    <x:x v="1"/>
+    <x:x v="4"/>
     <x:x v="0"/>
     <x:n v="7800"/>
     <x:n v="95"/>
@@ -11042,57 +11779,9 @@
     <x:n v="45979"/>
   </x:r>
   <x:r>
-    <x:x v="2"/>
-    <x:x v="0"/>
-    <x:x v="8"/>
-    <x:x v="3"/>
-    <x:n v="2400"/>
-    <x:n v="200"/>
-    <x:n v="1200"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:n v="45717"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:n v="1500"/>
-    <x:n v="180"/>
-    <x:n v="750"/>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:n v="45818"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="0"/>
-    <x:x v="5"/>
-    <x:x v="1"/>
-    <x:n v="1900"/>
-    <x:n v="160"/>
-    <x:n v="950"/>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:n v="45920"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="0"/>
-    <x:x v="8"/>
-    <x:x v="0"/>
-    <x:n v="3200"/>
-    <x:n v="220"/>
-    <x:n v="1600"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:n v="45992"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:x v="3"/>
+    <x:x v="1"/>
+    <x:x v="0"/>
+    <x:x v="2"/>
     <x:x v="3"/>
     <x:n v="18500"/>
     <x:n v="200"/>
@@ -11103,8 +11792,8 @@
   </x:r>
   <x:r>
     <x:x v="1"/>
-    <x:x v="1"/>
-    <x:x v="4"/>
+    <x:x v="0"/>
+    <x:x v="3"/>
     <x:x v="2"/>
     <x:n v="22000"/>
     <x:n v="72"/>
@@ -11115,7 +11804,7 @@
   </x:r>
   <x:r>
     <x:x v="1"/>
-    <x:x v="1"/>
+    <x:x v="0"/>
     <x:x v="0"/>
     <x:x v="1"/>
     <x:n v="7800"/>
@@ -11127,8 +11816,8 @@
   </x:r>
   <x:r>
     <x:x v="1"/>
-    <x:x v="1"/>
-    <x:x v="3"/>
+    <x:x v="0"/>
+    <x:x v="2"/>
     <x:x v="0"/>
     <x:n v="14200"/>
     <x:n v="165"/>
@@ -11139,8 +11828,8 @@
   </x:r>
   <x:r>
     <x:x v="1"/>
-    <x:x v="2"/>
-    <x:x v="2"/>
+    <x:x v="1"/>
+    <x:x v="1"/>
     <x:x v="3"/>
     <x:n v="9200"/>
     <x:n v="110"/>
@@ -11151,8 +11840,8 @@
   </x:r>
   <x:r>
     <x:x v="1"/>
-    <x:x v="2"/>
-    <x:x v="6"/>
+    <x:x v="1"/>
+    <x:x v="4"/>
     <x:x v="2"/>
     <x:n v="6500"/>
     <x:n v="78"/>
@@ -11163,20 +11852,8 @@
   </x:r>
   <x:r>
     <x:x v="1"/>
-    <x:x v="2"/>
-    <x:x v="7"/>
-    <x:x v="1"/>
-    <x:n v="3100"/>
-    <x:n v="130"/>
-    <x:n v="1550"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:n v="45545"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:x v="2"/>
+    <x:x v="1"/>
+    <x:x v="1"/>
     <x:x v="0"/>
     <x:n v="8800"/>
     <x:n v="98"/>
@@ -11186,56 +11863,8 @@
     <x:n v="45646"/>
   </x:r>
   <x:r>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:x v="5"/>
     <x:x v="3"/>
-    <x:n v="1800"/>
-    <x:n v="240"/>
-    <x:n v="900"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:n v="45359"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:x v="8"/>
-    <x:x v="2"/>
-    <x:n v="3500"/>
-    <x:n v="280"/>
-    <x:n v="1750"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:n v="45407"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:n v="2200"/>
-    <x:n v="190"/>
-    <x:n v="1100"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:n v="45487"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:x v="5"/>
-    <x:x v="0"/>
-    <x:n v="2800"/>
-    <x:n v="210"/>
-    <x:n v="1400"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:n v="45583"/>
-  </x:r>
-  <x:r>
-    <x:x v="3"/>
-    <x:x v="1"/>
+    <x:x v="0"/>
     <x:x v="0"/>
     <x:x v="3"/>
     <x:n v="5400"/>
@@ -11247,8 +11876,8 @@
   </x:r>
   <x:r>
     <x:x v="3"/>
-    <x:x v="1"/>
-    <x:x v="4"/>
+    <x:x v="0"/>
+    <x:x v="3"/>
     <x:x v="2"/>
     <x:n v="19500"/>
     <x:n v="65"/>
@@ -11259,8 +11888,8 @@
   </x:r>
   <x:r>
     <x:x v="3"/>
-    <x:x v="1"/>
-    <x:x v="3"/>
+    <x:x v="0"/>
+    <x:x v="2"/>
     <x:x v="1"/>
     <x:n v="13800"/>
     <x:n v="180"/>
@@ -11271,7 +11900,7 @@
   </x:r>
   <x:r>
     <x:x v="3"/>
-    <x:x v="1"/>
+    <x:x v="0"/>
     <x:x v="0"/>
     <x:x v="0"/>
     <x:n v="8200"/>
@@ -11283,20 +11912,8 @@
   </x:r>
   <x:r>
     <x:x v="3"/>
-    <x:x v="2"/>
-    <x:x v="7"/>
-    <x:x v="3"/>
-    <x:n v="2800"/>
-    <x:n v="140"/>
-    <x:n v="1400"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:n v="45662"/>
-  </x:r>
-  <x:r>
-    <x:x v="3"/>
-    <x:x v="2"/>
-    <x:x v="6"/>
+    <x:x v="1"/>
+    <x:x v="4"/>
     <x:x v="2"/>
     <x:n v="7200"/>
     <x:n v="60"/>
@@ -11307,8 +11924,8 @@
   </x:r>
   <x:r>
     <x:x v="3"/>
-    <x:x v="2"/>
-    <x:x v="2"/>
+    <x:x v="1"/>
+    <x:x v="1"/>
     <x:x v="1"/>
     <x:n v="5500"/>
     <x:n v="88"/>
@@ -11318,69 +11935,9 @@
     <x:n v="45925"/>
   </x:r>
   <x:r>
+    <x:x v="0"/>
+    <x:x v="0"/>
     <x:x v="3"/>
-    <x:x v="2"/>
-    <x:x v="7"/>
-    <x:x v="0"/>
-    <x:n v="3600"/>
-    <x:n v="105"/>
-    <x:n v="1800"/>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:n v="46001"/>
-  </x:r>
-  <x:r>
-    <x:x v="3"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:x v="3"/>
-    <x:n v="1200"/>
-    <x:n v="300"/>
-    <x:n v="600"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:n v="45731"/>
-  </x:r>
-  <x:r>
-    <x:x v="3"/>
-    <x:x v="0"/>
-    <x:x v="5"/>
-    <x:x v="2"/>
-    <x:n v="2100"/>
-    <x:n v="170"/>
-    <x:n v="1050"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:n v="45777"/>
-  </x:r>
-  <x:r>
-    <x:x v="3"/>
-    <x:x v="0"/>
-    <x:x v="8"/>
-    <x:x v="1"/>
-    <x:n v="2800"/>
-    <x:n v="230"/>
-    <x:n v="1400"/>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:n v="45860"/>
-  </x:r>
-  <x:r>
-    <x:x v="3"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:n v="1600"/>
-    <x:n v="250"/>
-    <x:n v="800"/>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:n v="45958"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:x v="4"/>
     <x:x v="3"/>
     <x:n v="20500"/>
     <x:n v="68"/>
@@ -11391,8 +11948,8 @@
   </x:r>
   <x:r>
     <x:x v="0"/>
-    <x:x v="1"/>
-    <x:x v="3"/>
+    <x:x v="0"/>
+    <x:x v="2"/>
     <x:x v="2"/>
     <x:n v="16800"/>
     <x:n v="190"/>
@@ -11403,7 +11960,7 @@
   </x:r>
   <x:r>
     <x:x v="0"/>
-    <x:x v="1"/>
+    <x:x v="0"/>
     <x:x v="0"/>
     <x:x v="1"/>
     <x:n v="8900"/>
@@ -11415,8 +11972,8 @@
   </x:r>
   <x:r>
     <x:x v="0"/>
-    <x:x v="1"/>
-    <x:x v="4"/>
+    <x:x v="0"/>
+    <x:x v="3"/>
     <x:x v="0"/>
     <x:n v="25000"/>
     <x:n v="82"/>
@@ -11427,8 +11984,8 @@
   </x:r>
   <x:r>
     <x:x v="0"/>
-    <x:x v="2"/>
-    <x:x v="6"/>
+    <x:x v="1"/>
+    <x:x v="4"/>
     <x:x v="3"/>
     <x:n v="11000"/>
     <x:n v="88"/>
@@ -11439,8 +11996,8 @@
   </x:r>
   <x:r>
     <x:x v="0"/>
-    <x:x v="2"/>
-    <x:x v="2"/>
+    <x:x v="1"/>
+    <x:x v="1"/>
     <x:x v="2"/>
     <x:n v="7500"/>
     <x:n v="95"/>
@@ -11451,20 +12008,8 @@
   </x:r>
   <x:r>
     <x:x v="0"/>
-    <x:x v="2"/>
-    <x:x v="7"/>
-    <x:x v="1"/>
-    <x:n v="4200"/>
-    <x:n v="120"/>
-    <x:n v="2100"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:n v="45543"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:x v="6"/>
+    <x:x v="1"/>
+    <x:x v="4"/>
     <x:x v="0"/>
     <x:n v="13500"/>
     <x:n v="105"/>
@@ -11472,59 +12017,76 @@
     <x:x v="1"/>
     <x:x v="2"/>
     <x:n v="45627"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:x v="8"/>
-    <x:x v="3"/>
-    <x:n v="4500"/>
-    <x:n v="350"/>
-    <x:n v="2250"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:n v="45369"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:n v="2800"/>
-    <x:n v="280"/>
-    <x:n v="1400"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:n v="45465"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:x v="5"/>
-    <x:x v="1"/>
-    <x:n v="3200"/>
-    <x:n v="260"/>
-    <x:n v="1600"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:n v="45503"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:x v="8"/>
-    <x:x v="0"/>
-    <x:n v="5800"/>
-    <x:n v="400"/>
-    <x:n v="2900"/>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:n v="45590"/>
   </x:r>
 </x:pivotCacheRecords>
 </file>
 
 <file path=pivotCache/pivotCacheRecords4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:pivotCacheRecords xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12">
+  <x:r>
+    <x:x v="1"/>
+    <x:x v="0"/>
+    <x:n v="18000"/>
+  </x:r>
+  <x:r>
+    <x:x v="1"/>
+    <x:x v="1"/>
+    <x:n v="9500"/>
+  </x:r>
+  <x:r>
+    <x:x v="1"/>
+    <x:x v="2"/>
+    <x:n v="4200"/>
+  </x:r>
+  <x:r>
+    <x:x v="2"/>
+    <x:x v="0"/>
+    <x:n v="22000"/>
+  </x:r>
+  <x:r>
+    <x:x v="2"/>
+    <x:x v="1"/>
+    <x:n v="12000"/>
+  </x:r>
+  <x:r>
+    <x:x v="2"/>
+    <x:x v="2"/>
+    <x:n v="5800"/>
+  </x:r>
+  <x:r>
+    <x:x v="0"/>
+    <x:x v="0"/>
+    <x:n v="15000"/>
+  </x:r>
+  <x:r>
+    <x:x v="0"/>
+    <x:x v="1"/>
+    <x:n v="7800"/>
+  </x:r>
+  <x:r>
+    <x:x v="0"/>
+    <x:x v="2"/>
+    <x:n v="3600"/>
+  </x:r>
+  <x:r>
+    <x:x v="3"/>
+    <x:x v="0"/>
+    <x:n v="11000"/>
+  </x:r>
+  <x:r>
+    <x:x v="3"/>
+    <x:x v="1"/>
+    <x:n v="6500"/>
+  </x:r>
+  <x:r>
+    <x:x v="3"/>
+    <x:x v="2"/>
+    <x:n v="2900"/>
+  </x:r>
+</x:pivotCacheRecords>
+</file>
+
+<file path=pivotCache/pivotCacheRecords5.xml><?xml version="1.0" encoding="utf-8"?>
 <x:pivotCacheRecords xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50">
   <x:r>
     <x:x v="1"/>
@@ -12127,2777 +12689,4 @@
     <x:n v="45590"/>
   </x:r>
 </x:pivotCacheRecords>
-</file>
-
-<file path=pivotCache/pivotCacheRecords5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:pivotCacheRecords xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50">
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:x v="4"/>
-    <x:x v="0"/>
-    <x:n v="12500"/>
-    <x:n v="45"/>
-    <x:n v="7500"/>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:n v="45672"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:x v="5"/>
-    <x:x v="0"/>
-    <x:n v="8900"/>
-    <x:n v="120"/>
-    <x:n v="5340"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:n v="45698"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:x v="8"/>
-    <x:x v="1"/>
-    <x:n v="6200"/>
-    <x:n v="38"/>
-    <x:n v="3720"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:n v="45767"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:x v="4"/>
-    <x:x v="1"/>
-    <x:n v="15800"/>
-    <x:n v="55"/>
-    <x:n v="9480"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:n v="45785"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:x v="5"/>
-    <x:x v="2"/>
-    <x:n v="11200"/>
-    <x:n v="150"/>
-    <x:n v="6720"/>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:n v="45850"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:x v="8"/>
-    <x:x v="3"/>
-    <x:n v="9500"/>
-    <x:n v="62"/>
-    <x:n v="5700"/>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:n v="45935"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:x v="0"/>
-    <x:n v="4200"/>
-    <x:n v="85"/>
-    <x:n v="2100"/>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:n v="45679"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:x v="6"/>
-    <x:x v="1"/>
-    <x:n v="5600"/>
-    <x:n v="70"/>
-    <x:n v="2800"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:n v="45762"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:n v="1800"/>
-    <x:n v="110"/>
-    <x:n v="900"/>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:n v="45872"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:x v="3"/>
-    <x:n v="7800"/>
-    <x:n v="95"/>
-    <x:n v="3900"/>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:n v="45979"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:n v="2400"/>
-    <x:n v="200"/>
-    <x:n v="1200"/>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:n v="45717"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:x v="7"/>
-    <x:x v="1"/>
-    <x:n v="1500"/>
-    <x:n v="180"/>
-    <x:n v="750"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:n v="45818"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:x v="3"/>
-    <x:x v="2"/>
-    <x:n v="1900"/>
-    <x:n v="160"/>
-    <x:n v="950"/>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:n v="45920"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:x v="0"/>
-    <x:x v="3"/>
-    <x:n v="3200"/>
-    <x:n v="220"/>
-    <x:n v="1600"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:n v="45992"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="1"/>
-    <x:x v="5"/>
-    <x:x v="0"/>
-    <x:n v="18500"/>
-    <x:n v="200"/>
-    <x:n v="11100"/>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:n v="45311"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="1"/>
-    <x:x v="4"/>
-    <x:x v="1"/>
-    <x:n v="22000"/>
-    <x:n v="72"/>
-    <x:n v="13200"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:n v="45427"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="1"/>
-    <x:x v="8"/>
-    <x:x v="2"/>
-    <x:n v="7800"/>
-    <x:n v="48"/>
-    <x:n v="4680"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:n v="45526"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="1"/>
-    <x:x v="5"/>
-    <x:x v="3"/>
-    <x:n v="14200"/>
-    <x:n v="165"/>
-    <x:n v="8520"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:n v="45626"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="0"/>
-    <x:x v="6"/>
-    <x:x v="0"/>
-    <x:n v="9200"/>
-    <x:n v="110"/>
-    <x:n v="4600"/>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:n v="45336"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:x v="1"/>
-    <x:n v="6500"/>
-    <x:n v="78"/>
-    <x:n v="3250"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:n v="45444"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:n v="3100"/>
-    <x:n v="130"/>
-    <x:n v="1550"/>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:n v="45545"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="0"/>
-    <x:x v="6"/>
-    <x:x v="3"/>
-    <x:n v="8800"/>
-    <x:n v="98"/>
-    <x:n v="4400"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:n v="45646"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="2"/>
-    <x:x v="3"/>
-    <x:x v="0"/>
-    <x:n v="1800"/>
-    <x:n v="240"/>
-    <x:n v="900"/>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:n v="45359"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="2"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:n v="3500"/>
-    <x:n v="280"/>
-    <x:n v="1750"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:n v="45407"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="2"/>
-    <x:x v="7"/>
-    <x:x v="2"/>
-    <x:n v="2200"/>
-    <x:n v="190"/>
-    <x:n v="1100"/>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:n v="45487"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="2"/>
-    <x:x v="3"/>
-    <x:x v="3"/>
-    <x:n v="2800"/>
-    <x:n v="210"/>
-    <x:n v="1400"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:n v="45583"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:x v="8"/>
-    <x:x v="0"/>
-    <x:n v="5400"/>
-    <x:n v="35"/>
-    <x:n v="3240"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:n v="45716"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:x v="4"/>
-    <x:x v="1"/>
-    <x:n v="19500"/>
-    <x:n v="65"/>
-    <x:n v="11700"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:n v="45797"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:x v="5"/>
-    <x:x v="2"/>
-    <x:n v="13800"/>
-    <x:n v="180"/>
-    <x:n v="8280"/>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:n v="45884"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:x v="8"/>
-    <x:x v="3"/>
-    <x:n v="8200"/>
-    <x:n v="52"/>
-    <x:n v="4920"/>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:n v="45963"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:n v="2800"/>
-    <x:n v="140"/>
-    <x:n v="1400"/>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:n v="45662"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:x v="1"/>
-    <x:n v="7200"/>
-    <x:n v="60"/>
-    <x:n v="3600"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:n v="45826"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:x v="6"/>
-    <x:x v="2"/>
-    <x:n v="5500"/>
-    <x:n v="88"/>
-    <x:n v="2750"/>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:n v="45925"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:x v="3"/>
-    <x:n v="3600"/>
-    <x:n v="105"/>
-    <x:n v="1800"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:n v="46001"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:x v="7"/>
-    <x:x v="0"/>
-    <x:n v="1200"/>
-    <x:n v="300"/>
-    <x:n v="600"/>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:n v="45731"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:x v="3"/>
-    <x:x v="1"/>
-    <x:n v="2100"/>
-    <x:n v="170"/>
-    <x:n v="1050"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:n v="45777"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:n v="2800"/>
-    <x:n v="230"/>
-    <x:n v="1400"/>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:n v="45860"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:x v="7"/>
-    <x:x v="3"/>
-    <x:n v="1600"/>
-    <x:n v="250"/>
-    <x:n v="800"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:n v="45958"/>
-  </x:r>
-  <x:r>
-    <x:x v="3"/>
-    <x:x v="1"/>
-    <x:x v="4"/>
-    <x:x v="0"/>
-    <x:n v="20500"/>
-    <x:n v="68"/>
-    <x:n v="12300"/>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:n v="45301"/>
-  </x:r>
-  <x:r>
-    <x:x v="3"/>
-    <x:x v="1"/>
-    <x:x v="5"/>
-    <x:x v="1"/>
-    <x:n v="16800"/>
-    <x:n v="190"/>
-    <x:n v="10080"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:n v="45387"/>
-  </x:r>
-  <x:r>
-    <x:x v="3"/>
-    <x:x v="1"/>
-    <x:x v="8"/>
-    <x:x v="2"/>
-    <x:n v="8900"/>
-    <x:n v="55"/>
-    <x:n v="5340"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:n v="45516"/>
-  </x:r>
-  <x:r>
-    <x:x v="3"/>
-    <x:x v="1"/>
-    <x:x v="4"/>
-    <x:x v="3"/>
-    <x:n v="25000"/>
-    <x:n v="82"/>
-    <x:n v="15000"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:n v="45611"/>
-  </x:r>
-  <x:r>
-    <x:x v="3"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:x v="0"/>
-    <x:n v="11000"/>
-    <x:n v="88"/>
-    <x:n v="5500"/>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:n v="45344"/>
-  </x:r>
-  <x:r>
-    <x:x v="3"/>
-    <x:x v="0"/>
-    <x:x v="6"/>
-    <x:x v="1"/>
-    <x:n v="7500"/>
-    <x:n v="95"/>
-    <x:n v="3750"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:n v="45442"/>
-  </x:r>
-  <x:r>
-    <x:x v="3"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:n v="4200"/>
-    <x:n v="120"/>
-    <x:n v="2100"/>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:n v="45543"/>
-  </x:r>
-  <x:r>
-    <x:x v="3"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:x v="3"/>
-    <x:n v="13500"/>
-    <x:n v="105"/>
-    <x:n v="6750"/>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:n v="45627"/>
-  </x:r>
-  <x:r>
-    <x:x v="3"/>
-    <x:x v="2"/>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:n v="4500"/>
-    <x:n v="350"/>
-    <x:n v="2250"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:n v="45369"/>
-  </x:r>
-  <x:r>
-    <x:x v="3"/>
-    <x:x v="2"/>
-    <x:x v="7"/>
-    <x:x v="1"/>
-    <x:n v="2800"/>
-    <x:n v="280"/>
-    <x:n v="1400"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:n v="45465"/>
-  </x:r>
-  <x:r>
-    <x:x v="3"/>
-    <x:x v="2"/>
-    <x:x v="3"/>
-    <x:x v="2"/>
-    <x:n v="3200"/>
-    <x:n v="260"/>
-    <x:n v="1600"/>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:n v="45503"/>
-  </x:r>
-  <x:r>
-    <x:x v="3"/>
-    <x:x v="2"/>
-    <x:x v="0"/>
-    <x:x v="3"/>
-    <x:n v="5800"/>
-    <x:n v="400"/>
-    <x:n v="2900"/>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:n v="45590"/>
-  </x:r>
-</x:pivotCacheRecords>
-</file>
-
-<file path=pivotCache/pivotCacheRecords6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:pivotCacheRecords xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50">
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="1"/>
-    <x:x v="4"/>
-    <x:x v="3"/>
-    <x:n v="12500"/>
-    <x:n v="45"/>
-    <x:n v="7500"/>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:n v="45672"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="1"/>
-    <x:x v="3"/>
-    <x:x v="3"/>
-    <x:n v="8900"/>
-    <x:n v="120"/>
-    <x:n v="5340"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:n v="45698"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:n v="6200"/>
-    <x:n v="38"/>
-    <x:n v="3720"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:n v="45767"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="1"/>
-    <x:x v="4"/>
-    <x:x v="2"/>
-    <x:n v="15800"/>
-    <x:n v="55"/>
-    <x:n v="9480"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:n v="45785"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="1"/>
-    <x:x v="3"/>
-    <x:x v="1"/>
-    <x:n v="11200"/>
-    <x:n v="150"/>
-    <x:n v="6720"/>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:n v="45850"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:n v="9500"/>
-    <x:n v="62"/>
-    <x:n v="5700"/>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:n v="45935"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="2"/>
-    <x:x v="6"/>
-    <x:x v="3"/>
-    <x:n v="4200"/>
-    <x:n v="85"/>
-    <x:n v="2100"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:n v="45679"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="2"/>
-    <x:x v="2"/>
-    <x:x v="2"/>
-    <x:n v="5600"/>
-    <x:n v="70"/>
-    <x:n v="2800"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:n v="45762"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="2"/>
-    <x:x v="7"/>
-    <x:x v="1"/>
-    <x:n v="1800"/>
-    <x:n v="110"/>
-    <x:n v="900"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:n v="45872"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="2"/>
-    <x:x v="6"/>
-    <x:x v="0"/>
-    <x:n v="7800"/>
-    <x:n v="95"/>
-    <x:n v="3900"/>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:n v="45979"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="0"/>
-    <x:x v="8"/>
-    <x:x v="3"/>
-    <x:n v="2400"/>
-    <x:n v="200"/>
-    <x:n v="1200"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:n v="45717"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:n v="1500"/>
-    <x:n v="180"/>
-    <x:n v="750"/>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:n v="45818"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="0"/>
-    <x:x v="5"/>
-    <x:x v="1"/>
-    <x:n v="1900"/>
-    <x:n v="160"/>
-    <x:n v="950"/>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:n v="45920"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="0"/>
-    <x:x v="8"/>
-    <x:x v="0"/>
-    <x:n v="3200"/>
-    <x:n v="220"/>
-    <x:n v="1600"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:n v="45992"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:x v="3"/>
-    <x:x v="3"/>
-    <x:n v="18500"/>
-    <x:n v="200"/>
-    <x:n v="11100"/>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:n v="45311"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:x v="4"/>
-    <x:x v="2"/>
-    <x:n v="22000"/>
-    <x:n v="72"/>
-    <x:n v="13200"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:n v="45427"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:n v="7800"/>
-    <x:n v="48"/>
-    <x:n v="4680"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:n v="45526"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:x v="3"/>
-    <x:x v="0"/>
-    <x:n v="14200"/>
-    <x:n v="165"/>
-    <x:n v="8520"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:n v="45626"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:x v="2"/>
-    <x:x v="3"/>
-    <x:n v="9200"/>
-    <x:n v="110"/>
-    <x:n v="4600"/>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:n v="45336"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:x v="6"/>
-    <x:x v="2"/>
-    <x:n v="6500"/>
-    <x:n v="78"/>
-    <x:n v="3250"/>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:n v="45444"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:x v="7"/>
-    <x:x v="1"/>
-    <x:n v="3100"/>
-    <x:n v="130"/>
-    <x:n v="1550"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:n v="45545"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:x v="2"/>
-    <x:x v="0"/>
-    <x:n v="8800"/>
-    <x:n v="98"/>
-    <x:n v="4400"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:n v="45646"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:x v="5"/>
-    <x:x v="3"/>
-    <x:n v="1800"/>
-    <x:n v="240"/>
-    <x:n v="900"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:n v="45359"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:x v="8"/>
-    <x:x v="2"/>
-    <x:n v="3500"/>
-    <x:n v="280"/>
-    <x:n v="1750"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:n v="45407"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:n v="2200"/>
-    <x:n v="190"/>
-    <x:n v="1100"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:n v="45487"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:x v="5"/>
-    <x:x v="0"/>
-    <x:n v="2800"/>
-    <x:n v="210"/>
-    <x:n v="1400"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:n v="45583"/>
-  </x:r>
-  <x:r>
-    <x:x v="3"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:x v="3"/>
-    <x:n v="5400"/>
-    <x:n v="35"/>
-    <x:n v="3240"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:n v="45716"/>
-  </x:r>
-  <x:r>
-    <x:x v="3"/>
-    <x:x v="1"/>
-    <x:x v="4"/>
-    <x:x v="2"/>
-    <x:n v="19500"/>
-    <x:n v="65"/>
-    <x:n v="11700"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:n v="45797"/>
-  </x:r>
-  <x:r>
-    <x:x v="3"/>
-    <x:x v="1"/>
-    <x:x v="3"/>
-    <x:x v="1"/>
-    <x:n v="13800"/>
-    <x:n v="180"/>
-    <x:n v="8280"/>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:n v="45884"/>
-  </x:r>
-  <x:r>
-    <x:x v="3"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:n v="8200"/>
-    <x:n v="52"/>
-    <x:n v="4920"/>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:n v="45963"/>
-  </x:r>
-  <x:r>
-    <x:x v="3"/>
-    <x:x v="2"/>
-    <x:x v="7"/>
-    <x:x v="3"/>
-    <x:n v="2800"/>
-    <x:n v="140"/>
-    <x:n v="1400"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:n v="45662"/>
-  </x:r>
-  <x:r>
-    <x:x v="3"/>
-    <x:x v="2"/>
-    <x:x v="6"/>
-    <x:x v="2"/>
-    <x:n v="7200"/>
-    <x:n v="60"/>
-    <x:n v="3600"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:n v="45826"/>
-  </x:r>
-  <x:r>
-    <x:x v="3"/>
-    <x:x v="2"/>
-    <x:x v="2"/>
-    <x:x v="1"/>
-    <x:n v="5500"/>
-    <x:n v="88"/>
-    <x:n v="2750"/>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:n v="45925"/>
-  </x:r>
-  <x:r>
-    <x:x v="3"/>
-    <x:x v="2"/>
-    <x:x v="7"/>
-    <x:x v="0"/>
-    <x:n v="3600"/>
-    <x:n v="105"/>
-    <x:n v="1800"/>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:n v="46001"/>
-  </x:r>
-  <x:r>
-    <x:x v="3"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:x v="3"/>
-    <x:n v="1200"/>
-    <x:n v="300"/>
-    <x:n v="600"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:n v="45731"/>
-  </x:r>
-  <x:r>
-    <x:x v="3"/>
-    <x:x v="0"/>
-    <x:x v="5"/>
-    <x:x v="2"/>
-    <x:n v="2100"/>
-    <x:n v="170"/>
-    <x:n v="1050"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:n v="45777"/>
-  </x:r>
-  <x:r>
-    <x:x v="3"/>
-    <x:x v="0"/>
-    <x:x v="8"/>
-    <x:x v="1"/>
-    <x:n v="2800"/>
-    <x:n v="230"/>
-    <x:n v="1400"/>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:n v="45860"/>
-  </x:r>
-  <x:r>
-    <x:x v="3"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:n v="1600"/>
-    <x:n v="250"/>
-    <x:n v="800"/>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:n v="45958"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:x v="4"/>
-    <x:x v="3"/>
-    <x:n v="20500"/>
-    <x:n v="68"/>
-    <x:n v="12300"/>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:n v="45301"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:x v="3"/>
-    <x:x v="2"/>
-    <x:n v="16800"/>
-    <x:n v="190"/>
-    <x:n v="10080"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:n v="45387"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:n v="8900"/>
-    <x:n v="55"/>
-    <x:n v="5340"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:n v="45516"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:x v="4"/>
-    <x:x v="0"/>
-    <x:n v="25000"/>
-    <x:n v="82"/>
-    <x:n v="15000"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:n v="45611"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:x v="6"/>
-    <x:x v="3"/>
-    <x:n v="11000"/>
-    <x:n v="88"/>
-    <x:n v="5500"/>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:n v="45344"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:x v="2"/>
-    <x:x v="2"/>
-    <x:n v="7500"/>
-    <x:n v="95"/>
-    <x:n v="3750"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:n v="45442"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:x v="7"/>
-    <x:x v="1"/>
-    <x:n v="4200"/>
-    <x:n v="120"/>
-    <x:n v="2100"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:n v="45543"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:x v="6"/>
-    <x:x v="0"/>
-    <x:n v="13500"/>
-    <x:n v="105"/>
-    <x:n v="6750"/>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:n v="45627"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:x v="8"/>
-    <x:x v="3"/>
-    <x:n v="4500"/>
-    <x:n v="350"/>
-    <x:n v="2250"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:n v="45369"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:n v="2800"/>
-    <x:n v="280"/>
-    <x:n v="1400"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:n v="45465"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:x v="5"/>
-    <x:x v="1"/>
-    <x:n v="3200"/>
-    <x:n v="260"/>
-    <x:n v="1600"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:n v="45503"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:x v="8"/>
-    <x:x v="0"/>
-    <x:n v="5800"/>
-    <x:n v="400"/>
-    <x:n v="2900"/>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:n v="45590"/>
-  </x:r>
-</x:pivotCacheRecords>
-</file>
-
-<file path=pivotCache/pivotCacheRecords7.xml><?xml version="1.0" encoding="utf-8"?>
-<x:pivotCacheRecords xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50">
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:x v="4"/>
-    <x:x v="0"/>
-    <x:n v="12500"/>
-    <x:n v="45"/>
-    <x:n v="7500"/>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:n v="45672"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:x v="5"/>
-    <x:x v="0"/>
-    <x:n v="8900"/>
-    <x:n v="120"/>
-    <x:n v="5340"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:n v="45698"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:x v="8"/>
-    <x:x v="1"/>
-    <x:n v="6200"/>
-    <x:n v="38"/>
-    <x:n v="3720"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:n v="45767"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:x v="4"/>
-    <x:x v="1"/>
-    <x:n v="15800"/>
-    <x:n v="55"/>
-    <x:n v="9480"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:n v="45785"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:x v="5"/>
-    <x:x v="2"/>
-    <x:n v="11200"/>
-    <x:n v="150"/>
-    <x:n v="6720"/>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:n v="45850"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:x v="8"/>
-    <x:x v="3"/>
-    <x:n v="9500"/>
-    <x:n v="62"/>
-    <x:n v="5700"/>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:n v="45935"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:x v="0"/>
-    <x:n v="4200"/>
-    <x:n v="85"/>
-    <x:n v="2100"/>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:n v="45679"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:x v="6"/>
-    <x:x v="1"/>
-    <x:n v="5600"/>
-    <x:n v="70"/>
-    <x:n v="2800"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:n v="45762"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:n v="1800"/>
-    <x:n v="110"/>
-    <x:n v="900"/>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:n v="45872"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:x v="3"/>
-    <x:n v="7800"/>
-    <x:n v="95"/>
-    <x:n v="3900"/>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:n v="45979"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:n v="2400"/>
-    <x:n v="200"/>
-    <x:n v="1200"/>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:n v="45717"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:x v="7"/>
-    <x:x v="1"/>
-    <x:n v="1500"/>
-    <x:n v="180"/>
-    <x:n v="750"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:n v="45818"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:x v="3"/>
-    <x:x v="2"/>
-    <x:n v="1900"/>
-    <x:n v="160"/>
-    <x:n v="950"/>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:n v="45920"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:x v="0"/>
-    <x:x v="3"/>
-    <x:n v="3200"/>
-    <x:n v="220"/>
-    <x:n v="1600"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:n v="45992"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="1"/>
-    <x:x v="5"/>
-    <x:x v="0"/>
-    <x:n v="18500"/>
-    <x:n v="200"/>
-    <x:n v="11100"/>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:n v="45311"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="1"/>
-    <x:x v="4"/>
-    <x:x v="1"/>
-    <x:n v="22000"/>
-    <x:n v="72"/>
-    <x:n v="13200"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:n v="45427"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="1"/>
-    <x:x v="8"/>
-    <x:x v="2"/>
-    <x:n v="7800"/>
-    <x:n v="48"/>
-    <x:n v="4680"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:n v="45526"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="1"/>
-    <x:x v="5"/>
-    <x:x v="3"/>
-    <x:n v="14200"/>
-    <x:n v="165"/>
-    <x:n v="8520"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:n v="45626"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="0"/>
-    <x:x v="6"/>
-    <x:x v="0"/>
-    <x:n v="9200"/>
-    <x:n v="110"/>
-    <x:n v="4600"/>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:n v="45336"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:x v="1"/>
-    <x:n v="6500"/>
-    <x:n v="78"/>
-    <x:n v="3250"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:n v="45444"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:n v="3100"/>
-    <x:n v="130"/>
-    <x:n v="1550"/>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:n v="45545"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="0"/>
-    <x:x v="6"/>
-    <x:x v="3"/>
-    <x:n v="8800"/>
-    <x:n v="98"/>
-    <x:n v="4400"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:n v="45646"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="2"/>
-    <x:x v="3"/>
-    <x:x v="0"/>
-    <x:n v="1800"/>
-    <x:n v="240"/>
-    <x:n v="900"/>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:n v="45359"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="2"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:n v="3500"/>
-    <x:n v="280"/>
-    <x:n v="1750"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:n v="45407"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="2"/>
-    <x:x v="7"/>
-    <x:x v="2"/>
-    <x:n v="2200"/>
-    <x:n v="190"/>
-    <x:n v="1100"/>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:n v="45487"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="2"/>
-    <x:x v="3"/>
-    <x:x v="3"/>
-    <x:n v="2800"/>
-    <x:n v="210"/>
-    <x:n v="1400"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:n v="45583"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:x v="8"/>
-    <x:x v="0"/>
-    <x:n v="5400"/>
-    <x:n v="35"/>
-    <x:n v="3240"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:n v="45716"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:x v="4"/>
-    <x:x v="1"/>
-    <x:n v="19500"/>
-    <x:n v="65"/>
-    <x:n v="11700"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:n v="45797"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:x v="5"/>
-    <x:x v="2"/>
-    <x:n v="13800"/>
-    <x:n v="180"/>
-    <x:n v="8280"/>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:n v="45884"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:x v="8"/>
-    <x:x v="3"/>
-    <x:n v="8200"/>
-    <x:n v="52"/>
-    <x:n v="4920"/>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:n v="45963"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:n v="2800"/>
-    <x:n v="140"/>
-    <x:n v="1400"/>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:n v="45662"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:x v="1"/>
-    <x:n v="7200"/>
-    <x:n v="60"/>
-    <x:n v="3600"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:n v="45826"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:x v="6"/>
-    <x:x v="2"/>
-    <x:n v="5500"/>
-    <x:n v="88"/>
-    <x:n v="2750"/>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:n v="45925"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:x v="3"/>
-    <x:n v="3600"/>
-    <x:n v="105"/>
-    <x:n v="1800"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:n v="46001"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:x v="7"/>
-    <x:x v="0"/>
-    <x:n v="1200"/>
-    <x:n v="300"/>
-    <x:n v="600"/>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:n v="45731"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:x v="3"/>
-    <x:x v="1"/>
-    <x:n v="2100"/>
-    <x:n v="170"/>
-    <x:n v="1050"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:n v="45777"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:n v="2800"/>
-    <x:n v="230"/>
-    <x:n v="1400"/>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:n v="45860"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:x v="7"/>
-    <x:x v="3"/>
-    <x:n v="1600"/>
-    <x:n v="250"/>
-    <x:n v="800"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:n v="45958"/>
-  </x:r>
-  <x:r>
-    <x:x v="3"/>
-    <x:x v="1"/>
-    <x:x v="4"/>
-    <x:x v="0"/>
-    <x:n v="20500"/>
-    <x:n v="68"/>
-    <x:n v="12300"/>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:n v="45301"/>
-  </x:r>
-  <x:r>
-    <x:x v="3"/>
-    <x:x v="1"/>
-    <x:x v="5"/>
-    <x:x v="1"/>
-    <x:n v="16800"/>
-    <x:n v="190"/>
-    <x:n v="10080"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:n v="45387"/>
-  </x:r>
-  <x:r>
-    <x:x v="3"/>
-    <x:x v="1"/>
-    <x:x v="8"/>
-    <x:x v="2"/>
-    <x:n v="8900"/>
-    <x:n v="55"/>
-    <x:n v="5340"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:n v="45516"/>
-  </x:r>
-  <x:r>
-    <x:x v="3"/>
-    <x:x v="1"/>
-    <x:x v="4"/>
-    <x:x v="3"/>
-    <x:n v="25000"/>
-    <x:n v="82"/>
-    <x:n v="15000"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:n v="45611"/>
-  </x:r>
-  <x:r>
-    <x:x v="3"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:x v="0"/>
-    <x:n v="11000"/>
-    <x:n v="88"/>
-    <x:n v="5500"/>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:n v="45344"/>
-  </x:r>
-  <x:r>
-    <x:x v="3"/>
-    <x:x v="0"/>
-    <x:x v="6"/>
-    <x:x v="1"/>
-    <x:n v="7500"/>
-    <x:n v="95"/>
-    <x:n v="3750"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:n v="45442"/>
-  </x:r>
-  <x:r>
-    <x:x v="3"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:n v="4200"/>
-    <x:n v="120"/>
-    <x:n v="2100"/>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:n v="45543"/>
-  </x:r>
-  <x:r>
-    <x:x v="3"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:x v="3"/>
-    <x:n v="13500"/>
-    <x:n v="105"/>
-    <x:n v="6750"/>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:n v="45627"/>
-  </x:r>
-  <x:r>
-    <x:x v="3"/>
-    <x:x v="2"/>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:n v="4500"/>
-    <x:n v="350"/>
-    <x:n v="2250"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:n v="45369"/>
-  </x:r>
-  <x:r>
-    <x:x v="3"/>
-    <x:x v="2"/>
-    <x:x v="7"/>
-    <x:x v="1"/>
-    <x:n v="2800"/>
-    <x:n v="280"/>
-    <x:n v="1400"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:n v="45465"/>
-  </x:r>
-  <x:r>
-    <x:x v="3"/>
-    <x:x v="2"/>
-    <x:x v="3"/>
-    <x:x v="2"/>
-    <x:n v="3200"/>
-    <x:n v="260"/>
-    <x:n v="1600"/>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:n v="45503"/>
-  </x:r>
-  <x:r>
-    <x:x v="3"/>
-    <x:x v="2"/>
-    <x:x v="0"/>
-    <x:x v="3"/>
-    <x:n v="5800"/>
-    <x:n v="400"/>
-    <x:n v="2900"/>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:n v="45590"/>
-  </x:r>
-</x:pivotCacheRecords>
-</file>
-
-<file path=pivotCache/pivotCacheRecords8.xml><?xml version="1.0" encoding="utf-8"?>
-<x:pivotCacheRecords xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50">
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:x v="4"/>
-    <x:x v="0"/>
-    <x:n v="12500"/>
-    <x:n v="45"/>
-    <x:n v="7500"/>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:x v="0"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:x v="5"/>
-    <x:x v="0"/>
-    <x:n v="8900"/>
-    <x:n v="120"/>
-    <x:n v="5340"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:x v="8"/>
-    <x:x v="1"/>
-    <x:n v="6200"/>
-    <x:n v="38"/>
-    <x:n v="3720"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:x v="2"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:x v="4"/>
-    <x:x v="1"/>
-    <x:n v="15800"/>
-    <x:n v="55"/>
-    <x:n v="9480"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:x v="3"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:x v="5"/>
-    <x:x v="2"/>
-    <x:n v="11200"/>
-    <x:n v="150"/>
-    <x:n v="6720"/>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:x v="4"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:x v="8"/>
-    <x:x v="3"/>
-    <x:n v="9500"/>
-    <x:n v="62"/>
-    <x:n v="5700"/>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:x v="5"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:x v="0"/>
-    <x:n v="4200"/>
-    <x:n v="85"/>
-    <x:n v="2100"/>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:x v="6"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:x v="6"/>
-    <x:x v="1"/>
-    <x:n v="5600"/>
-    <x:n v="70"/>
-    <x:n v="2800"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:x v="7"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:n v="1800"/>
-    <x:n v="110"/>
-    <x:n v="900"/>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:x v="8"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:x v="3"/>
-    <x:n v="7800"/>
-    <x:n v="95"/>
-    <x:n v="3900"/>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:x v="9"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:n v="2400"/>
-    <x:n v="200"/>
-    <x:n v="1200"/>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:x v="10"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:x v="7"/>
-    <x:x v="1"/>
-    <x:n v="1500"/>
-    <x:n v="180"/>
-    <x:n v="750"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:x v="11"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:x v="3"/>
-    <x:x v="2"/>
-    <x:n v="1900"/>
-    <x:n v="160"/>
-    <x:n v="950"/>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:x v="12"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:x v="0"/>
-    <x:x v="3"/>
-    <x:n v="3200"/>
-    <x:n v="220"/>
-    <x:n v="1600"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:x v="13"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="1"/>
-    <x:x v="5"/>
-    <x:x v="0"/>
-    <x:n v="18500"/>
-    <x:n v="200"/>
-    <x:n v="11100"/>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:x v="14"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="1"/>
-    <x:x v="4"/>
-    <x:x v="1"/>
-    <x:n v="22000"/>
-    <x:n v="72"/>
-    <x:n v="13200"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:x v="15"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="1"/>
-    <x:x v="8"/>
-    <x:x v="2"/>
-    <x:n v="7800"/>
-    <x:n v="48"/>
-    <x:n v="4680"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:x v="16"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="1"/>
-    <x:x v="5"/>
-    <x:x v="3"/>
-    <x:n v="14200"/>
-    <x:n v="165"/>
-    <x:n v="8520"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:x v="17"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="0"/>
-    <x:x v="6"/>
-    <x:x v="0"/>
-    <x:n v="9200"/>
-    <x:n v="110"/>
-    <x:n v="4600"/>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:x v="18"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:x v="1"/>
-    <x:n v="6500"/>
-    <x:n v="78"/>
-    <x:n v="3250"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:x v="19"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:n v="3100"/>
-    <x:n v="130"/>
-    <x:n v="1550"/>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:x v="20"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="0"/>
-    <x:x v="6"/>
-    <x:x v="3"/>
-    <x:n v="8800"/>
-    <x:n v="98"/>
-    <x:n v="4400"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:x v="21"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="2"/>
-    <x:x v="3"/>
-    <x:x v="0"/>
-    <x:n v="1800"/>
-    <x:n v="240"/>
-    <x:n v="900"/>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:x v="22"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="2"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:n v="3500"/>
-    <x:n v="280"/>
-    <x:n v="1750"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:x v="23"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="2"/>
-    <x:x v="7"/>
-    <x:x v="2"/>
-    <x:n v="2200"/>
-    <x:n v="190"/>
-    <x:n v="1100"/>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:x v="24"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="2"/>
-    <x:x v="3"/>
-    <x:x v="3"/>
-    <x:n v="2800"/>
-    <x:n v="210"/>
-    <x:n v="1400"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:x v="25"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:x v="8"/>
-    <x:x v="0"/>
-    <x:n v="5400"/>
-    <x:n v="35"/>
-    <x:n v="3240"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:x v="26"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:x v="4"/>
-    <x:x v="1"/>
-    <x:n v="19500"/>
-    <x:n v="65"/>
-    <x:n v="11700"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:x v="27"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:x v="5"/>
-    <x:x v="2"/>
-    <x:n v="13800"/>
-    <x:n v="180"/>
-    <x:n v="8280"/>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:x v="28"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:x v="8"/>
-    <x:x v="3"/>
-    <x:n v="8200"/>
-    <x:n v="52"/>
-    <x:n v="4920"/>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:x v="29"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:n v="2800"/>
-    <x:n v="140"/>
-    <x:n v="1400"/>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:x v="30"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:x v="1"/>
-    <x:n v="7200"/>
-    <x:n v="60"/>
-    <x:n v="3600"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:x v="31"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:x v="6"/>
-    <x:x v="2"/>
-    <x:n v="5500"/>
-    <x:n v="88"/>
-    <x:n v="2750"/>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:x v="32"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:x v="3"/>
-    <x:n v="3600"/>
-    <x:n v="105"/>
-    <x:n v="1800"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:x v="33"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:x v="7"/>
-    <x:x v="0"/>
-    <x:n v="1200"/>
-    <x:n v="300"/>
-    <x:n v="600"/>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:x v="34"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:x v="3"/>
-    <x:x v="1"/>
-    <x:n v="2100"/>
-    <x:n v="170"/>
-    <x:n v="1050"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:x v="35"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:n v="2800"/>
-    <x:n v="230"/>
-    <x:n v="1400"/>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:x v="36"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:x v="7"/>
-    <x:x v="3"/>
-    <x:n v="1600"/>
-    <x:n v="250"/>
-    <x:n v="800"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:x v="37"/>
-  </x:r>
-  <x:r>
-    <x:x v="3"/>
-    <x:x v="1"/>
-    <x:x v="4"/>
-    <x:x v="0"/>
-    <x:n v="20500"/>
-    <x:n v="68"/>
-    <x:n v="12300"/>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:x v="38"/>
-  </x:r>
-  <x:r>
-    <x:x v="3"/>
-    <x:x v="1"/>
-    <x:x v="5"/>
-    <x:x v="1"/>
-    <x:n v="16800"/>
-    <x:n v="190"/>
-    <x:n v="10080"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:x v="39"/>
-  </x:r>
-  <x:r>
-    <x:x v="3"/>
-    <x:x v="1"/>
-    <x:x v="8"/>
-    <x:x v="2"/>
-    <x:n v="8900"/>
-    <x:n v="55"/>
-    <x:n v="5340"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:x v="40"/>
-  </x:r>
-  <x:r>
-    <x:x v="3"/>
-    <x:x v="1"/>
-    <x:x v="4"/>
-    <x:x v="3"/>
-    <x:n v="25000"/>
-    <x:n v="82"/>
-    <x:n v="15000"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:x v="41"/>
-  </x:r>
-  <x:r>
-    <x:x v="3"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:x v="0"/>
-    <x:n v="11000"/>
-    <x:n v="88"/>
-    <x:n v="5500"/>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:x v="42"/>
-  </x:r>
-  <x:r>
-    <x:x v="3"/>
-    <x:x v="0"/>
-    <x:x v="6"/>
-    <x:x v="1"/>
-    <x:n v="7500"/>
-    <x:n v="95"/>
-    <x:n v="3750"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:x v="43"/>
-  </x:r>
-  <x:r>
-    <x:x v="3"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:n v="4200"/>
-    <x:n v="120"/>
-    <x:n v="2100"/>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:x v="44"/>
-  </x:r>
-  <x:r>
-    <x:x v="3"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:x v="3"/>
-    <x:n v="13500"/>
-    <x:n v="105"/>
-    <x:n v="6750"/>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:x v="45"/>
-  </x:r>
-  <x:r>
-    <x:x v="3"/>
-    <x:x v="2"/>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:n v="4500"/>
-    <x:n v="350"/>
-    <x:n v="2250"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:x v="46"/>
-  </x:r>
-  <x:r>
-    <x:x v="3"/>
-    <x:x v="2"/>
-    <x:x v="7"/>
-    <x:x v="1"/>
-    <x:n v="2800"/>
-    <x:n v="280"/>
-    <x:n v="1400"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:x v="47"/>
-  </x:r>
-  <x:r>
-    <x:x v="3"/>
-    <x:x v="2"/>
-    <x:x v="3"/>
-    <x:x v="2"/>
-    <x:n v="3200"/>
-    <x:n v="260"/>
-    <x:n v="1600"/>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:x v="48"/>
-  </x:r>
-  <x:r>
-    <x:x v="3"/>
-    <x:x v="2"/>
-    <x:x v="0"/>
-    <x:x v="3"/>
-    <x:n v="5800"/>
-    <x:n v="400"/>
-    <x:n v="2900"/>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:x v="49"/>
-  </x:r>
-</x:pivotCacheRecords>
-</file>
-
-<file path=pivotCache/pivotCacheRecords9.xml><?xml version="1.0" encoding="utf-8"?>
-<x:pivotCacheRecords xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29">
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="0"/>
-    <x:x v="3"/>
-    <x:x v="3"/>
-    <x:n v="12500"/>
-    <x:n v="45"/>
-    <x:n v="7500"/>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:n v="45672"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:x v="3"/>
-    <x:n v="8900"/>
-    <x:n v="120"/>
-    <x:n v="5340"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:n v="45698"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:n v="6200"/>
-    <x:n v="38"/>
-    <x:n v="3720"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:n v="45767"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="0"/>
-    <x:x v="3"/>
-    <x:x v="2"/>
-    <x:n v="15800"/>
-    <x:n v="55"/>
-    <x:n v="9480"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:n v="45785"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:x v="1"/>
-    <x:n v="11200"/>
-    <x:n v="150"/>
-    <x:n v="6720"/>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:n v="45850"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:n v="9500"/>
-    <x:n v="62"/>
-    <x:n v="5700"/>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:n v="45935"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="1"/>
-    <x:x v="4"/>
-    <x:x v="3"/>
-    <x:n v="4200"/>
-    <x:n v="85"/>
-    <x:n v="2100"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:n v="45679"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:n v="5600"/>
-    <x:n v="70"/>
-    <x:n v="2800"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:n v="45762"/>
-  </x:r>
-  <x:r>
-    <x:x v="2"/>
-    <x:x v="1"/>
-    <x:x v="4"/>
-    <x:x v="0"/>
-    <x:n v="7800"/>
-    <x:n v="95"/>
-    <x:n v="3900"/>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:n v="45979"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:x v="3"/>
-    <x:n v="18500"/>
-    <x:n v="200"/>
-    <x:n v="11100"/>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:n v="45311"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:x v="3"/>
-    <x:x v="2"/>
-    <x:n v="22000"/>
-    <x:n v="72"/>
-    <x:n v="13200"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:n v="45427"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:n v="7800"/>
-    <x:n v="48"/>
-    <x:n v="4680"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:n v="45526"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:x v="0"/>
-    <x:n v="14200"/>
-    <x:n v="165"/>
-    <x:n v="8520"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:n v="45626"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:x v="3"/>
-    <x:n v="9200"/>
-    <x:n v="110"/>
-    <x:n v="4600"/>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:n v="45336"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:x v="4"/>
-    <x:x v="2"/>
-    <x:n v="6500"/>
-    <x:n v="78"/>
-    <x:n v="3250"/>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:n v="45444"/>
-  </x:r>
-  <x:r>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:n v="8800"/>
-    <x:n v="98"/>
-    <x:n v="4400"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:n v="45646"/>
-  </x:r>
-  <x:r>
-    <x:x v="3"/>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:x v="3"/>
-    <x:n v="5400"/>
-    <x:n v="35"/>
-    <x:n v="3240"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:n v="45716"/>
-  </x:r>
-  <x:r>
-    <x:x v="3"/>
-    <x:x v="0"/>
-    <x:x v="3"/>
-    <x:x v="2"/>
-    <x:n v="19500"/>
-    <x:n v="65"/>
-    <x:n v="11700"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:n v="45797"/>
-  </x:r>
-  <x:r>
-    <x:x v="3"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:x v="1"/>
-    <x:n v="13800"/>
-    <x:n v="180"/>
-    <x:n v="8280"/>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:n v="45884"/>
-  </x:r>
-  <x:r>
-    <x:x v="3"/>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:n v="8200"/>
-    <x:n v="52"/>
-    <x:n v="4920"/>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:n v="45963"/>
-  </x:r>
-  <x:r>
-    <x:x v="3"/>
-    <x:x v="1"/>
-    <x:x v="4"/>
-    <x:x v="2"/>
-    <x:n v="7200"/>
-    <x:n v="60"/>
-    <x:n v="3600"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:n v="45826"/>
-  </x:r>
-  <x:r>
-    <x:x v="3"/>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:n v="5500"/>
-    <x:n v="88"/>
-    <x:n v="2750"/>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:n v="45925"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:x v="3"/>
-    <x:x v="3"/>
-    <x:n v="20500"/>
-    <x:n v="68"/>
-    <x:n v="12300"/>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:n v="45301"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:x v="2"/>
-    <x:n v="16800"/>
-    <x:n v="190"/>
-    <x:n v="10080"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:n v="45387"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:n v="8900"/>
-    <x:n v="55"/>
-    <x:n v="5340"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:n v="45516"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:x v="3"/>
-    <x:x v="0"/>
-    <x:n v="25000"/>
-    <x:n v="82"/>
-    <x:n v="15000"/>
-    <x:x v="0"/>
-    <x:x v="2"/>
-    <x:n v="45611"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:x v="4"/>
-    <x:x v="3"/>
-    <x:n v="11000"/>
-    <x:n v="88"/>
-    <x:n v="5500"/>
-    <x:x v="0"/>
-    <x:x v="0"/>
-    <x:n v="45344"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:n v="7500"/>
-    <x:n v="95"/>
-    <x:n v="3750"/>
-    <x:x v="1"/>
-    <x:x v="0"/>
-    <x:n v="45442"/>
-  </x:r>
-  <x:r>
-    <x:x v="0"/>
-    <x:x v="1"/>
-    <x:x v="4"/>
-    <x:x v="0"/>
-    <x:n v="13500"/>
-    <x:n v="105"/>
-    <x:n v="6750"/>
-    <x:x v="1"/>
-    <x:x v="2"/>
-    <x:n v="45627"/>
-  </x:r>
-</x:pivotCacheRecords>
 </file>